--- a/template/src/assets/chihuahua.xlsx
+++ b/template/src/assets/chihuahua.xlsx
@@ -1,12 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mythili\Desktop\pet-admin\template\src\assets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536370B5-73F7-4B14-8900-452F12EC1211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1268,15 +1288,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -1286,7 +1307,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1296,42 +1317,40 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1521,25 +1540,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K52"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.75"/>
-    <col customWidth="1" min="2" max="2" width="22.25"/>
-    <col customWidth="1" min="8" max="8" width="21.63"/>
-    <col customWidth="1" min="9" max="9" width="28.25"/>
-    <col customWidth="1" min="10" max="10" width="16.0"/>
-    <col customWidth="1" min="11" max="11" width="39.25"/>
+    <col min="1" max="1" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" customWidth="1"/>
+    <col min="9" max="9" width="28.21875" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1574,11 +1596,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1593,23 +1615,23 @@
       <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J2" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A2 &amp; "" located in "" &amp; B2 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A2 &amp; "" Care Guide and Maintenance Costs in "" &amp; B2 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B2 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Shivaji Nagar, Bangalore&lt;/h2&gt;
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A2 &amp; "" located in "" &amp; B2 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A2 &amp; "" Care Guide and Maintenance Costs in "" &amp; B2 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B2 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Shivaji Nagar, Bangalore&lt;/h2&gt;
 Caring for a Chihuahua puppy in central Bengaluru's Shivaji Nagar requires a structured wellness routine tailored to dense urban environments. To ensure long-term heal"&amp;"th, prioritize high-protein nutrition formulated for toy breeds, daily indoor mental stimulation alongside controlled short walks along quieter streets like Infantry Road, and strict dental hygiene to prevent early periodontal disease. Navigating busy com"&amp;"mercial hubs exposes small pups to urban dust, heat stress, and traffic noise, making consistent climate control, tick prevention, and regular grooming essential. On average, annual maintenance costs in Shivaji Nagar range between ₹15,000 and ₹35,000, cov"&amp;"ering premium puppy kibble, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Shivaji Nagar, Bangalore&lt;/h2&gt;
 Caring for a Chihuahua puppy in central Bengaluru's Shivaji Nagar requires a structured wellness routine tailored to dense urban environments. To ensure long-term health, prioritize high-protein nutrition formulated for toy breeds, daily indoor mental stimulation alongside controlled short walks along quieter streets like Infantry Road, and strict dental hygiene to prevent early periodontal disease. Navigating busy commercial hubs exposes small pups to urban dust, heat stress, and traffic noise, making consistent climate control, tick prevention, and regular grooming essential. On average, annual maintenance costs in Shivaji Nagar range between ₹15,000 and ₹35,000, covering premium puppy kibble, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.</v>
       </c>
       <c r="K2" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A2 &amp; "" in "" &amp; B2 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A2 &amp; "" in "" &amp; B2 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelines"&amp;", area-specific animal welfare laws, nearby vet care).
@@ -1619,11 +1641,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Shivaji Nagar, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What BBMP regulations apply when acquiring a Chihuahua puppy in Shivaji Nagar?&lt;/h3&gt;&lt;p&gt;Pet parents around Commercial Street and Infantry Road must obtain an annual BBMP pet license, register microchip details, and ensure up-to-date rabies vaccinations. Before buying, review ethical sourcing practices or connect with &lt;a href="https://www.peopleforanimalsindia.org"&gt;animal welfare shelter initiatives&lt;/a&gt; to explore local adoption alternatives.&lt;/p&gt;&lt;h3&gt;Where can I access nearby vet care for toy breeds in Shivaji Nagar?&lt;/h3&gt;&lt;p&gt;Veterinary clinics near Russell Market and the Shivaji Nagar Bus Station provide routine immunizations, dental care, and health evaluations for small dogs. If you observe illegal breeding conditions or mistreatment near central commercial zones, contact &lt;a href="https://www.petaindia.com"&gt;animal rights advocacy groups&lt;/a&gt; to lodge a complaint.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for compact apartment living in central Bengaluru?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas are ideal for apartment life due to their small footprint. Daily indoor exercise combined with controlled short walks along quieter lanes near Infantry Road keeps them healthy and well-adjusted.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1638,21 +1660,21 @@
       <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J3" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A3 &amp; "" located in "" &amp; B3 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A3 &amp; "" Care Guide and Maintenance Costs in "" &amp; B3 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B3 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Indiranagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in the bustling urban neighborhood of Indiranagar requires a dedicated wellness and maintenance routine tailored for compact apartment living"&amp;". To maintain optimal health, provide nutrient-dense puppy kibble specifically formulated for toy breeds, prioritize daily indoor play alongside gentle short walks near 100 Feet Road or Defence Colony, and maintain regular dental brushing to avoid early p"&amp;"eriodontitis. High urban traffic and warm local weather mean monitoring for heat sensitivity, implementing strict tick and flea precautions, and keeping up with routine coat maintenance. On average, annual care and maintenance costs for a Chihuahua in Ind"&amp;"iranagar range between ₹15,000 and ₹35,000, covering premium diet requirements, routine veterinary visits, mandatory core vaccinations, parasite preventive treatments, and local grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A3 &amp; "" located in "" &amp; B3 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A3 &amp; "" Care Guide and Maintenance Costs in "" &amp; B3 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B3 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Indiranagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in the bustling urban neighborhood of Indiranagar requires a dedicated wellness and maintenance routine tailored for compact apartment living"&amp;". To maintain optimal health, provide nutrient-dense puppy kibble specifically formulated for toy breeds, prioritize daily indoor play alongside gentle short walks near 100 Feet Road or Defence Colony, and maintain regular dental brushing to avoid early p"&amp;"eriodontitis. High urban traffic and warm local weather mean monitoring for heat sensitivity, implementing strict tick and flea precautions, and keeping up with routine coat maintenance. On average, annual care and maintenance costs for a Chihuahua in Ind"&amp;"iranagar range between ₹15,000 and ₹35,000, covering premium diet requirements, routine veterinary visits, mandatory core vaccinations, parasite preventive treatments, and local grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Indiranagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in the bustling urban neighborhood of Indiranagar requires a dedicated wellness and maintenance routine tailored for compact apartment living. To maintain optimal health, provide nutrient-dense puppy kibble specifically formulated for toy breeds, prioritize daily indoor play alongside gentle short walks near 100 Feet Road or Defence Colony, and maintain regular dental brushing to avoid early periodontitis. High urban traffic and warm local weather mean monitoring for heat sensitivity, implementing strict tick and flea precautions, and keeping up with routine coat maintenance. On average, annual care and maintenance costs for a Chihuahua in Indiranagar range between ₹15,000 and ₹35,000, covering premium diet requirements, routine veterinary visits, mandatory core vaccinations, parasite preventive treatments, and local grooming services.</v>
       </c>
       <c r="K3" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A3 &amp; "" in "" &amp; B3 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A3 &amp; "" in "" &amp; B3 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelines"&amp;", area-specific animal welfare laws, nearby vet care).
@@ -1662,11 +1684,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Indiranagar, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What BBMP licensing and animal welfare laws apply in Indiranagar?&lt;/h3&gt;&lt;p&gt;Pet owners along 100 Feet Road and Defence Colony must secure an annual BBMP pet license, maintain current rabies immunizations, and microchip their puppies. Before buying, review ethical sourcing standards or consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; for adoption options in East Bengaluru.&lt;/p&gt;&lt;h3&gt;Where can I find reliable nearby vet care for Chihuahuas in Indiranagar?&lt;/h3&gt;&lt;p&gt;Veterinary clinics near 12th Main and the Indiranagar Metro Station offer specialized care for toy breeds, including health checks and dental upkeep. If you encounter unsafe breeding practices or neglect around HAL 2nd Stage, report the incident through &lt;a href="https://www.petaindia.com"&gt;animal cruelty reporting channels&lt;/a&gt;.&lt;/p&gt;&lt;h3&gt;Are Chihuahuas suitable for apartment living along 100 Feet Road?&lt;/h3&gt;&lt;p&gt;Yes, their small size makes Chihuahuas ideal for high-density apartment living. Regular indoor playtime paired with short walks through peaceful residential avenues near Defence Colony will keep your puppy healthy and active.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1681,21 +1703,21 @@
       <c r="F4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J4" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A4 &amp; "" located in "" &amp; B4 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A4 &amp; "" Care Guide and Maintenance Costs in "" &amp; B4 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B4 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Koramangala, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in the energetic neighborhood of Koramangala, Bangalore requires consistent wellness management suited to modern urban apartment living. To "&amp;"keep your toy breed thriving near 80 Feet Road and Sony World Junction, prioritize nutrient-dense food formulated for small breeds, routine oral hygiene to combat early dental issues, and daily indoor exercise paired with brief walks in quieter residentia"&amp;"l pockets. High-density living and local climate conditions necessitate regular tick and flea preventive care, up-to-date vaccinations, and proactive hydration monitoring to avoid hypoglycemia. On average, annual maintenance costs for a Chihuahua puppy in"&amp;" Koramangala range between ₹15,000 and ₹35,000, which accounts for high-quality nutrition, periodic veterinary checkups, routine deworming, immunizations, and professional grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A4 &amp; "" located in "" &amp; B4 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A4 &amp; "" Care Guide and Maintenance Costs in "" &amp; B4 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B4 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Koramangala, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in the energetic neighborhood of Koramangala, Bangalore requires consistent wellness management suited to modern urban apartment living. To "&amp;"keep your toy breed thriving near 80 Feet Road and Sony World Junction, prioritize nutrient-dense food formulated for small breeds, routine oral hygiene to combat early dental issues, and daily indoor exercise paired with brief walks in quieter residentia"&amp;"l pockets. High-density living and local climate conditions necessitate regular tick and flea preventive care, up-to-date vaccinations, and proactive hydration monitoring to avoid hypoglycemia. On average, annual maintenance costs for a Chihuahua puppy in"&amp;" Koramangala range between ₹15,000 and ₹35,000, which accounts for high-quality nutrition, periodic veterinary checkups, routine deworming, immunizations, and professional grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Koramangala, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in the energetic neighborhood of Koramangala, Bangalore requires consistent wellness management suited to modern urban apartment living. To keep your toy breed thriving near 80 Feet Road and Sony World Junction, prioritize nutrient-dense food formulated for small breeds, routine oral hygiene to combat early dental issues, and daily indoor exercise paired with brief walks in quieter residential pockets. High-density living and local climate conditions necessitate regular tick and flea preventive care, up-to-date vaccinations, and proactive hydration monitoring to avoid hypoglycemia. On average, annual maintenance costs for a Chihuahua puppy in Koramangala range between ₹15,000 and ₹35,000, which accounts for high-quality nutrition, periodic veterinary checkups, routine deworming, immunizations, and professional grooming services.</v>
       </c>
       <c r="K4" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A4 &amp; "" in "" &amp; B4 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A4 &amp; "" in "" &amp; B4 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelines"&amp;", area-specific animal welfare laws, nearby vet care).
@@ -1705,11 +1727,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Koramangala, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What local pet laws and BBMP guidelines affect dog owners in Koramangala?&lt;/h3&gt;&lt;p&gt;Residents near 80 Feet Road and Jyoti Nivas College Road must register their pets with BBMP, maintain mandatory rabies vaccinations, and follow apartment association rules. To support ethical pet care or explore rehoming, consider supporting local &lt;a href="https://www.peopleforanimalsindia.org"&gt;animal welfare groups&lt;/a&gt; in Bengaluru.&lt;/p&gt;&lt;h3&gt;How do I find trusted veterinary care for toy breeds around Sony World Junction?&lt;/h3&gt;&lt;p&gt;Koramangala features specialized veterinary clinics equipped for toy breed health checks, dental cleanings, and emergency care near Forum Mall. If you encounter illegal breeding or suspected cruelty in the area, report it to &lt;a href="https://www.petaindia.com"&gt;animal rights protection organizations&lt;/a&gt; immediately.&lt;/p&gt;&lt;h3&gt;Is Koramangala suitable for raising a Chihuahua puppy in a high-rise apartment?&lt;/h3&gt;&lt;p&gt;Yes, Koramangala's modern apartment complexes are ideal for toy breeds due to their minimal space requirements. Short, controlled walks around quieter residential blocks off 100 Feet Road alongside regular indoor enrichment ensure your puppy stays active and mentally stimulated.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1724,21 +1746,21 @@
       <c r="F5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>43</v>
       </c>
       <c r="J5" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A5 &amp; "" located in "" &amp; B5 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A5 &amp; "" Care Guide and Maintenance Costs in "" &amp; B5 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B5 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in HSR Layout, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in HSR Layout requires a tailored wellness and maintenance routine suitable for South Bengaluru's active residential hubs. To maintain peak p"&amp;"hysical health, provide high-protein toy-breed nutrition, encourage daily indoor play, and maintain vigilant dental hygiene to guard against early periodontal issues. Navigating bustling sectors near 27th Main Road and the Outer Ring Road introduces expos"&amp;"ure to urban dust, traffic noise, and seasonal humidity, requiring regular coat grooming, proactive tick prevention, and reliable indoor climate control to keep delicate toy breeds comfortable. On average, annual care and maintenance costs in HSR Layout r"&amp;"ange between ₹15,000 and ₹35,000, encompassing premium puppy kibble, routine veterinary checkups, core vaccinations, deworming treatments, and periodic professional grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A5 &amp; "" located in "" &amp; B5 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A5 &amp; "" Care Guide and Maintenance Costs in "" &amp; B5 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B5 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in HSR Layout, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in HSR Layout requires a tailored wellness and maintenance routine suitable for South Bengaluru's active residential hubs. To maintain peak p"&amp;"hysical health, provide high-protein toy-breed nutrition, encourage daily indoor play, and maintain vigilant dental hygiene to guard against early periodontal issues. Navigating bustling sectors near 27th Main Road and the Outer Ring Road introduces expos"&amp;"ure to urban dust, traffic noise, and seasonal humidity, requiring regular coat grooming, proactive tick prevention, and reliable indoor climate control to keep delicate toy breeds comfortable. On average, annual care and maintenance costs in HSR Layout r"&amp;"ange between ₹15,000 and ₹35,000, encompassing premium puppy kibble, routine veterinary checkups, core vaccinations, deworming treatments, and periodic professional grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in HSR Layout, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in HSR Layout requires a tailored wellness and maintenance routine suitable for South Bengaluru's active residential hubs. To maintain peak physical health, provide high-protein toy-breed nutrition, encourage daily indoor play, and maintain vigilant dental hygiene to guard against early periodontal issues. Navigating bustling sectors near 27th Main Road and the Outer Ring Road introduces exposure to urban dust, traffic noise, and seasonal humidity, requiring regular coat grooming, proactive tick prevention, and reliable indoor climate control to keep delicate toy breeds comfortable. On average, annual care and maintenance costs in HSR Layout range between ₹15,000 and ₹35,000, encompassing premium puppy kibble, routine veterinary checkups, core vaccinations, deworming treatments, and periodic professional grooming services.</v>
       </c>
       <c r="K5" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A5 &amp; "" in "" &amp; B5 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A5 &amp; "" in "" &amp; B5 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelines"&amp;", area-specific animal welfare laws, nearby vet care).
@@ -1748,11 +1770,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in HSR Layout, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What BBMP registration mandates apply to Chihuahua puppies in HSR Layout?&lt;/h3&gt;&lt;p&gt;Pet owners along 27th Main and Outer Ring Road must obtain an annual BBMP pet license, register microchip details, and maintain current rabies immunizations. Before bringing home a puppy, consider reviewing local adoption guidelines or reaching out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue organizations&lt;/a&gt; for alternative placement options.&lt;/p&gt;&lt;h3&gt;Where can I find veterinary care for toy breeds around Agara Lake and HSR Layout?&lt;/h3&gt;&lt;p&gt;Several veterinary clinics across Sectors 1 to 7 offer specialized care, dental checkups, and routine vaccinations for small dogs. If you observe unauthorized breeding operations or animal mistreatment near local residential sectors, contact &lt;a href="https://www.petaindia.com"&gt;cruelty prevention advocates&lt;/a&gt; to submit a report.&lt;/p&gt;&lt;h3&gt;How well do Chihuahua puppies adapt to high-rise apartment living in HSR Layout?&lt;/h3&gt;&lt;p&gt;Chihuahuas thrive in apartment environments due to their compact size and low outdoor space requirements. Regular indoor mental engagement along with brief, controlled walks near Agara Lake or quieter residential streets in Sector 3 ensures proper exercise and socialization.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1767,21 +1789,21 @@
       <c r="F6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J6" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A6 &amp; "" located in "" &amp; B6 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A6 &amp; "" Care Guide and Maintenance Costs in "" &amp; B6 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B6 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Jayanagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in Jayanagar requires a consistent health and wellness routine adapted to South Bengaluru's residential environment. To support optimal growth "&amp;"and long-term vitality, provide high-quality toy-breed nutrition, implement strict daily dental hygiene to prevent early periodontal issues, and ensure gentle daily exercise with controlled walks around Madhavan Park or peaceful residential avenues near 4"&amp;"th Block. Navigating local urban conditions means safeguarding your small pet against seasonal humidity, mosquito exposure, and pavement heat during peak hours, making regular tick control, hydration, and gentle coats for cooler evenings essential. Annual"&amp;" maintenance costs in Jayanagar typically average between ₹15,000 and ₹35,000, which encompasses premium puppy food, routine veterinary consultations, mandatory vaccinations, periodic deworming, and professional grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A6 &amp; "" located in "" &amp; B6 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A6 &amp; "" Care Guide and Maintenance Costs in "" &amp; B6 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B6 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Jayanagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in Jayanagar requires a consistent health and wellness routine adapted to South Bengaluru's residential environment. To support optimal growth "&amp;"and long-term vitality, provide high-quality toy-breed nutrition, implement strict daily dental hygiene to prevent early periodontal issues, and ensure gentle daily exercise with controlled walks around Madhavan Park or peaceful residential avenues near 4"&amp;"th Block. Navigating local urban conditions means safeguarding your small pet against seasonal humidity, mosquito exposure, and pavement heat during peak hours, making regular tick control, hydration, and gentle coats for cooler evenings essential. Annual"&amp;" maintenance costs in Jayanagar typically average between ₹15,000 and ₹35,000, which encompasses premium puppy food, routine veterinary consultations, mandatory vaccinations, periodic deworming, and professional grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Jayanagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in Jayanagar requires a consistent health and wellness routine adapted to South Bengaluru's residential environment. To support optimal growth and long-term vitality, provide high-quality toy-breed nutrition, implement strict daily dental hygiene to prevent early periodontal issues, and ensure gentle daily exercise with controlled walks around Madhavan Park or peaceful residential avenues near 4th Block. Navigating local urban conditions means safeguarding your small pet against seasonal humidity, mosquito exposure, and pavement heat during peak hours, making regular tick control, hydration, and gentle coats for cooler evenings essential. Annual maintenance costs in Jayanagar typically average between ₹15,000 and ₹35,000, which encompasses premium puppy food, routine veterinary consultations, mandatory vaccinations, periodic deworming, and professional grooming services.</v>
       </c>
       <c r="K6" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A6 &amp; "" in "" &amp; B6 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A6 &amp; "" in "" &amp; B6 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelines"&amp;", area-specific animal welfare laws, nearby vet care).
@@ -1791,11 +1813,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Jayanagar, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal BBMP pet licensing laws apply to Chihuahua owners in Jayanagar?&lt;/h3&gt;&lt;p&gt;Residents around 4th Block Shopping Complex and South End Circle must register their dogs annually with the BBMP, ensure valid rabies immunizations, and implant a microchip. Before purchasing a pup, consider exploring ethical sourcing or connecting with &lt;a href="https://www.peopleforanimalsindia.org"&gt;local adoption guidelines&lt;/a&gt; to find shelter animals in need.&lt;/p&gt;&lt;h3&gt;Where can I find veterinary facilities for toy breeds around Jayanagar?&lt;/h3&gt;&lt;p&gt;Experienced pet clinics located near Madhavan Park and Kanakapura Road provide specialized pediatric care, dental checkups, and vaccinations for small breeds. If you encounter suspected unlicensed breeding or animal abuse, report it to &lt;a href="https://www.petaindia.com"&gt;cruelty reporting networks&lt;/a&gt; for swift action.&lt;/p&gt;&lt;h3&gt;How do I care for a young Chihuahua in South Bengaluru's environment?&lt;/h3&gt;&lt;p&gt;Ensure your puppy stays hydrated during warm afternoons, avoids hot pavement near high-traffic avenues, and receives routine indoor exercise paired with brief walks in quiet residential lanes across Jayanagar.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1810,21 +1832,21 @@
       <c r="F7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>57</v>
       </c>
       <c r="J7" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A7 &amp; "" located in "" &amp; B7 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A7 &amp; "" Care Guide and Maintenance Costs in "" &amp; B7 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B7 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in JP Nagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in JP Nagar requires a tailored wellness routine suited to South Bangalore's active residential environment. To ensure long-term health, focus o"&amp;"n high-protein nutrition specifically formulated for toy breeds, daily indoor play, and gentle evening strolls near Puttenahalli Lake or quiet residential avenues in Phases 1 through 9. Navigating apartment living near busy transit corridors like the 100 "&amp;"Feet Ring Road highlights the importance of consistent climate control, protective care during hot weather, strict dental hygiene, and regular tick prevention. On average, annual maintenance costs in JP Nagar range between ₹15,000 and ₹35,000, which cover"&amp;"s premium nutritional diets, routine veterinary checkups, core vaccinations, deworming schedules, and periodic grooming treatments.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A7 &amp; "" located in "" &amp; B7 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A7 &amp; "" Care Guide and Maintenance Costs in "" &amp; B7 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B7 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in JP Nagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in JP Nagar requires a tailored wellness routine suited to South Bangalore's active residential environment. To ensure long-term health, focus o"&amp;"n high-protein nutrition specifically formulated for toy breeds, daily indoor play, and gentle evening strolls near Puttenahalli Lake or quiet residential avenues in Phases 1 through 9. Navigating apartment living near busy transit corridors like the 100 "&amp;"Feet Ring Road highlights the importance of consistent climate control, protective care during hot weather, strict dental hygiene, and regular tick prevention. On average, annual maintenance costs in JP Nagar range between ₹15,000 and ₹35,000, which cover"&amp;"s premium nutritional diets, routine veterinary checkups, core vaccinations, deworming schedules, and periodic grooming treatments.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in JP Nagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in JP Nagar requires a tailored wellness routine suited to South Bangalore's active residential environment. To ensure long-term health, focus on high-protein nutrition specifically formulated for toy breeds, daily indoor play, and gentle evening strolls near Puttenahalli Lake or quiet residential avenues in Phases 1 through 9. Navigating apartment living near busy transit corridors like the 100 Feet Ring Road highlights the importance of consistent climate control, protective care during hot weather, strict dental hygiene, and regular tick prevention. On average, annual maintenance costs in JP Nagar range between ₹15,000 and ₹35,000, which covers premium nutritional diets, routine veterinary checkups, core vaccinations, deworming schedules, and periodic grooming treatments.</v>
       </c>
       <c r="K7" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A7 &amp; "" in "" &amp; B7 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A7 &amp; "" in "" &amp; B7 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelines"&amp;", area-specific animal welfare laws, nearby vet care).
@@ -1834,11 +1856,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in JP Nagar, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What local municipal regulations apply to owning a Chihuahua in JP Nagar?&lt;/h3&gt;&lt;p&gt;Pet owners along 100 Feet Ring Road and near Puttenahalli Lake must adhere to BBMP guidelines, including microchipping, rabies vaccinations, and obtaining an official pet license. Consider reviewing &lt;a href="https://www.peopleforanimalsindia.org"&gt;local animal shelter adoption programs&lt;/a&gt; before deciding to buy a pup.&lt;/p&gt;&lt;h3&gt;Where can I find specialized vet care for small breeds near JP Nagar?&lt;/h3&gt;&lt;p&gt;Veterinary clinics near 100 Feet Ring Road and the Green Line Metro Station offer complete health checks and dental care tailored for toy breeds. If you witness unethical breeding practices or pet abuse in South Bangalore, report it through &lt;a href="https://www.petaindia.com"&gt;animal rights protection channels&lt;/a&gt;.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for high-rise apartment living in JP Nagar Phases 1 to 9?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in compact apartment environments across JP Nagar. Gentle evening walks around quiet residential avenues and regular indoor play easily fulfill their daily activity requirements.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1853,21 +1875,21 @@
       <c r="F8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>63</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J8" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A8 &amp; "" located in "" &amp; B8 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A8 &amp; "" Care Guide and Maintenance Costs in "" &amp; B8 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B8 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Malleshwaram, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in Malleshwaram's historic residential avenues requires an attentive wellness routine adapted to classic urban living. To ensure optimal he"&amp;"alth, provide nutrient-dense food tailored for toy breeds, daily indoor activity alongside gentle walks around Sankey Tank or Margosa Road, and routine dental hygiene to prevent early tooth loss. Navigating busy neighborhood streets near 8th Cross exposes"&amp;" small puppies to urban dust, heat variations, and loud crowds, emphasizing the need for proper hydration, tick prophylaxis, and routine grooming. On average, annual maintenance costs in Malleshwaram range between ₹15,000 and ₹35,000, covering quality pup"&amp;"py food, routine veterinary consultations, core vaccinations, deworming, and periodic grooming treatments.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A8 &amp; "" located in "" &amp; B8 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A8 &amp; "" Care Guide and Maintenance Costs in "" &amp; B8 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B8 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Malleshwaram, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in Malleshwaram's historic residential avenues requires an attentive wellness routine adapted to classic urban living. To ensure optimal he"&amp;"alth, provide nutrient-dense food tailored for toy breeds, daily indoor activity alongside gentle walks around Sankey Tank or Margosa Road, and routine dental hygiene to prevent early tooth loss. Navigating busy neighborhood streets near 8th Cross exposes"&amp;" small puppies to urban dust, heat variations, and loud crowds, emphasizing the need for proper hydration, tick prophylaxis, and routine grooming. On average, annual maintenance costs in Malleshwaram range between ₹15,000 and ₹35,000, covering quality pup"&amp;"py food, routine veterinary consultations, core vaccinations, deworming, and periodic grooming treatments.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Malleshwaram, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in Malleshwaram's historic residential avenues requires an attentive wellness routine adapted to classic urban living. To ensure optimal health, provide nutrient-dense food tailored for toy breeds, daily indoor activity alongside gentle walks around Sankey Tank or Margosa Road, and routine dental hygiene to prevent early tooth loss. Navigating busy neighborhood streets near 8th Cross exposes small puppies to urban dust, heat variations, and loud crowds, emphasizing the need for proper hydration, tick prophylaxis, and routine grooming. On average, annual maintenance costs in Malleshwaram range between ₹15,000 and ₹35,000, covering quality puppy food, routine veterinary consultations, core vaccinations, deworming, and periodic grooming treatments.</v>
       </c>
       <c r="K8" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A8 &amp; "" in "" &amp; B8 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A8 &amp; "" in "" &amp; B8 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelines"&amp;", area-specific animal welfare laws, nearby vet care).
@@ -1877,11 +1899,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Malleshwaram, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal rules and BBMP licensing apply to Chihuahua owners in Malleshwaram?&lt;/h3&gt;&lt;p&gt;Pet owners along Sampige Road and Margosa Road must register their dogs for a BBMP pet license, maintain microchip records, and ensure timely rabies vaccinations. Before buying, review ethical sourcing practices or connect with &lt;a href="https://www.peopleforanimalsindia.org"&gt;animal welfare organizations&lt;/a&gt; to explore local adoption guidelines.&lt;/p&gt;&lt;h3&gt;Where can I find reliable nearby vet care for toy breeds around Sampige Road?&lt;/h3&gt;&lt;p&gt;Veterinary clinics near Mantri Square and 8th Cross Market offer specialized care, dental health checks, and routine vaccinations for small dogs. If you observe unethical breeding practices or cruelty near commercial hubs, reach out to &lt;a href="https://www.petaindia.com"&gt;cruelty reporting networks&lt;/a&gt; to submit a report.&lt;/p&gt;&lt;h3&gt;How well do Chihuahua puppies adapt to home living in historic Malleshwaram?&lt;/h3&gt;&lt;p&gt;Chihuahuas adapt exceptionally well to classic North Bengaluru apartments due to their modest space requirements. Regular indoor activities paired with short morning walks near Sankey Tank provide ideal physical and mental stimulation.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1896,23 +1918,23 @@
       <c r="F9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A9 &amp; "" located in "" &amp; B9 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A9 &amp; "" Care Guide and Maintenance Costs in "" &amp; B9 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B9 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Whitefield, Bangalore&lt;/h2&gt;
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A9 &amp; "" located in "" &amp; B9 &amp; "". Start the output directly with an HTML h2 heading containing the vehicl"&amp;"e/service name and location (e.g., &lt;h2&gt;"" &amp; A9 &amp; "" Care Guide and Maintenance Costs in "" &amp; B9 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-tear "&amp;"factors specific to "" &amp; B9 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Whitefield, Bangalore&lt;/h2&gt;
 Caring for a Chihuahua puppy in East Bengaluru's IT corridor of Whitefield requires a dedicated routine adapted to modern high-rise apartment living. To foster optimal de"&amp;"velopment, provide high-quality toy-breed nutrition, routine dental care, and managed indoor exercise supplemented with short walks near ITPL Main Road or Borewell Road during cooler hours. Navigating suburban construction dust, seasonal humidity, and hig"&amp;"h-density residential surroundings requires consistent tick and flea treatments, air filtration indoors, and regular coat grooming. On average, annual maintenance costs in Whitefield range from ₹18,000 to ₹40,000, covering premium puppy food, routine vete"&amp;"rinary health assessments, vaccinations, deworming, and professional grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Whitefield, Bangalore&lt;/h2&gt;
 Caring for a Chihuahua puppy in East Bengaluru's IT corridor of Whitefield requires a dedicated routine adapted to modern high-rise apartment living. To foster optimal development, provide high-quality toy-breed nutrition, routine dental care, and managed indoor exercise supplemented with short walks near ITPL Main Road or Borewell Road during cooler hours. Navigating suburban construction dust, seasonal humidity, and high-density residential surroundings requires consistent tick and flea treatments, air filtration indoors, and regular coat grooming. On average, annual maintenance costs in Whitefield range from ₹18,000 to ₹40,000, covering premium puppy food, routine veterinary health assessments, vaccinations, deworming, and professional grooming services.</v>
       </c>
       <c r="K9" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A9 &amp; "" in "" &amp; B9 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A9 &amp; "" in "" &amp; B9 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelines"&amp;", area-specific animal welfare laws, nearby vet care).
@@ -1922,11 +1944,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Whitefield, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal rules apply to buying a Chihuahua puppy in Whitefield?&lt;/h3&gt;&lt;p&gt;Pet owners in the ITPL and Hope Farm Junction areas must comply with BBMP pet licensing rules by obtaining annual permits, maintaining updated rabies vaccination records, and adhering to local adoption guidelines. Consider checking ethical &lt;a href="https://www.peopleforanimalsindia.org"&gt;animal rescue organization listings&lt;/a&gt; before finalizing any purchase.&lt;/p&gt;&lt;h3&gt;Where can I locate specialized veterinary care for toy breeds around ITPL Main Road?&lt;/h3&gt;&lt;p&gt;High-standard veterinary facilities along Borewell Road and the Purple Line metro corridor offer pediatric health screenings, dental management, and vaccination schedules. If you encounter illegal puppy breeding or unethical treatment, notify &lt;a href="https://www.petaindia.com"&gt;cruelty prevention groups&lt;/a&gt; immediately.&lt;/p&gt;&lt;h3&gt;How do Chihuahua puppies adjust to high-rise apartment living in Whitefield's tech corridor?&lt;/h3&gt;&lt;p&gt;Chihuahuas thrive in high-rise apartments due to their tiny size. Providing indoor play zones and short walks near quieter residential pockets protects them from local dust and traffic while fulfilling their daily exercise requirements.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1941,21 +1963,21 @@
       <c r="F10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>79</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>81</v>
       </c>
       <c r="J10" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A10 &amp; "" located in "" &amp; B10 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A10 &amp; "" Care Guide and Maintenance Costs in "" &amp; B10 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B10 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Marathahalli, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in East Bengaluru's tech hub of Marathahalli requires a structured wellness routine tailored to busy urban surroundings. To maintain optima"&amp;"l health, provide nutrient-rich food formulated specifically for small breeds, daily indoor play alongside controlled outdoor walks near quieter streets off Varthur Road, and vigilant oral hygiene to guard against early dental issues. Navigating busy zone"&amp;"s around Outer Ring Road and Marathahalli Bridge exposes young pups to environmental dust, traffic noise, and warm weather, making consistent climate control, coat brushing, and tick prevention essential. On average, annual maintenance costs in Marathahal"&amp;"li range between ₹15,000 and ₹35,000, covering premium puppy food, routine veterinary health checks, core vaccinations, regular deworming, and periodic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A10 &amp; "" located in "" &amp; B10 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A10 &amp; "" Care Guide and Maintenance Costs in "" &amp; B10 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B10 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Marathahalli, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in East Bengaluru's tech hub of Marathahalli requires a structured wellness routine tailored to busy urban surroundings. To maintain optima"&amp;"l health, provide nutrient-rich food formulated specifically for small breeds, daily indoor play alongside controlled outdoor walks near quieter streets off Varthur Road, and vigilant oral hygiene to guard against early dental issues. Navigating busy zone"&amp;"s around Outer Ring Road and Marathahalli Bridge exposes young pups to environmental dust, traffic noise, and warm weather, making consistent climate control, coat brushing, and tick prevention essential. On average, annual maintenance costs in Marathahal"&amp;"li range between ₹15,000 and ₹35,000, covering premium puppy food, routine veterinary health checks, core vaccinations, regular deworming, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Marathahalli, Bangalore&lt;/h2&gt; Caring for a Chihuahua puppy in East Bengaluru's tech hub of Marathahalli requires a structured wellness routine tailored to busy urban surroundings. To maintain optimal health, provide nutrient-rich food formulated specifically for small breeds, daily indoor play alongside controlled outdoor walks near quieter streets off Varthur Road, and vigilant oral hygiene to guard against early dental issues. Navigating busy zones around Outer Ring Road and Marathahalli Bridge exposes young pups to environmental dust, traffic noise, and warm weather, making consistent climate control, coat brushing, and tick prevention essential. On average, annual maintenance costs in Marathahalli range between ₹15,000 and ₹35,000, covering premium puppy food, routine veterinary health checks, core vaccinations, regular deworming, and periodic professional grooming.</v>
       </c>
       <c r="K10" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A10 &amp; "" in "" &amp; B10 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A10 &amp; "" in "" &amp; B10 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -1965,11 +1987,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Marathahalli, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What are the BBMP pet registration rules for Chihuahua owners in Marathahalli?&lt;/h3&gt;&lt;p&gt;Residents near Outer Ring Road and Prestige Tech Park bringing home a Chihuahua puppy must secure an annual BBMP pet license, ensure complete microchipping, and keep rabies immunizations current. Prior to purchasing, check local pet care guidelines or reach out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue and adoption centers&lt;/a&gt; to consider ethical alternatives.&lt;/p&gt;&lt;h3&gt;How do I report illegal dog breeding or pet abuse around Marathahalli?&lt;/h3&gt;&lt;p&gt;If you encounter uncertified breeders or inhumane conditions near Varthur Road or Marathahalli Bridge, report the issue to local municipal authorities and &lt;a href="https://www.petaindia.com"&gt;cruelty prevention organizations&lt;/a&gt; to ensure animal protection laws are upheld.&lt;/p&gt;&lt;h3&gt;Where can I find veterinary care for toy breeds in the Marathahalli tech corridor?&lt;/h3&gt;&lt;p&gt;Multiple veterinary clinics near Kalamandir and along the Outer Ring Road specialize in small breed care, offering vaccinations, dental checkups, and routine wellness exams tailored for toy Chihuahuas.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1984,21 +2006,21 @@
       <c r="F11" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J11" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A11 &amp; "" located in "" &amp; B11 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A11 &amp; "" Care Guide and Maintenance Costs in "" &amp; B11 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B11 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Banashankari, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in South Bengaluru's Banashankari neighborhood requires a structured health routine tailored to local urban living. To maintain optimal vita"&amp;"lity, ensure a nutrition-rich diet designed for small breeds, routine oral hygiene to avoid early dental issues, and controlled indoor play complemented by short, peaceful walks around quiet spots near Banashankari 3rd Stage or the BDA Complex. Navigating"&amp;" the warmer microclimate and busy residential zones of South Bengaluru means protecting your puppy against humidity-induced skin allergies, tick infestations, and stress from ambient traffic noise along the Outer Ring Road. On average, annual maintenance "&amp;"and care costs in Banashankari range from ₹15,000 to ₹35,000, which includes premium toy-breed food, preventive vaccinations, deworming schedules, periodic veterinary checkups, and routine grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A11 &amp; "" located in "" &amp; B11 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A11 &amp; "" Care Guide and Maintenance Costs in "" &amp; B11 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B11 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Banashankari, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in South Bengaluru's Banashankari neighborhood requires a structured health routine tailored to local urban living. To maintain optimal vita"&amp;"lity, ensure a nutrition-rich diet designed for small breeds, routine oral hygiene to avoid early dental issues, and controlled indoor play complemented by short, peaceful walks around quiet spots near Banashankari 3rd Stage or the BDA Complex. Navigating"&amp;" the warmer microclimate and busy residential zones of South Bengaluru means protecting your puppy against humidity-induced skin allergies, tick infestations, and stress from ambient traffic noise along the Outer Ring Road. On average, annual maintenance "&amp;"and care costs in Banashankari range from ₹15,000 to ₹35,000, which includes premium toy-breed food, preventive vaccinations, deworming schedules, periodic veterinary checkups, and routine grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Banashankari, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in South Bengaluru's Banashankari neighborhood requires a structured health routine tailored to local urban living. To maintain optimal vitality, ensure a nutrition-rich diet designed for small breeds, routine oral hygiene to avoid early dental issues, and controlled indoor play complemented by short, peaceful walks around quiet spots near Banashankari 3rd Stage or the BDA Complex. Navigating the warmer microclimate and busy residential zones of South Bengaluru means protecting your puppy against humidity-induced skin allergies, tick infestations, and stress from ambient traffic noise along the Outer Ring Road. On average, annual maintenance and care costs in Banashankari range from ₹15,000 to ₹35,000, which includes premium toy-breed food, preventive vaccinations, deworming schedules, periodic veterinary checkups, and routine grooming services.</v>
       </c>
       <c r="K11" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A11 &amp; "" in "" &amp; B11 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A11 &amp; "" in "" &amp; B11 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2008,11 +2030,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Banashankari, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal guidelines govern buying or adopting a Chihuahua puppy in Banashankari?&lt;/h3&gt;&lt;p&gt;Residents around Banashankari 3rd Stage and Kamakya Theatre must obtain a valid BBMP pet license, register their puppy's microchip, and keep core vaccinations current. Before buying, consider reviewing ethical breeding standards or reaching out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; for adoption options.&lt;/p&gt;&lt;h3&gt;How can I locate reliable veterinary care for toy breeds in Banashankari?&lt;/h3&gt;&lt;p&gt;Veterinary facilities near the BDA Complex and Banashankari TTMC offer specialized care for toy breeds, including dental checkups and preventive health plans. If you suspect unethical breeding practices or animal mistreatment near Outer Ring Road, report it through &lt;a href="https://www.petaindia.com"&gt;cruelty prevention channels&lt;/a&gt;.&lt;/p&gt;&lt;h3&gt;Are Chihuahuas suitable for apartment living in South Bengaluru?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in apartment environments due to their small size. Regular indoor playtime combined with brief, controlled walks around quiet neighborhood streets near Banashankari 3rd Stage ensures they stay physically active and happy.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -2027,21 +2049,21 @@
       <c r="F12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="2" t="s">
         <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="2" t="s">
         <v>97</v>
       </c>
       <c r="J12" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A12 &amp; "" located in "" &amp; B12 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A12 &amp; "" Care Guide and Maintenance Costs in "" &amp; B12 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B12 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in BTM Layout, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in BTM Layout requires a structured wellness routine tailored for high-density urban environments. To ensure long-term vitality, prioritize hi"&amp;"gh-protein nutrition formulated for toy breeds, daily indoor play alongside controlled short walks around BTM Lake or 2nd Stage, and rigorous dental hygiene to prevent early periodontal issues. Navigating active commercial corridors along Tavarekere Main "&amp;"Road and Silk Board Junction exposes small dogs to street dust, traffic noise, and heat, making reliable hydration, tick prevention, and regular coat grooming essential. On average, annual maintenance costs in BTM Layout range between ₹15,000 and ₹35,000,"&amp;" covering quality puppy food, routine veterinary visits, core vaccinations, deworming, and periodic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A12 &amp; "" located in "" &amp; B12 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A12 &amp; "" Care Guide and Maintenance Costs in "" &amp; B12 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B12 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in BTM Layout, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in BTM Layout requires a structured wellness routine tailored for high-density urban environments. To ensure long-term vitality, prioritize hi"&amp;"gh-protein nutrition formulated for toy breeds, daily indoor play alongside controlled short walks around BTM Lake or 2nd Stage, and rigorous dental hygiene to prevent early periodontal issues. Navigating active commercial corridors along Tavarekere Main "&amp;"Road and Silk Board Junction exposes small dogs to street dust, traffic noise, and heat, making reliable hydration, tick prevention, and regular coat grooming essential. On average, annual maintenance costs in BTM Layout range between ₹15,000 and ₹35,000,"&amp;" covering quality puppy food, routine veterinary visits, core vaccinations, deworming, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in BTM Layout, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in BTM Layout requires a structured wellness routine tailored for high-density urban environments. To ensure long-term vitality, prioritize high-protein nutrition formulated for toy breeds, daily indoor play alongside controlled short walks around BTM Lake or 2nd Stage, and rigorous dental hygiene to prevent early periodontal issues. Navigating active commercial corridors along Tavarekere Main Road and Silk Board Junction exposes small dogs to street dust, traffic noise, and heat, making reliable hydration, tick prevention, and regular coat grooming essential. On average, annual maintenance costs in BTM Layout range between ₹15,000 and ₹35,000, covering quality puppy food, routine veterinary visits, core vaccinations, deworming, and periodic professional grooming.</v>
       </c>
       <c r="K12" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A12 &amp; "" in "" &amp; B12 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A12 &amp; "" in "" &amp; B12 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2051,11 +2073,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in BTM Layout, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal BBMP pet licensing requirements exist for Chihuahuas in BTM Layout?&lt;/h3&gt;&lt;p&gt;Pet owners near 2nd Stage, Tavarekere Main Road, and Vega City Mall must obtain an annual BBMP pet license, maintain updated rabies vaccination records, and register microchip details. Before purchasing, verify responsible breeding practices or consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; to consider ethical adoption options.&lt;/p&gt;&lt;h3&gt;Where can I find veterinary clinics and healthcare support for toy breeds in BTM Layout?&lt;/h3&gt;&lt;p&gt;Veterinary centers located near Central Silk Board and Udupi Garden Circle provide routine checkups, vaccinations, and dental care tailored for toy breeds. If you witness suspected illegal breeding or mistreatment around commercial areas, contact &lt;a href="https://www.petaindia.com"&gt;animal cruelty prevention groups&lt;/a&gt; to submit an official report.&lt;/p&gt;&lt;h3&gt;How do Chihuahua puppies adapt to apartment living near high-traffic areas in South Bangalore?&lt;/h3&gt;&lt;p&gt;Chihuahuas thrive in compact apartments due to their small size and modest space needs. To manage stress from heavy traffic noise along Outer Ring Road, provide routine indoor play combined with short, controlled walks around quieter residential lanes near BTM Lake.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -2070,21 +2092,21 @@
       <c r="F13" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="2" t="s">
         <v>105</v>
       </c>
       <c r="J13" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A13 &amp; "" located in "" &amp; B13 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A13 &amp; "" Care Guide and Maintenance Costs in "" &amp; B13 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B13 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in RT Nagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in North Bengaluru's RT Nagar requires a structured care routine tailored for urban residential living near busy transit corridors like Bellary "&amp;"Road and Dinnur Market. To ensure optimal health, prioritize nutrient-dense food formulated specifically for toy breeds, daily indoor play alongside controlled short walks along quieter residential lanes, and strict oral hygiene to prevent early dental is"&amp;"sues. Navigating active commercial hubs exposes small puppies to urban dust, heat variations, and traffic noise, making consistent climate control, tick prevention, and regular grooming essential. On average, annual maintenance costs in RT Nagar range bet"&amp;"ween ₹15,000 and ₹35,000, covering high-quality puppy food, routine veterinary visits, core vaccinations, timely deworming, and periodic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A13 &amp; "" located in "" &amp; B13 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A13 &amp; "" Care Guide and Maintenance Costs in "" &amp; B13 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B13 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in RT Nagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in North Bengaluru's RT Nagar requires a structured care routine tailored for urban residential living near busy transit corridors like Bellary "&amp;"Road and Dinnur Market. To ensure optimal health, prioritize nutrient-dense food formulated specifically for toy breeds, daily indoor play alongside controlled short walks along quieter residential lanes, and strict oral hygiene to prevent early dental is"&amp;"sues. Navigating active commercial hubs exposes small puppies to urban dust, heat variations, and traffic noise, making consistent climate control, tick prevention, and regular grooming essential. On average, annual maintenance costs in RT Nagar range bet"&amp;"ween ₹15,000 and ₹35,000, covering high-quality puppy food, routine veterinary visits, core vaccinations, timely deworming, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in RT Nagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in North Bengaluru's RT Nagar requires a structured care routine tailored for urban residential living near busy transit corridors like Bellary Road and Dinnur Market. To ensure optimal health, prioritize nutrient-dense food formulated specifically for toy breeds, daily indoor play alongside controlled short walks along quieter residential lanes, and strict oral hygiene to prevent early dental issues. Navigating active commercial hubs exposes small puppies to urban dust, heat variations, and traffic noise, making consistent climate control, tick prevention, and regular grooming essential. On average, annual maintenance costs in RT Nagar range between ₹15,000 and ₹35,000, covering high-quality puppy food, routine veterinary visits, core vaccinations, timely deworming, and periodic professional grooming.</v>
       </c>
       <c r="K13" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A13 &amp; "" in "" &amp; B13 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A13 &amp; "" in "" &amp; B13 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2094,11 +2116,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in RT Nagar, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal rules apply to Chihuahua puppy owners in RT Nagar?&lt;/h3&gt;&lt;p&gt;Pet parents around RT Nagar Main Road and Dinnur Market must adhere to BBMP licensing regulations, which mandate mandatory microchipping and yearly rabies vaccinations. Before purchasing a pup, consider checking local adoption guidelines or supporting &lt;a href="https://www.peopleforanimalsindia.org"&gt;animal welfare organisations&lt;/a&gt; for rescue options in North Bangalore.&lt;/p&gt;&lt;h3&gt;Where can I find reliable vet care and address animal welfare issues near RT Nagar?&lt;/h3&gt;&lt;p&gt;Veterinary facilities near Bellary Road and Hebbal offer routine immunizations, wellness checks, and specialized care for toy breeds. If you witness unethical breeding practices or animal mistreatment near Dinnur Market, reach out to &lt;a href="https://www.petaindia.com"&gt;animal rights protection groups&lt;/a&gt; to report violations immediately.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for residential living near busy RT Nagar corridors?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in apartment environments due to their compact size. Providing regular indoor play and brief morning walks along quieter residential lanes off RT Nagar Main Road helps protect them from heavy traffic noise and pollution while meeting their exercise needs.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2113,21 +2135,21 @@
       <c r="F14" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="2" t="s">
         <v>113</v>
       </c>
       <c r="J14" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A14 &amp; "" located in "" &amp; B14 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A14 &amp; "" Care Guide and Maintenance Costs in "" &amp; B14 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B14 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kammanahalli, Bangalore&lt;/h2&gt;Raising a Chihuahua puppy in the lively residential hub of Kammanahalli requires a proactive care strategy adapted to bustling urban living. To maintain optimal vitality"&amp;", provide nutrient-dense food tailored for toy breeds, schedule controlled exercise sessions around quieter spots near HRBR Layout, and maintain strict oral hygiene to avoid early dental issues. Navigating local neighborhoods exposes small pets to ambient"&amp;" dust, traffic noise, and seasonal humidity, making routine tick prevention, coat grooming, and a calm indoor rest area indispensable. Annual maintenance costs in Kammanahalli typically range between ₹15,000 and ₹35,000, covering high-quality puppy diet, "&amp;"routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A14 &amp; "" located in "" &amp; B14 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A14 &amp; "" Care Guide and Maintenance Costs in "" &amp; B14 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B14 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kammanahalli, Bangalore&lt;/h2&gt;Raising a Chihuahua puppy in the lively residential hub of Kammanahalli requires a proactive care strategy adapted to bustling urban living. To maintain optimal vitality"&amp;", provide nutrient-dense food tailored for toy breeds, schedule controlled exercise sessions around quieter spots near HRBR Layout, and maintain strict oral hygiene to avoid early dental issues. Navigating local neighborhoods exposes small pets to ambient"&amp;" dust, traffic noise, and seasonal humidity, making routine tick prevention, coat grooming, and a calm indoor rest area indispensable. Annual maintenance costs in Kammanahalli typically range between ₹15,000 and ₹35,000, covering high-quality puppy diet, "&amp;"routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kammanahalli, Bangalore&lt;/h2&gt;Raising a Chihuahua puppy in the lively residential hub of Kammanahalli requires a proactive care strategy adapted to bustling urban living. To maintain optimal vitality, provide nutrient-dense food tailored for toy breeds, schedule controlled exercise sessions around quieter spots near HRBR Layout, and maintain strict oral hygiene to avoid early dental issues. Navigating local neighborhoods exposes small pets to ambient dust, traffic noise, and seasonal humidity, making routine tick prevention, coat grooming, and a calm indoor rest area indispensable. Annual maintenance costs in Kammanahalli typically range between ₹15,000 and ₹35,000, covering high-quality puppy diet, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming services.</v>
       </c>
       <c r="K14" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A14 &amp; "" in "" &amp; B14 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A14 &amp; "" in "" &amp; B14 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2137,11 +2159,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Kammanahalli, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What BBMP registration and pet ownership rules apply in Kammanahalli?&lt;/h3&gt;&lt;p&gt;Residents around Kammanahalli Main Road and HRBR Layout must secure an annual BBMP pet license, maintain microchipping records, and stay up to date with core vaccinations. Before purchasing a pup, consider checking local adoption guidelines or visiting &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue dog shelters in Bangalore&lt;/a&gt; to support ethical pet practices.&lt;/p&gt;&lt;h3&gt;How can I report improper breeding conditions or animal mistreatment near Kammanahalli?&lt;/h3&gt;&lt;p&gt;If you encounter unauthorized breeding facilities or poor welfare standards near Kullappa Circle or Lingarajapuram, report the infraction to civic authorities or get guidance from &lt;a href="https://www.petaindia.com"&gt;cruelty reporting networks&lt;/a&gt; to ensure compliance with animal welfare laws.&lt;/p&gt;&lt;h3&gt;Where can I locate trusted veterinary services for toy breeds in Kammanahalli?&lt;/h3&gt;&lt;p&gt;Veterinary clinics around 80 Feet Road and HRBR Layout provide complete health management for mini breeds, including dental checkups, vaccinations, and nutrition counseling. Routine wellness visits help prevent breed-specific risks like hypoglycemia and patellar luxation in young puppies.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -2156,21 +2178,21 @@
       <c r="F15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>118</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J15" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A15 &amp; "" located in "" &amp; B15 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A15 &amp; "" Care Guide and Maintenance Costs in "" &amp; B15 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B15 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kalyan Nagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in Kalyan Nagar involves establishing a balanced health and upkeep schedule tailored to modern East Bengaluru living. Prioritize nutrient-ri"&amp;"ch food formulated for mini breeds, daily dental brushing to counteract susceptibility to periodontal issues, and short, controlled walks around quieter residential lanes near HRBR Layout and Hennur Main Road. Navigating urban surroundings around busy ave"&amp;"nues like 80 Feet Road exposes small dogs to road dust, traffic noise, and warm weather, necessitating consistent hydration, tick and flea prevention, and routine coat grooming. Owners in Kalyan Nagar can expect annual care and maintenance costs to averag"&amp;"e between ₹15,000 and ₹35,000, which encompasses premium toy-breed diet supplies, routine pediatric veterinary evaluations, periodic vaccinations, deworming treatments, and basic professional grooming sessions.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A15 &amp; "" located in "" &amp; B15 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A15 &amp; "" Care Guide and Maintenance Costs in "" &amp; B15 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B15 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kalyan Nagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in Kalyan Nagar involves establishing a balanced health and upkeep schedule tailored to modern East Bengaluru living. Prioritize nutrient-ri"&amp;"ch food formulated for mini breeds, daily dental brushing to counteract susceptibility to periodontal issues, and short, controlled walks around quieter residential lanes near HRBR Layout and Hennur Main Road. Navigating urban surroundings around busy ave"&amp;"nues like 80 Feet Road exposes small dogs to road dust, traffic noise, and warm weather, necessitating consistent hydration, tick and flea prevention, and routine coat grooming. Owners in Kalyan Nagar can expect annual care and maintenance costs to averag"&amp;"e between ₹15,000 and ₹35,000, which encompasses premium toy-breed diet supplies, routine pediatric veterinary evaluations, periodic vaccinations, deworming treatments, and basic professional grooming sessions.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kalyan Nagar, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in Kalyan Nagar involves establishing a balanced health and upkeep schedule tailored to modern East Bengaluru living. Prioritize nutrient-rich food formulated for mini breeds, daily dental brushing to counteract susceptibility to periodontal issues, and short, controlled walks around quieter residential lanes near HRBR Layout and Hennur Main Road. Navigating urban surroundings around busy avenues like 80 Feet Road exposes small dogs to road dust, traffic noise, and warm weather, necessitating consistent hydration, tick and flea prevention, and routine coat grooming. Owners in Kalyan Nagar can expect annual care and maintenance costs to average between ₹15,000 and ₹35,000, which encompasses premium toy-breed diet supplies, routine pediatric veterinary evaluations, periodic vaccinations, deworming treatments, and basic professional grooming sessions.</v>
       </c>
       <c r="K15" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A15 &amp; "" in "" &amp; B15 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A15 &amp; "" in "" &amp; B15 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2180,11 +2202,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Kalyan Nagar, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal BBMP regulations apply to owning a Chihuahua puppy in Kalyan Nagar?&lt;/h3&gt;&lt;p&gt;Pet owners along Hennur Main Road and HRBR Layout must register their dogs for a BBMP pet license, maintain annual rabies vaccinations, and ensure microchipping. Before purchasing, check local adoption guidelines or reach out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;animal welfare organizations&lt;/a&gt; for alternative adoption options.&lt;/p&gt;&lt;h3&gt;Where can I find veterinary care and report pet neglect around Kalyan Nagar?&lt;/h3&gt;&lt;p&gt;Veterinary clinics near 80 Feet Road and Banaswadi railway station offer vaccinations, health checks, and pediatric care for toy breeds. If you witness cruelty or illegal breeding practices in East Bengaluru, report them promptly to &lt;a href="https://www.petaindia.com"&gt;animal rights protection groups&lt;/a&gt;.&lt;/p&gt;&lt;h3&gt;How do I care for a Chihuahua puppy in Kalyan Nagar's urban environment?&lt;/h3&gt;&lt;p&gt;Keep your puppy safe from street dust and traffic near busy avenues by taking short walks along quieter residential lanes off HRBR Layout. Provide fresh water, toy-breed nutrition, and daily indoor playtime to support healthy development in apartment settings.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -2199,21 +2221,21 @@
       <c r="F16" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>126</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="2" t="s">
         <v>128</v>
       </c>
       <c r="J16" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A16 &amp; "" located in "" &amp; B16 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A16 &amp; "" Care Guide and Maintenance Costs in "" &amp; B16 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B16 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Yelahanka, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in northern Bengaluru's Yelahanka precinct requires a structured wellness routine suited to expanding suburban residential environments. To kee"&amp;"p your toy companion healthy near Airport Road and Kogilu, prioritize high-protein nutrition formulated specifically for toy breeds, indoor mental stimulation combined with controlled outdoor walks, and diligent dental care to prevent early periodontal is"&amp;"sues. Navigating local dust, seasonal heat variations, and urban outdoor exposure necessitates regular grooming, routine parasite prevention, and consistent coat care. On average, annual maintenance costs in Yelahanka range between ₹15,000 and ₹35,000, co"&amp;"vering specialized puppy food, routine veterinary checkups, essential vaccinations, deworming, and professional grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A16 &amp; "" located in "" &amp; B16 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A16 &amp; "" Care Guide and Maintenance Costs in "" &amp; B16 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B16 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Yelahanka, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in northern Bengaluru's Yelahanka precinct requires a structured wellness routine suited to expanding suburban residential environments. To kee"&amp;"p your toy companion healthy near Airport Road and Kogilu, prioritize high-protein nutrition formulated specifically for toy breeds, indoor mental stimulation combined with controlled outdoor walks, and diligent dental care to prevent early periodontal is"&amp;"sues. Navigating local dust, seasonal heat variations, and urban outdoor exposure necessitates regular grooming, routine parasite prevention, and consistent coat care. On average, annual maintenance costs in Yelahanka range between ₹15,000 and ₹35,000, co"&amp;"vering specialized puppy food, routine veterinary checkups, essential vaccinations, deworming, and professional grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Yelahanka, Bangalore&lt;/h2&gt;Caring for a Chihuahua puppy in northern Bengaluru's Yelahanka precinct requires a structured wellness routine suited to expanding suburban residential environments. To keep your toy companion healthy near Airport Road and Kogilu, prioritize high-protein nutrition formulated specifically for toy breeds, indoor mental stimulation combined with controlled outdoor walks, and diligent dental care to prevent early periodontal issues. Navigating local dust, seasonal heat variations, and urban outdoor exposure necessitates regular grooming, routine parasite prevention, and consistent coat care. On average, annual maintenance costs in Yelahanka range between ₹15,000 and ₹35,000, covering specialized puppy food, routine veterinary checkups, essential vaccinations, deworming, and professional grooming services.</v>
       </c>
       <c r="K16" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A16 &amp; "" in "" &amp; B16 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A16 &amp; "" in "" &amp; B16 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2223,11 +2245,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies for Sale in Yelahanka, Bangalore - FAQs&lt;/h2&gt;&lt;h3&gt;What BBMP compliance is required when buying a Chihuahua puppy in Yelahanka?&lt;/h3&gt;&lt;p&gt;Pet owners across Yelahanka New Town and Kogilu must secure an annual BBMP pet license, register microchip details, and maintain updated rabies vaccination records under municipal guidelines. Before purchasing, verify responsible breeding standards or consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue networks&lt;/a&gt; for adoption options.&lt;/p&gt;&lt;h3&gt;Where can I find veterinary care for Chihuahua puppies near Yelahanka?&lt;/h3&gt;&lt;p&gt;Established veterinary clinics along the Airport Road (NH 44) belt and Bellary Road provide routine immunizations, pediatric care, and health screenings for toy breeds. If you encounter illegal breeding operations or neglect in northern Bengaluru, contact &lt;a href="https://www.petaindia.com"&gt;animal rights protection groups&lt;/a&gt; to report violations.&lt;/p&gt;&lt;h3&gt;How well do Chihuahua puppies adapt to residential living in Yelahanka Old Town?&lt;/h3&gt;&lt;p&gt;Chihuahuas thrive in suburban homes and apartments throughout Yelahanka thanks to their compact size and low exercise demands. Engaging indoor activity paired with short walks along quiet streets near Yelahanka Lake helps maintain their overall physical health.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -2242,21 +2264,21 @@
       <c r="F17" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="2" t="s">
         <v>134</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="2" t="s">
         <v>136</v>
       </c>
       <c r="J17" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A17 &amp; "" located in "" &amp; B17 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A17 &amp; "" Care Guide and Maintenance Costs in "" &amp; B17 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B17 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Trichy, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Trichy demands a dedicated wellness regimen adapted to the region's warm tropical climate and urban layout around neighborhoods like Thillai N"&amp;"agar and KK Nagar. Prioritize a balanced, high-protein diet designed for small breeds, ensure constant access to fresh water to mitigate heat stress, and plan exercise during cooler early morning or evening hours. Trichy's warm environment requires vigila"&amp;"nt tick and flea prevention, regular dental care to avoid periodontal issues common in toy breeds, and routine grooming. On average, annual care and maintenance costs in Trichy range between ₹12,000 and ₹30,000, which covers premium puppy food, core vacci"&amp;"nations, regular veterinary checkups, deworming, and basic grooming supplies.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A17 &amp; "" located in "" &amp; B17 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A17 &amp; "" Care Guide and Maintenance Costs in "" &amp; B17 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B17 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Trichy, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Trichy demands a dedicated wellness regimen adapted to the region's warm tropical climate and urban layout around neighborhoods like Thillai N"&amp;"agar and KK Nagar. Prioritize a balanced, high-protein diet designed for small breeds, ensure constant access to fresh water to mitigate heat stress, and plan exercise during cooler early morning or evening hours. Trichy's warm environment requires vigila"&amp;"nt tick and flea prevention, regular dental care to avoid periodontal issues common in toy breeds, and routine grooming. On average, annual care and maintenance costs in Trichy range between ₹12,000 and ₹30,000, which covers premium puppy food, core vacci"&amp;"nations, regular veterinary checkups, deworming, and basic grooming supplies.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Trichy, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Trichy demands a dedicated wellness regimen adapted to the region's warm tropical climate and urban layout around neighborhoods like Thillai Nagar and KK Nagar. Prioritize a balanced, high-protein diet designed for small breeds, ensure constant access to fresh water to mitigate heat stress, and plan exercise during cooler early morning or evening hours. Trichy's warm environment requires vigilant tick and flea prevention, regular dental care to avoid periodontal issues common in toy breeds, and routine grooming. On average, annual care and maintenance costs in Trichy range between ₹12,000 and ₹30,000, which covers premium puppy food, core vaccinations, regular veterinary checkups, deworming, and basic grooming supplies.</v>
       </c>
       <c r="K17" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A17 &amp; "" in "" &amp; B17 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A17 &amp; "" in "" &amp; B17 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2266,11 +2288,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Trichy, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal requirements apply when keeping a Chihuahua puppy in Trichy?&lt;/h3&gt;&lt;p&gt;Dog owners in residential areas like Thillai Nagar and KK Nagar should register their pets with the Tiruchirappalli City Municipal Corporation and maintain updated rabies vaccination records. Prior to purchasing, check local adoption guidelines or reach out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;animal welfare organizations in Tamil Nadu&lt;/a&gt; to consider rescue options.&lt;/p&gt;&lt;h3&gt;How can I find qualified veterinary care for a toy puppy near Woraiyur?&lt;/h3&gt;&lt;p&gt;Trusted veterinary clinics operating near Central Bus Stand and Pudukottai Road handle vaccinations, health screenings, and heat stress care for small breeds. If you come across unlicensed breeding kennels or suspect mistreatment, report it through &lt;a href="https://www.petaindia.com"&gt;cruelty reporting networks&lt;/a&gt; to ensure local animal protection laws are enforced.&lt;/p&gt;&lt;h3&gt;How do Chihuahua puppies manage Trichy's warm climate?&lt;/h3&gt;&lt;p&gt;Chihuahuas adapt well to indoor apartment living across Trichy, provided they stay in cool environments with constant access to fresh water. Plan short outdoor walks around Thillai Nagar during early mornings or late evenings to avoid peak daytime heat.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -2285,21 +2307,21 @@
       <c r="F18" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="2" t="s">
         <v>141</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J18" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A18 &amp; "" located in "" &amp; B18 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A18 &amp; "" Care Guide and Maintenance Costs in "" &amp; B18 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B18 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Salem, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Salem, Tamil Nadu requires a tailored wellness routine to handle the region's warm climate near prominent areas like Five Roads, Fairlands, and"&amp;" Hasthampatti. To maintain optimal health, provide high-protein nutrition formulated for toy breeds, ensure constant access to fresh water to mitigate heat stress during warmer months, and maintain strict dental hygiene to prevent early periodontal issues"&amp;". Short, shaded walks along quieter residential streets paired with indoor play keep these energetic pups active while protecting their sensitive paws from hot pavement along busy thoroughfares like NH 544. On average, annual care and maintenance costs in"&amp;" Salem range between ₹15,000 and ₹35,000, covering premium puppy food, routine veterinary health checks, core vaccinations, deworming, and essential grooming supplies.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A18 &amp; "" located in "" &amp; B18 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A18 &amp; "" Care Guide and Maintenance Costs in "" &amp; B18 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B18 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Salem, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Salem, Tamil Nadu requires a tailored wellness routine to handle the region's warm climate near prominent areas like Five Roads, Fairlands, and"&amp;" Hasthampatti. To maintain optimal health, provide high-protein nutrition formulated for toy breeds, ensure constant access to fresh water to mitigate heat stress during warmer months, and maintain strict dental hygiene to prevent early periodontal issues"&amp;". Short, shaded walks along quieter residential streets paired with indoor play keep these energetic pups active while protecting their sensitive paws from hot pavement along busy thoroughfares like NH 544. On average, annual care and maintenance costs in"&amp;" Salem range between ₹15,000 and ₹35,000, covering premium puppy food, routine veterinary health checks, core vaccinations, deworming, and essential grooming supplies.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Salem, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Salem, Tamil Nadu requires a tailored wellness routine to handle the region's warm climate near prominent areas like Five Roads, Fairlands, and Hasthampatti. To maintain optimal health, provide high-protein nutrition formulated for toy breeds, ensure constant access to fresh water to mitigate heat stress during warmer months, and maintain strict dental hygiene to prevent early periodontal issues. Short, shaded walks along quieter residential streets paired with indoor play keep these energetic pups active while protecting their sensitive paws from hot pavement along busy thoroughfares like NH 544. On average, annual care and maintenance costs in Salem range between ₹15,000 and ₹35,000, covering premium puppy food, routine veterinary health checks, core vaccinations, deworming, and essential grooming supplies.</v>
       </c>
       <c r="K18" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A18 &amp; "" in "" &amp; B18 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A18 &amp; "" in "" &amp; B18 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2309,11 +2331,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies for Sale in Salem, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What local regulations and health guidelines apply when getting a Chihuahua puppy in Salem?&lt;/h3&gt;&lt;p&gt;Pet owners around Five Roads and Hasthampatti must adhere to Salem City Municipal Corporation rules regarding mandatory anti-rabies vaccinations and licensing. Prospective owners should review ethical breeding practices or support &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; to consider adoption options.&lt;/p&gt;&lt;h3&gt;How do I manage climate care and find veterinary services in Salem for a toy breed?&lt;/h3&gt;&lt;p&gt;Veterinary clinics near Fairlands and Saradha College Main Road offer routine health checks, vaccinations, and dental care tailored for toy breeds sensitive to heat. If you encounter mistreatment or illegal breeding facilities along the NH 544 corridor, reach out to &lt;a href="https://www.petaindia.com"&gt;cruelty reporting channels&lt;/a&gt; to protect animal safety.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies well-suited for residential living in Salem?&lt;/h3&gt;&lt;p&gt;Yes, their compact size makes Chihuahuas ideal for homes in Alagapuram and Swarnapuri. Providing indoor activities alongside brief, shaded morning strolls protects their paws from hot summer pavement while maintaining proper physical fitness.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -2328,21 +2350,21 @@
       <c r="F19" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="2" t="s">
         <v>149</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="2" t="s">
         <v>151</v>
       </c>
       <c r="J19" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A19 &amp; "" located in "" &amp; B19 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A19 &amp; "" Care Guide and Maintenance Costs in "" &amp; B19 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B19 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Erode, Tamil Nadu&lt;/h2&gt;Raising a healthy Chihuahua puppy in Erode requires a tailored wellness routine designed to handle the region's warm climate along the Kaveri corridor. To maintain optimal vit"&amp;"ality, focus on feeding high-quality nutrient-dense kibble suited for toy breeds, ensuring constant hydration, and providing indoor exercise alongside shaded morning walks around residential areas like Thindal and Perundurai Road. Protecting small pups fr"&amp;"om high summer temperatures requires proper ventilation, heat management, and routine tick control. Additionally, maintaining oral hygiene through regular dental brushing is crucial to prevent early periodontal issues common in miniature breeds. On averag"&amp;"e, annual care and maintenance costs for a Chihuahua in Erode range between ₹15,000 and ₹35,000, covering specialized puppy food, routine veterinary checkups, core vaccinations, preventive deworming, and periodic grooming treatments.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A19 &amp; "" located in "" &amp; B19 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A19 &amp; "" Care Guide and Maintenance Costs in "" &amp; B19 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B19 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Erode, Tamil Nadu&lt;/h2&gt;Raising a healthy Chihuahua puppy in Erode requires a tailored wellness routine designed to handle the region's warm climate along the Kaveri corridor. To maintain optimal vit"&amp;"ality, focus on feeding high-quality nutrient-dense kibble suited for toy breeds, ensuring constant hydration, and providing indoor exercise alongside shaded morning walks around residential areas like Thindal and Perundurai Road. Protecting small pups fr"&amp;"om high summer temperatures requires proper ventilation, heat management, and routine tick control. Additionally, maintaining oral hygiene through regular dental brushing is crucial to prevent early periodontal issues common in miniature breeds. On averag"&amp;"e, annual care and maintenance costs for a Chihuahua in Erode range between ₹15,000 and ₹35,000, covering specialized puppy food, routine veterinary checkups, core vaccinations, preventive deworming, and periodic grooming treatments.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Erode, Tamil Nadu&lt;/h2&gt;Raising a healthy Chihuahua puppy in Erode requires a tailored wellness routine designed to handle the region's warm climate along the Kaveri corridor. To maintain optimal vitality, focus on feeding high-quality nutrient-dense kibble suited for toy breeds, ensuring constant hydration, and providing indoor exercise alongside shaded morning walks around residential areas like Thindal and Perundurai Road. Protecting small pups from high summer temperatures requires proper ventilation, heat management, and routine tick control. Additionally, maintaining oral hygiene through regular dental brushing is crucial to prevent early periodontal issues common in miniature breeds. On average, annual care and maintenance costs for a Chihuahua in Erode range between ₹15,000 and ₹35,000, covering specialized puppy food, routine veterinary checkups, core vaccinations, preventive deworming, and periodic grooming treatments.</v>
       </c>
       <c r="K19" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A19 &amp; "" in "" &amp; B19 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A19 &amp; "" in "" &amp; B19 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2352,11 +2374,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies for Sale in Erode, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal guidelines apply when buying a Chihuahua puppy in Erode?&lt;/h3&gt;&lt;p&gt;Pet owners around Perundurai Road and Thindal must adhere to Erode City Municipal Corporation mandates, ensuring timely rabies immunizations and proper shelter. Prior to purchasing, consider reviewing &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; to evaluate ethical adoption possibilities.&lt;/p&gt;&lt;h3&gt;Where can I find reliable vet care and address animal welfare concerns in Erode?&lt;/h3&gt;&lt;p&gt;Veterinary facilities near Brough Road and Surampatti offer specialized care and routine vaccinations for toy breeds. If you witness illegal breeding practices or neglect in the area, report them immediately to &lt;a href="https://www.petaindia.com"&gt;cruelty reporting networks&lt;/a&gt; for swift action.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suited to the local climate in Erode?&lt;/h3&gt;&lt;p&gt;Yes, but their small size requires protection from intense summer heat along the Kaveri corridor. Providing indoor climate control, fresh water, and early morning walks near Thindal ensures your puppy stays healthy and active.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -2371,21 +2393,21 @@
       <c r="F20" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="2" t="s">
         <v>159</v>
       </c>
       <c r="J20" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A20 &amp; "" located in "" &amp; B20 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A20 &amp; "" Care Guide and Maintenance Costs in "" &amp; B20 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B20 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Madurai, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Madurai's warm, tropical climate requires a well-planned health and care routine tailored to local conditions. Due to high temperatures in re"&amp;"gions near KK Nagar and Anna Nagar, keeping your toy breed well-hydrated and housed in well-ventilated, air-conditioned spaces is crucial to prevent heat stress and hypoglycemia. Focus on high-protein, small-kibble nutrition designed for toy breeds, along"&amp;" with regular dental care to avoid early periodontal issues. Because warm weather increases parasite exposure, consistent tick and flea preventive treatments are essential. Annual maintenance costs for raising a Chihuahua in Madurai typically range from ₹"&amp;"15,000 to ₹35,000, which accounts for premium diet requirements, routine veterinary visits, mandatory rabies and core vaccinations, periodic deworming, and basic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A20 &amp; "" located in "" &amp; B20 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A20 &amp; "" Care Guide and Maintenance Costs in "" &amp; B20 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B20 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Madurai, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Madurai's warm, tropical climate requires a well-planned health and care routine tailored to local conditions. Due to high temperatures in re"&amp;"gions near KK Nagar and Anna Nagar, keeping your toy breed well-hydrated and housed in well-ventilated, air-conditioned spaces is crucial to prevent heat stress and hypoglycemia. Focus on high-protein, small-kibble nutrition designed for toy breeds, along"&amp;" with regular dental care to avoid early periodontal issues. Because warm weather increases parasite exposure, consistent tick and flea preventive treatments are essential. Annual maintenance costs for raising a Chihuahua in Madurai typically range from ₹"&amp;"15,000 to ₹35,000, which accounts for premium diet requirements, routine veterinary visits, mandatory rabies and core vaccinations, periodic deworming, and basic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Madurai, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Madurai's warm, tropical climate requires a well-planned health and care routine tailored to local conditions. Due to high temperatures in regions near KK Nagar and Anna Nagar, keeping your toy breed well-hydrated and housed in well-ventilated, air-conditioned spaces is crucial to prevent heat stress and hypoglycemia. Focus on high-protein, small-kibble nutrition designed for toy breeds, along with regular dental care to avoid early periodontal issues. Because warm weather increases parasite exposure, consistent tick and flea preventive treatments are essential. Annual maintenance costs for raising a Chihuahua in Madurai typically range from ₹15,000 to ₹35,000, which accounts for premium diet requirements, routine veterinary visits, mandatory rabies and core vaccinations, periodic deworming, and basic professional grooming.</v>
       </c>
       <c r="K20" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A20 &amp; "" in "" &amp; B20 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A20 &amp; "" in "" &amp; B20 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2395,11 +2417,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Madurai, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal guidelines apply when buying a Chihuahua puppy in Madurai?&lt;/h3&gt;&lt;p&gt;Pet owners across KK Nagar and Anna Nagar must follow Madurai Corporation regulations, which require valid rabies vaccination records and adherence to local pet management rules. Prior to buying, consider reviewing ethical sourcing options or reaching out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue and welfare organizations&lt;/a&gt; to explore adoption alternatives in Madurai.&lt;/p&gt;&lt;h3&gt;Where can I find reliable nearby vet care for toy breeds in Madurai?&lt;/h3&gt;&lt;p&gt;Veterinary centers located near Simmakkal and the Vaigai River belt offer specialized pediatric care, heatstroke prevention, and vaccination services for compact dogs. If you observe illegal breeding practices or neglect around local markets, notify &lt;a href="https://www.petaindia.com"&gt;animal protection advocates&lt;/a&gt; to take appropriate action.&lt;/p&gt;&lt;h3&gt;How do Chihuahua puppies manage Madurai's tropical climate?&lt;/h3&gt;&lt;p&gt;Due to intense heat near areas like Madurai Junction, toy breeds require shaded, well-ventilated indoor spaces and continuous hydration. Short morning walks near quiet residential streets keep them active while avoiding daytime temperature spikes.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2414,21 +2436,21 @@
       <c r="F21" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="2" t="s">
         <v>165</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="2" t="s">
         <v>167</v>
       </c>
       <c r="J21" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A21 &amp; "" located in "" &amp; B21 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A21 &amp; "" Care Guide and Maintenance Costs in "" &amp; B21 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B21 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Coimbatore, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Coimbatore requires a tailored wellness routine suited to South India's warm, tropical climate. Prioritize high-quality, small-kibble nutr"&amp;"ition high in protein to maintain their fast metabolism, ensure consistent indoor climate control to prevent heat stress, and establish daily oral hygiene habits to safeguard against early dental issues. In bustling residential hubs like RS Puram, DB Road"&amp;", and Avinashi Road, keep outdoor walks brief during peak sunlight hours to protect their sensitive paws from hot asphalt while keeping up with tick and flea prevention. On average, annual maintenance costs in Coimbatore range between ₹15,000 and ₹35,000,"&amp;" covering premium breed-specific food, routine veterinary health checks, core vaccinations, timely deworming, and regular grooming sessions.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A21 &amp; "" located in "" &amp; B21 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A21 &amp; "" Care Guide and Maintenance Costs in "" &amp; B21 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B21 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Coimbatore, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Coimbatore requires a tailored wellness routine suited to South India's warm, tropical climate. Prioritize high-quality, small-kibble nutr"&amp;"ition high in protein to maintain their fast metabolism, ensure consistent indoor climate control to prevent heat stress, and establish daily oral hygiene habits to safeguard against early dental issues. In bustling residential hubs like RS Puram, DB Road"&amp;", and Avinashi Road, keep outdoor walks brief during peak sunlight hours to protect their sensitive paws from hot asphalt while keeping up with tick and flea prevention. On average, annual maintenance costs in Coimbatore range between ₹15,000 and ₹35,000,"&amp;" covering premium breed-specific food, routine veterinary health checks, core vaccinations, timely deworming, and regular grooming sessions.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Coimbatore, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Coimbatore requires a tailored wellness routine suited to South India's warm, tropical climate. Prioritize high-quality, small-kibble nutrition high in protein to maintain their fast metabolism, ensure consistent indoor climate control to prevent heat stress, and establish daily oral hygiene habits to safeguard against early dental issues. In bustling residential hubs like RS Puram, DB Road, and Avinashi Road, keep outdoor walks brief during peak sunlight hours to protect their sensitive paws from hot asphalt while keeping up with tick and flea prevention. On average, annual maintenance costs in Coimbatore range between ₹15,000 and ₹35,000, covering premium breed-specific food, routine veterinary health checks, core vaccinations, timely deworming, and regular grooming sessions.</v>
       </c>
       <c r="K21" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A21 &amp; "" in "" &amp; B21 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A21 &amp; "" in "" &amp; B21 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2438,11 +2460,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Coimbatore, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal regulations and licensing apply to Chihuahua owners in Coimbatore?&lt;/h3&gt;&lt;p&gt;Pet parents around RS Puram and Avinashi Road must comply with Coimbatore City Municipal Corporation guidelines by maintaining valid rabies vaccination records and obtaining local dog licenses. Before purchasing, consider reviewing local ethical sourcing guidelines or reaching out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;compassionate animal rescue organizations&lt;/a&gt; for pet adoption options.&lt;/p&gt;&lt;h3&gt;Where can I find nearby vet care for Chihuahua puppies in Coimbatore?&lt;/h3&gt;&lt;p&gt;Trusted veterinary clinics located near Gandhipuram and DB Road provide routine vaccinations, microchipping, and specialized health evaluations for toy breeds. If you witness illegal breeding facilities or animal mistreatment near commercial hubs, submit a report through &lt;a href="https://www.petaindia.com"&gt;cruelty prevention channels&lt;/a&gt;.&lt;/p&gt;&lt;h3&gt;How do I protect a Chihuahua puppy from the summer heat in Coimbatore?&lt;/h3&gt;&lt;p&gt;Due to South India's warm tropical climate, keep your puppy in well-ventilated indoor areas during peak afternoon hours and walk them during cooler early mornings around quiet residential avenues near Brookefields Mall.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -2457,21 +2479,21 @@
       <c r="F22" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="2" t="s">
         <v>173</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="2" t="s">
         <v>175</v>
       </c>
       <c r="J22" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A22 &amp; "" located in "" &amp; B22 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A22 &amp; "" Care Guide and Maintenance Costs in "" &amp; B22 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B22 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Ooty, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the chilly, high-altitude climate of Ooty requires specific wellness routines focused on thermal protection and respiratory health. Due to their"&amp;" minute body mass and short coat, toy breeds in the Nilgiris are particularly sensitive to cold mountain air and damp weather, making insulated sweaters, fleece-lined bedding, and draft-free indoor resting spots essential around areas like Charring Cross "&amp;"and Commercial Road. Maintain a calorie-dense, high-protein diet to support metabolic heat production, provide indoor activity options during heavy mist or rains, and keep up with strict dental care to prevent early oral issues. On average, annual care an"&amp;"d maintenance costs in Ooty range between ₹18,000 and ₹40,000, covering premium nutrient-rich kibble, thermal wear, core vaccinations, deworming, routine veterinary wellness checks, and basic grooming supplies.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A22 &amp; "" located in "" &amp; B22 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A22 &amp; "" Care Guide and Maintenance Costs in "" &amp; B22 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B22 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Ooty, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the chilly, high-altitude climate of Ooty requires specific wellness routines focused on thermal protection and respiratory health. Due to their"&amp;" minute body mass and short coat, toy breeds in the Nilgiris are particularly sensitive to cold mountain air and damp weather, making insulated sweaters, fleece-lined bedding, and draft-free indoor resting spots essential around areas like Charring Cross "&amp;"and Commercial Road. Maintain a calorie-dense, high-protein diet to support metabolic heat production, provide indoor activity options during heavy mist or rains, and keep up with strict dental care to prevent early oral issues. On average, annual care an"&amp;"d maintenance costs in Ooty range between ₹18,000 and ₹40,000, covering premium nutrient-rich kibble, thermal wear, core vaccinations, deworming, routine veterinary wellness checks, and basic grooming supplies.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Ooty, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the chilly, high-altitude climate of Ooty requires specific wellness routines focused on thermal protection and respiratory health. Due to their minute body mass and short coat, toy breeds in the Nilgiris are particularly sensitive to cold mountain air and damp weather, making insulated sweaters, fleece-lined bedding, and draft-free indoor resting spots essential around areas like Charring Cross and Commercial Road. Maintain a calorie-dense, high-protein diet to support metabolic heat production, provide indoor activity options during heavy mist or rains, and keep up with strict dental care to prevent early oral issues. On average, annual care and maintenance costs in Ooty range between ₹18,000 and ₹40,000, covering premium nutrient-rich kibble, thermal wear, core vaccinations, deworming, routine veterinary wellness checks, and basic grooming supplies.</v>
       </c>
       <c r="K22" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A22 &amp; "" in "" &amp; B22 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A22 &amp; "" in "" &amp; B22 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2481,11 +2503,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Ooty, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What local regulations and animal welfare guidelines apply when getting a Chihuahua in Ooty?&lt;/h3&gt;&lt;p&gt;Pet parents across the Nilgiris district must ensure proper rabies vaccinations and comply with local municipal registration rules. Prospective owners are encouraged to review &lt;a href="https://www.peopleforanimalsindia.org"&gt;local adoption guidelines&lt;/a&gt; or verify that commercial breeders adhere to ethical handling standards.&lt;/p&gt;&lt;h3&gt;How should I protect a Chihuahua puppy against Ooty's cold high-altitude climate?&lt;/h3&gt;&lt;p&gt;Given the chilly weather near Charring Cross and Commercial Road, provide warm thermal sweaters, draft-free bedding, and calorie-dense nutrition. For routine immunizations and climate-specific guidance, seek nearby vet care around Udhagamandalam.&lt;/p&gt;&lt;h3&gt;Where can I report illegal breeding or pet mistreatment in the Nilgiris area?&lt;/h3&gt;&lt;p&gt;If you suspect unauthorized breeding kennels or encounter animal abuse near local markets, contact &lt;a href="https://www.petaindia.com"&gt;cruelty reporting organizations&lt;/a&gt; to alert animal protection authorities.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2500,21 +2522,21 @@
       <c r="F23" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>181</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="2" t="s">
         <v>183</v>
       </c>
       <c r="J23" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A23 &amp; "" located in "" &amp; B23 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A23 &amp; "" Care Guide and Maintenance Costs in "" &amp; B23 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B23 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kodaikanal, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the chilly, high-altitude hill station of Kodaikanal requires dedicated attention to thermal regulation and cold-weather wellness. Given t"&amp;"heir minimal body fat and high sensitivity to low temperatures, keeping your pup equipped with fleece sweaters, insulated bedding, and indoor heating during misty mornings around Kodaikanal Lake or Bryant Park is essential to prevent hypothermia and hypog"&amp;"lycemia. Prioritize high-calorie, nutrient-dense puppy food to help maintain their metabolic heat, along with regular dental care and protected exercise routines on damp outdoor trails to avoid respiratory distress. Annual maintenance costs in Kodaikanal "&amp;"typically range between ₹15,000 and ₹35,000, which covers premium toy-breed nutrition, cold-weather accessories, routine veterinary visits, mandatory vaccinations, deworming, and periodic grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A23 &amp; "" located in "" &amp; B23 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A23 &amp; "" Care Guide and Maintenance Costs in "" &amp; B23 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B23 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kodaikanal, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the chilly, high-altitude hill station of Kodaikanal requires dedicated attention to thermal regulation and cold-weather wellness. Given t"&amp;"heir minimal body fat and high sensitivity to low temperatures, keeping your pup equipped with fleece sweaters, insulated bedding, and indoor heating during misty mornings around Kodaikanal Lake or Bryant Park is essential to prevent hypothermia and hypog"&amp;"lycemia. Prioritize high-calorie, nutrient-dense puppy food to help maintain their metabolic heat, along with regular dental care and protected exercise routines on damp outdoor trails to avoid respiratory distress. Annual maintenance costs in Kodaikanal "&amp;"typically range between ₹15,000 and ₹35,000, which covers premium toy-breed nutrition, cold-weather accessories, routine veterinary visits, mandatory vaccinations, deworming, and periodic grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kodaikanal, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the chilly, high-altitude hill station of Kodaikanal requires dedicated attention to thermal regulation and cold-weather wellness. Given their minimal body fat and high sensitivity to low temperatures, keeping your pup equipped with fleece sweaters, insulated bedding, and indoor heating during misty mornings around Kodaikanal Lake or Bryant Park is essential to prevent hypothermia and hypoglycemia. Prioritize high-calorie, nutrient-dense puppy food to help maintain their metabolic heat, along with regular dental care and protected exercise routines on damp outdoor trails to avoid respiratory distress. Annual maintenance costs in Kodaikanal typically range between ₹15,000 and ₹35,000, which covers premium toy-breed nutrition, cold-weather accessories, routine veterinary visits, mandatory vaccinations, deworming, and periodic grooming.</v>
       </c>
       <c r="K23" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A23 &amp; "" in "" &amp; B23 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A23 &amp; "" in "" &amp; B23 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2524,11 +2546,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Kodaikanal, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What local animal welfare laws and registration guidelines apply in Kodaikanal?&lt;/h3&gt;&lt;p&gt;Pet owners in the Dindigul district around Coaker's Walk and Bryant Park must maintain up-to-date anti-rabies vaccination records and adhere to Tamil Nadu local body pet guidelines. Before purchasing a puppy, review ethical breeding practices or consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; to consider adoption alternatives.&lt;/p&gt;&lt;h3&gt;Where can I find reliable nearby vet care for a toy breed in Kodaikanal?&lt;/h3&gt;&lt;p&gt;Veterinary services around Kodaikanal Lake and Laws Ghat Road offer routine wellness examinations, thermal management advice, and core immunizations for Chihuahuas. If you witness unethical breeding conditions or animal abuse in the Nilgiris-Dindigul hill region, report the incident to &lt;a href="https://www.petaindia.com"&gt;cruelty prevention groups&lt;/a&gt;.&lt;/p&gt;&lt;h3&gt;How do I care for a Chihuahua puppy in Kodaikanal's cold hill climate?&lt;/h3&gt;&lt;p&gt;Due to high altitude and damp weather near Coaker's Walk, Chihuahua puppies require fleece apparel, heated indoor spaces, and high-calorie nutrition to prevent hypothermia and hypoglycemia during cold mornings.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2543,21 +2565,21 @@
       <c r="F24" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="2" t="s">
         <v>189</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="2" t="s">
         <v>191</v>
       </c>
       <c r="J24" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A24 &amp; "" located in "" &amp; B24 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A24 &amp; "" Care Guide and Maintenance Costs in "" &amp; B24 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B24 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Tirupur, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Tirupur requires a thoughtful management routine adapted to the region's warm industrial environment. To support your pet's long-term health "&amp;"near prominent areas like Avinashi Road and Gandhi Nagar, provide high-protein nutrition formulated specifically for toy breeds, ensure continuous hydration to manage warm weather, and establish daily oral hygiene to prevent early periodontal disease. Nav"&amp;"igating busy municipal streets and surrounding textile hubs exposes delicate puppies to ambient dust, traffic noise, and heat stress, making consistent climate control, regular coat grooming, and up-to-date tick prevention essential. On average, annual ma"&amp;"intenance costs in Tirupur range between ₹15,000 and ₹35,000, covering quality puppy food, routine veterinary checkups, core vaccinations, deworming schedules, and periodic grooming treatments.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A24 &amp; "" located in "" &amp; B24 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A24 &amp; "" Care Guide and Maintenance Costs in "" &amp; B24 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B24 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Tirupur, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Tirupur requires a thoughtful management routine adapted to the region's warm industrial environment. To support your pet's long-term health "&amp;"near prominent areas like Avinashi Road and Gandhi Nagar, provide high-protein nutrition formulated specifically for toy breeds, ensure continuous hydration to manage warm weather, and establish daily oral hygiene to prevent early periodontal disease. Nav"&amp;"igating busy municipal streets and surrounding textile hubs exposes delicate puppies to ambient dust, traffic noise, and heat stress, making consistent climate control, regular coat grooming, and up-to-date tick prevention essential. On average, annual ma"&amp;"intenance costs in Tirupur range between ₹15,000 and ₹35,000, covering quality puppy food, routine veterinary checkups, core vaccinations, deworming schedules, and periodic grooming treatments.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Tirupur, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Tirupur requires a thoughtful management routine adapted to the region's warm industrial environment. To support your pet's long-term health near prominent areas like Avinashi Road and Gandhi Nagar, provide high-protein nutrition formulated specifically for toy breeds, ensure continuous hydration to manage warm weather, and establish daily oral hygiene to prevent early periodontal disease. Navigating busy municipal streets and surrounding textile hubs exposes delicate puppies to ambient dust, traffic noise, and heat stress, making consistent climate control, regular coat grooming, and up-to-date tick prevention essential. On average, annual maintenance costs in Tirupur range between ₹15,000 and ₹35,000, covering quality puppy food, routine veterinary checkups, core vaccinations, deworming schedules, and periodic grooming treatments.</v>
       </c>
       <c r="K24" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A24 &amp; "" in "" &amp; B24 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A24 &amp; "" in "" &amp; B24 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2567,11 +2589,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Tirupur, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal guidelines apply when acquiring a Chihuahua puppy in Tirupur?&lt;/h3&gt;&lt;p&gt;Pet owners along Avinashi Road and Gandhi Nagar must register their dogs with the Tirupur City Municipal Corporation, keep rabies vaccinations up to date, and adhere to local pet ownership norms. To promote ethical practices, review local adoption guidelines or reach out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue and adoption networks&lt;/a&gt; before purchasing.&lt;/p&gt;&lt;h3&gt;Where can I access nearby vet care for toy breeds in Tirupur?&lt;/h3&gt;&lt;p&gt;Veterinary clinics near Kumaran Road and Rayapuram offer routine immunizations, health checks, and preventive treatments for small breeds. If you encounter mistreatment or unethical breeding practices in the textile hub, report them through &lt;a href="https://www.petaindia.com"&gt;animal protection organizations&lt;/a&gt; to ensure compliance with animal welfare standards.&lt;/p&gt;&lt;h3&gt;How do I care for a Chihuahua puppy in Tirupur's climate?&lt;/h3&gt;&lt;p&gt;Due to warm weather near industrial areas, ensure your Chihuahua stays hydrated, resides in a well-ventilated space, and receives regular grooming to manage dust exposure along busy transit routes like Kumaran Road.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2586,21 +2608,21 @@
       <c r="F25" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="2" t="s">
         <v>197</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J25" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A25 &amp; "" located in "" &amp; B25 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A25 &amp; "" Care Guide and Maintenance Costs in "" &amp; B25 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B25 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Karur, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the bustling textile hub of Karur requires a dedicated wellness routine adapted to the region's warm inland climate. To keep your toy breed hea"&amp;"lthy near Kovai Road and Jawahar Bazaar, prioritize a nutrient-dense diet formulated for small breeds, ensure constant access to fresh water to prevent heat exhaustion, and maintain strict daily dental care to avoid early oral health issues. Warm ambient "&amp;"temperatures and dusty urban streets around the Pasupathiswarar Temple precinct make routine tick prevention, coat hygiene, and indoor temperature management essential. On average, annual maintenance costs in Karur range between ₹12,000 and ₹30,000, cover"&amp;"ing high-quality puppy kibble, routine veterinary checkups, core vaccinations, deworming, and essential grooming supplies.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A25 &amp; "" located in "" &amp; B25 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A25 &amp; "" Care Guide and Maintenance Costs in "" &amp; B25 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B25 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Karur, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the bustling textile hub of Karur requires a dedicated wellness routine adapted to the region's warm inland climate. To keep your toy breed hea"&amp;"lthy near Kovai Road and Jawahar Bazaar, prioritize a nutrient-dense diet formulated for small breeds, ensure constant access to fresh water to prevent heat exhaustion, and maintain strict daily dental care to avoid early oral health issues. Warm ambient "&amp;"temperatures and dusty urban streets around the Pasupathiswarar Temple precinct make routine tick prevention, coat hygiene, and indoor temperature management essential. On average, annual maintenance costs in Karur range between ₹12,000 and ₹30,000, cover"&amp;"ing high-quality puppy kibble, routine veterinary checkups, core vaccinations, deworming, and essential grooming supplies.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Karur, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the bustling textile hub of Karur requires a dedicated wellness routine adapted to the region's warm inland climate. To keep your toy breed healthy near Kovai Road and Jawahar Bazaar, prioritize a nutrient-dense diet formulated for small breeds, ensure constant access to fresh water to prevent heat exhaustion, and maintain strict daily dental care to avoid early oral health issues. Warm ambient temperatures and dusty urban streets around the Pasupathiswarar Temple precinct make routine tick prevention, coat hygiene, and indoor temperature management essential. On average, annual maintenance costs in Karur range between ₹12,000 and ₹30,000, covering high-quality puppy kibble, routine veterinary checkups, core vaccinations, deworming, and essential grooming supplies.</v>
       </c>
       <c r="K25" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A25 &amp; "" in "" &amp; B25 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A25 &amp; "" in "" &amp; B25 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2610,11 +2632,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies for Sale in Karur, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal rules and local adoption guidelines apply in Karur?&lt;/h3&gt;&lt;p&gt;Pet owners near Kovai Road and Jawahar Bazaar should register their Chihuahua with the Karur City Municipal Corporation and keep rabies vaccinations current. Before buying, review ethical pet ownership standards or connect with &lt;a href="https://www.peopleforanimalsindia.org"&gt;local animal rescue networks&lt;/a&gt; to consider adoption options.&lt;/p&gt;&lt;h3&gt;How can I report unethical breeding or pet neglect in Karur?&lt;/h3&gt;&lt;p&gt;If you encounter unauthorized breeding setups or poor welfare conditions around the Pasupathiswarar Temple area, reach out to &lt;a href="https://www.petaindia.com"&gt;animal protection advocates&lt;/a&gt; to lodge a formal cruelty complaint and ensure statutory standards are enforced.&lt;/p&gt;&lt;h3&gt;Where can I find reliable vet care for small breed puppies in Karur?&lt;/h3&gt;&lt;p&gt;Veterinary services located near the New Bus Stand and Kovai Road offer dedicated health checks, vaccination schedules, and nutritional guidance tailored to toy breeds managing Karur's warm inland climate.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2629,21 +2651,21 @@
       <c r="F26" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>205</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="2" t="s">
         <v>207</v>
       </c>
       <c r="J26" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A26 &amp; "" located in "" &amp; B26 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A26 &amp; "" Care Guide and Maintenance Costs in "" &amp; B26 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B26 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in RS Puram, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the upscale neighborhood of RS Puram, Coimbatore requires a consistent wellness and care routine tailored for compact urban living. To ensur"&amp;"e optimal vitality, provide high-protein nutrition specifically formulated for toy breeds, engage in indoor mental play alongside gentle morning strolls near DB Road or Kumaraswamy Park, and maintain daily dental care to avoid early periodontal issues. Co"&amp;"imbatore's warm, tropical climate makes heat management, constant access to fresh water, tick prevention, and regular grooming essential for sensitive toy companions. On average, annual maintenance costs in RS Puram range between ₹15,000 and ₹35,000, cove"&amp;"ring premium puppy food, routine veterinary checkups, core vaccinations, deworming, and professional grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A26 &amp; "" located in "" &amp; B26 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A26 &amp; "" Care Guide and Maintenance Costs in "" &amp; B26 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B26 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in RS Puram, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the upscale neighborhood of RS Puram, Coimbatore requires a consistent wellness and care routine tailored for compact urban living. To ensur"&amp;"e optimal vitality, provide high-protein nutrition specifically formulated for toy breeds, engage in indoor mental play alongside gentle morning strolls near DB Road or Kumaraswamy Park, and maintain daily dental care to avoid early periodontal issues. Co"&amp;"imbatore's warm, tropical climate makes heat management, constant access to fresh water, tick prevention, and regular grooming essential for sensitive toy companions. On average, annual maintenance costs in RS Puram range between ₹15,000 and ₹35,000, cove"&amp;"ring premium puppy food, routine veterinary checkups, core vaccinations, deworming, and professional grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in RS Puram, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the upscale neighborhood of RS Puram, Coimbatore requires a consistent wellness and care routine tailored for compact urban living. To ensure optimal vitality, provide high-protein nutrition specifically formulated for toy breeds, engage in indoor mental play alongside gentle morning strolls near DB Road or Kumaraswamy Park, and maintain daily dental care to avoid early periodontal issues. Coimbatore's warm, tropical climate makes heat management, constant access to fresh water, tick prevention, and regular grooming essential for sensitive toy companions. On average, annual maintenance costs in RS Puram range between ₹15,000 and ₹35,000, covering premium puppy food, routine veterinary checkups, core vaccinations, deworming, and professional grooming services.</v>
       </c>
       <c r="K26" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A26 &amp; "" in "" &amp; B26 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A26 &amp; "" in "" &amp; B26 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2653,11 +2675,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in RS Puram, Coimbatore - FAQs&lt;/h2&gt;&lt;h3&gt;What local pet registration laws apply to Chihuahua owners in RS Puram?&lt;/h3&gt;&lt;p&gt;Pet owners near DB Road and TV Swamy Road must comply with Coimbatore City Municipal Corporation guidelines by maintaining valid anti-rabies vaccination records and securing local pet permits. Before buying a puppy, check &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; to consider ethical adoption alternatives in the area.&lt;/p&gt;&lt;h3&gt;Where can I find nearby vet care and clinics for toy breeds in RS Puram?&lt;/h3&gt;&lt;p&gt;Veterinary facilities around DB Road and Brookefields Mall offer routine health checks, diagnostic screenings, and vaccination services for delicate toy breeds like Chihuahuas. If you witness unethical breeding practices or animal mistreatment near commercial hubs, contact &lt;a href="https://www.petaindia.com"&gt;animal protection advocates&lt;/a&gt; to file a formal report.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for residential apartment living in RS Puram?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in RS Puram apartments due to their tiny size and low space requirements. Light daily walks near Kumaraswamy Park paired with indoor play keep them mentally stimulated and healthy in Coimbatore's warm climate.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2672,21 +2694,21 @@
       <c r="F27" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="2" t="s">
         <v>213</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="2" t="s">
         <v>215</v>
       </c>
       <c r="J27" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A27 &amp; "" located in "" &amp; B27 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A27 &amp; "" Care Guide and Maintenance Costs in "" &amp; B27 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B27 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Gandhipuram, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the bustling commercial heart of Gandhipuram, Coimbatore requires a well-balanced health and upkeep regimen designed for urban living. To"&amp;" safeguard your puppy's well-being near busy commercial corridors like Cross Cut Road and 100 Feet Road, prioritize high-protein toy-breed nutrition, daily indoor exercise to avoid traffic hazards, and strict dental hygiene to prevent early periodontal is"&amp;"sues. Navigating Gandhipuram's dense urban environment exposes delicate pups to heat stress, ambient dust, and noise pollution, making constant hydration, indoor climate control, and routine grooming critical. On average, annual maintenance costs in Gandh"&amp;"ipuram range from ₹15,000 to ₹35,000, which covers quality puppy kibble, routine veterinary checkups, core vaccinations, preventive parasite care, and periodic grooming treatments.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A27 &amp; "" located in "" &amp; B27 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A27 &amp; "" Care Guide and Maintenance Costs in "" &amp; B27 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B27 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Gandhipuram, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the bustling commercial heart of Gandhipuram, Coimbatore requires a well-balanced health and upkeep regimen designed for urban living. To"&amp;" safeguard your puppy's well-being near busy commercial corridors like Cross Cut Road and 100 Feet Road, prioritize high-protein toy-breed nutrition, daily indoor exercise to avoid traffic hazards, and strict dental hygiene to prevent early periodontal is"&amp;"sues. Navigating Gandhipuram's dense urban environment exposes delicate pups to heat stress, ambient dust, and noise pollution, making constant hydration, indoor climate control, and routine grooming critical. On average, annual maintenance costs in Gandh"&amp;"ipuram range from ₹15,000 to ₹35,000, which covers quality puppy kibble, routine veterinary checkups, core vaccinations, preventive parasite care, and periodic grooming treatments.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Gandhipuram, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the bustling commercial heart of Gandhipuram, Coimbatore requires a well-balanced health and upkeep regimen designed for urban living. To safeguard your puppy's well-being near busy commercial corridors like Cross Cut Road and 100 Feet Road, prioritize high-protein toy-breed nutrition, daily indoor exercise to avoid traffic hazards, and strict dental hygiene to prevent early periodontal issues. Navigating Gandhipuram's dense urban environment exposes delicate pups to heat stress, ambient dust, and noise pollution, making constant hydration, indoor climate control, and routine grooming critical. On average, annual maintenance costs in Gandhipuram range from ₹15,000 to ₹35,000, which covers quality puppy kibble, routine veterinary checkups, core vaccinations, preventive parasite care, and periodic grooming treatments.</v>
       </c>
       <c r="K27" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A27 &amp; "" in "" &amp; B27 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A27 &amp; "" in "" &amp; B27 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2696,11 +2718,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Gandhipuram, Coimbatore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal regulations apply when acquiring a Chihuahua puppy in Gandhipuram?&lt;/h3&gt;&lt;p&gt;Pet parents around 100 Feet Road and Cross Cut Road must register their dogs with the Coimbatore City Municipal Corporation, complete microchipping, and keep rabies immunizations up to date. Prior to buying, ensure breeders comply with ethical guidelines or consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;community rescue programs&lt;/a&gt; for local adoption options.&lt;/p&gt;&lt;h3&gt;Where can I find nearby vet care for toy breeds in Gandhipuram?&lt;/h3&gt;&lt;p&gt;Veterinary clinics operating near Brookefields Mall and the Gandhipuram Bus Stand offer essential puppy immunizations, routine checkups, and diagnostic screenings. If you encounter illegal breeding or animal mistreatment near commercial hubs, contact &lt;a href="https://www.petaindia.com"&gt;humane treatment advocates&lt;/a&gt; to lodge a formal report.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for urban living in central Gandhipuram?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in apartment settings along busy corridors like Cross Cut Road. Providing daily indoor playtime, adequate hydration, and climate-controlled living protects delicate puppies from central Coimbatore's high traffic and warm ambient temperatures.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2715,21 +2737,21 @@
       <c r="F28" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>221</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="2" t="s">
         <v>223</v>
       </c>
       <c r="J28" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A28 &amp; "" located in "" &amp; B28 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A28 &amp; "" Care Guide and Maintenance Costs in "" &amp; B28 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B28 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Saibaba Colony, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Saibaba Colony requires a well-structured care and wellness routine tailored to North Coimbatore's residential climate. To ensure robu"&amp;"st development, feed high-quality, nutrient-dense kibble designed for toy breeds, maintain strict daily dental hygiene to prevent early periodontitis, and schedule short morning or evening walks along peaceful avenues like NSR Road or Alagesan Road to kee"&amp;"p them active without overheating. Protecting your tiny pet against local environmental factors requires consistent tick and flea treatments, proper ventilation during warmer months, and routine coat brushing. On average, annual care and maintenance costs"&amp;" in Saibaba Colony range between ₹15,000 and ₹35,000, which covers premium small-breed food, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A28 &amp; "" located in "" &amp; B28 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A28 &amp; "" Care Guide and Maintenance Costs in "" &amp; B28 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B28 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Saibaba Colony, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Saibaba Colony requires a well-structured care and wellness routine tailored to North Coimbatore's residential climate. To ensure robu"&amp;"st development, feed high-quality, nutrient-dense kibble designed for toy breeds, maintain strict daily dental hygiene to prevent early periodontitis, and schedule short morning or evening walks along peaceful avenues like NSR Road or Alagesan Road to kee"&amp;"p them active without overheating. Protecting your tiny pet against local environmental factors requires consistent tick and flea treatments, proper ventilation during warmer months, and routine coat brushing. On average, annual care and maintenance costs"&amp;" in Saibaba Colony range between ₹15,000 and ₹35,000, which covers premium small-breed food, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Saibaba Colony, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Saibaba Colony requires a well-structured care and wellness routine tailored to North Coimbatore's residential climate. To ensure robust development, feed high-quality, nutrient-dense kibble designed for toy breeds, maintain strict daily dental hygiene to prevent early periodontitis, and schedule short morning or evening walks along peaceful avenues like NSR Road or Alagesan Road to keep them active without overheating. Protecting your tiny pet against local environmental factors requires consistent tick and flea treatments, proper ventilation during warmer months, and routine coat brushing. On average, annual care and maintenance costs in Saibaba Colony range between ₹15,000 and ₹35,000, which covers premium small-breed food, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.</v>
       </c>
       <c r="K28" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A28 &amp; "" in "" &amp; B28 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A28 &amp; "" in "" &amp; B28 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2739,11 +2761,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Saibaba Colony, Coimbatore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal regulations and licensing rules apply to Chihuahua puppies in Saibaba Colony?&lt;/h3&gt;&lt;p&gt;Pet parents around NSR Road and Alagesan Road must register their dogs with the Coimbatore City Municipal Corporation and keep up-to-date rabies immunizations. Before bringing home a puppy, consider local adoption guidelines or consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue and shelter organizations&lt;/a&gt; to explore rehoming opportunities.&lt;/p&gt;&lt;h3&gt;Where can I find reliable nearby vet care for toy breeds in Saibaba Colony?&lt;/h3&gt;&lt;p&gt;Veterinary clinics near Mettupalayam Road and Thadagam Road offer specialized care, vaccinations, and routine health checks for small breeds. If you notice unethical breeding facilities or poor conditions nearby, report them directly to &lt;a href="https://www.petaindia.com"&gt;animal protection advocates&lt;/a&gt; to ensure proper care standards are enforced.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies well-suited for home environments in Saibaba Colony?&lt;/h3&gt;&lt;p&gt;Yes, their compact size makes them perfectly suited for apartment residences and residential layouts in North Coimbatore. Regular short walks along quieter neighborhood streets paired with indoor activities provide adequate daily exercise for these energetic companions.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2758,21 +2780,21 @@
       <c r="F29" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="2" t="s">
         <v>228</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="2" t="s">
         <v>230</v>
       </c>
       <c r="J29" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A29 &amp; "" located in "" &amp; B29 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A29 &amp; "" Care Guide and Maintenance Costs in "" &amp; B29 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B29 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Peelamedu, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Peelamedu’s fast-paced tech and educational corridor requires a well-regulated routine tailored to urban apartment living near Avinashi Roa"&amp;"d and TIDEL Park. To keep your toy companion thriving, provide a nutrient-rich diet specifically formulated for small breeds, establish a consistent indoor dental care regimen to prevent early periodontal issues, and ensure moderate daily exercise during "&amp;"cooler morning or evening hours around quiet residential pockets near PSG College. Coimbatore's warm microclimate and heavy transit exposure mean pet parents must prioritize constant hydration, indoor climate control, proactive tick and flea treatments, a"&amp;"nd protection against pavement heat. On average, annual care and maintenance costs in Peelamedu range from ₹15,000 to ₹35,000, covering high-quality puppy food, routine veterinary health checkups, scheduled vaccinations, deworming protocols, and essential"&amp;" grooming sessions.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A29 &amp; "" located in "" &amp; B29 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A29 &amp; "" Care Guide and Maintenance Costs in "" &amp; B29 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B29 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Peelamedu, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Peelamedu’s fast-paced tech and educational corridor requires a well-regulated routine tailored to urban apartment living near Avinashi Roa"&amp;"d and TIDEL Park. To keep your toy companion thriving, provide a nutrient-rich diet specifically formulated for small breeds, establish a consistent indoor dental care regimen to prevent early periodontal issues, and ensure moderate daily exercise during "&amp;"cooler morning or evening hours around quiet residential pockets near PSG College. Coimbatore's warm microclimate and heavy transit exposure mean pet parents must prioritize constant hydration, indoor climate control, proactive tick and flea treatments, a"&amp;"nd protection against pavement heat. On average, annual care and maintenance costs in Peelamedu range from ₹15,000 to ₹35,000, covering high-quality puppy food, routine veterinary health checkups, scheduled vaccinations, deworming protocols, and essential"&amp;" grooming sessions.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Peelamedu, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Peelamedu’s fast-paced tech and educational corridor requires a well-regulated routine tailored to urban apartment living near Avinashi Road and TIDEL Park. To keep your toy companion thriving, provide a nutrient-rich diet specifically formulated for small breeds, establish a consistent indoor dental care regimen to prevent early periodontal issues, and ensure moderate daily exercise during cooler morning or evening hours around quiet residential pockets near PSG College. Coimbatore's warm microclimate and heavy transit exposure mean pet parents must prioritize constant hydration, indoor climate control, proactive tick and flea treatments, and protection against pavement heat. On average, annual care and maintenance costs in Peelamedu range from ₹15,000 to ₹35,000, covering high-quality puppy food, routine veterinary health checkups, scheduled vaccinations, deworming protocols, and essential grooming sessions.</v>
       </c>
       <c r="K29" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A29 &amp; "" in "" &amp; B29 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A29 &amp; "" in "" &amp; B29 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2782,11 +2804,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Peelamedu, Coimbatore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal registration rules apply when getting a Chihuahua puppy in Peelamedu?&lt;/h3&gt;&lt;p&gt;Pet owners near Avinashi Road and TIDEL Park must follow Coimbatore City Municipal Corporation regulations regarding annual pet licensing, mandatory microchipping, and updated rabies immunizations. Before purchasing, verify ethical breeding credentials or check &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue group networks&lt;/a&gt; for local adoption options.&lt;/p&gt;&lt;h3&gt;Where can I find reliable nearby vet care for toy breeds around Peelamedu?&lt;/h3&gt;&lt;p&gt;Established veterinary clinics near Fun Republic Mall and PSG College offer specialized care for toy breeds, including patellar evaluations and dental checks. If you suspect unethical breeding practices or animal neglect in the IT belt, report it to &lt;a href="https://www.petaindia.com"&gt;animal protection organizations&lt;/a&gt; immediately.&lt;/p&gt;&lt;h3&gt;How do I care for a Chihuahua puppy in Peelamedu's warm climate?&lt;/h3&gt;&lt;p&gt;Keep your puppy indoors during peak afternoon temperatures, provide continuous access to fresh water, and exercise them during cooler hours near quiet residential lanes in Peelamedu. Regular hydration and temperature monitoring prevent heat stress in tiny toy breeds.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2801,21 +2823,21 @@
       <c r="F30" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="2" t="s">
         <v>236</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="2" t="s">
         <v>238</v>
       </c>
       <c r="J30" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A30 &amp; "" located in "" &amp; B30 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A30 &amp; "" Care Guide and Maintenance Costs in "" &amp; B30 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B30 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Singanallur, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Singanallur requires a dedicated wellness approach adapted to eastern Coimbatore's busy urban climate along the Trichy Road corridor. To "&amp;"keep your toy breed thriving near Kamarajar Road and Singanallur Lake, provide nutrient-rich puppy food designed for mini breeds, maintain regular dental brushing to avoid periodontitis, and schedule short outdoor walks during cooler morning hours to safe"&amp;"guard them against pavement heat. Navigating dense traffic zones and local humidity makes consistent tick and flea control, proper indoor ventilation, and routine coat grooming essential. On average, annual care and maintenance costs in Singanallur range "&amp;"from ₹15,000 to ₹35,000, covering high-quality nutrition, routine veterinary checkups, core vaccinations, deworming, and periodic grooming treatments.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A30 &amp; "" located in "" &amp; B30 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A30 &amp; "" Care Guide and Maintenance Costs in "" &amp; B30 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B30 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Singanallur, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Singanallur requires a dedicated wellness approach adapted to eastern Coimbatore's busy urban climate along the Trichy Road corridor. To "&amp;"keep your toy breed thriving near Kamarajar Road and Singanallur Lake, provide nutrient-rich puppy food designed for mini breeds, maintain regular dental brushing to avoid periodontitis, and schedule short outdoor walks during cooler morning hours to safe"&amp;"guard them against pavement heat. Navigating dense traffic zones and local humidity makes consistent tick and flea control, proper indoor ventilation, and routine coat grooming essential. On average, annual care and maintenance costs in Singanallur range "&amp;"from ₹15,000 to ₹35,000, covering high-quality nutrition, routine veterinary checkups, core vaccinations, deworming, and periodic grooming treatments.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Singanallur, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Singanallur requires a dedicated wellness approach adapted to eastern Coimbatore's busy urban climate along the Trichy Road corridor. To keep your toy breed thriving near Kamarajar Road and Singanallur Lake, provide nutrient-rich puppy food designed for mini breeds, maintain regular dental brushing to avoid periodontitis, and schedule short outdoor walks during cooler morning hours to safeguard them against pavement heat. Navigating dense traffic zones and local humidity makes consistent tick and flea control, proper indoor ventilation, and routine coat grooming essential. On average, annual care and maintenance costs in Singanallur range from ₹15,000 to ₹35,000, covering high-quality nutrition, routine veterinary checkups, core vaccinations, deworming, and periodic grooming treatments.</v>
       </c>
       <c r="K30" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A30 &amp; "" in "" &amp; B30 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A30 &amp; "" in "" &amp; B30 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2825,11 +2847,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Singanallur, Coimbatore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal guidelines affect Chihuahua owners in Singanallur?&lt;/h3&gt;&lt;p&gt;Pet owners near Trichy Road and Kamarajar Road must adhere to Coimbatore City Municipal Corporation rules, which mandate microchipping and annual anti-rabies vaccinations. Prospective owners are encouraged to consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue groups&lt;/a&gt; to consider adoption before purchasing from commercial breeders.&lt;/p&gt;&lt;h3&gt;Where can I find reliable veterinary care for toy breeds around Singanallur?&lt;/h3&gt;&lt;p&gt;Veterinary clinics near Singanallur Lake and the bus terminus offer routine health checkups, deworming, and specialized care for small breeds. If you witness unethical breeding practices or animal mistreatment near commercial hubs, report them directly to &lt;a href="https://www.petaindia.com"&gt;cruelty prevention organizations&lt;/a&gt;.&lt;/p&gt;&lt;h3&gt;Are Chihuahuas suited for residential living in eastern Coimbatore?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in compact homes due to their small size. Regular indoor activity alongside brief morning walks near quieter residential pockets in Singanallur provides sufficient exercise while protecting them from high pavement temperatures.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2844,21 +2866,21 @@
       <c r="F31" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="2" t="s">
         <v>244</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="2" t="s">
         <v>246</v>
       </c>
       <c r="J31" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A31 &amp; "" located in "" &amp; B31 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A31 &amp; "" Care Guide and Maintenance Costs in "" &amp; B31 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B31 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Ramanathapuram, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Ramanathapuram, Coimbatore requires a tailored wellness routine suited to the warm climate and active urban environment near Trichy Ro"&amp;"ad and Nanjundapuram Road. To keep your toy breed in optimal health, prioritize a nutrient-dense, high-protein diet specially formulated for small dogs, maintain continuous hydration, and keep indoor living spaces well-ventilated to prevent heat exhaustio"&amp;"n. Daily care should focus on gentle indoor play, controlled short walks near quieter spots along Sungam Bypass, and consistent oral hygiene to protect against early dental issues common in toy breeds. Expect annual routine maintenance and care expenses i"&amp;"n Ramanathapuram to range from ₹15,000 to ₹35,000, which covers high-quality puppy food, routine veterinary health checks, mandatory vaccinations, deworming, and periodic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A31 &amp; "" located in "" &amp; B31 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A31 &amp; "" Care Guide and Maintenance Costs in "" &amp; B31 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B31 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Ramanathapuram, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Ramanathapuram, Coimbatore requires a tailored wellness routine suited to the warm climate and active urban environment near Trichy Ro"&amp;"ad and Nanjundapuram Road. To keep your toy breed in optimal health, prioritize a nutrient-dense, high-protein diet specially formulated for small dogs, maintain continuous hydration, and keep indoor living spaces well-ventilated to prevent heat exhaustio"&amp;"n. Daily care should focus on gentle indoor play, controlled short walks near quieter spots along Sungam Bypass, and consistent oral hygiene to protect against early dental issues common in toy breeds. Expect annual routine maintenance and care expenses i"&amp;"n Ramanathapuram to range from ₹15,000 to ₹35,000, which covers high-quality puppy food, routine veterinary health checks, mandatory vaccinations, deworming, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Ramanathapuram, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Ramanathapuram, Coimbatore requires a tailored wellness routine suited to the warm climate and active urban environment near Trichy Road and Nanjundapuram Road. To keep your toy breed in optimal health, prioritize a nutrient-dense, high-protein diet specially formulated for small dogs, maintain continuous hydration, and keep indoor living spaces well-ventilated to prevent heat exhaustion. Daily care should focus on gentle indoor play, controlled short walks near quieter spots along Sungam Bypass, and consistent oral hygiene to protect against early dental issues common in toy breeds. Expect annual routine maintenance and care expenses in Ramanathapuram to range from ₹15,000 to ₹35,000, which covers high-quality puppy food, routine veterinary health checks, mandatory vaccinations, deworming, and periodic professional grooming.</v>
       </c>
       <c r="K31" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A31 &amp; "" in "" &amp; B31 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A31 &amp; "" in "" &amp; B31 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2868,11 +2890,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Ramanathapuram, Coimbatore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal regulations apply to owning a Chihuahua puppy in Ramanathapuram?&lt;/h3&gt;&lt;p&gt;Pet owners along Trichy Road and near Nanjundapuram Road must follow Coimbatore City Municipal Corporation rules, which mandate microchipping, yearly rabies vaccinations, and local licensing. Before purchasing, consider reviewing &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue networks&lt;/a&gt; to check adoption options.&lt;/p&gt;&lt;h3&gt;Where can I locate reliable nearby vet care for a toy breed in Ramanathapuram?&lt;/h3&gt;&lt;p&gt;Veterinary clinics around Sungam Bypass and Race Course offer comprehensive pediatric checks, dental maintenance, and vaccine schedules for small dogs. If you observe unethical breeding practices or mistreatment near local commercial belts, contact &lt;a href="https://www.petaindia.com"&gt;animal cruelty intervention organizations&lt;/a&gt; to file a official report.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for residential apartments in Ramanathapuram?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas adapt exceptionally well to modern apartment layouts near Puliakulam. Short indoor play sessions combined with brief evening walks along quieter residential lanes near Trichy Road fulfill their physical needs.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2887,21 +2909,21 @@
       <c r="F32" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="2" t="s">
         <v>252</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="2" t="s">
         <v>254</v>
       </c>
       <c r="J32" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A32 &amp; "" located in "" &amp; B32 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A32 &amp; "" Care Guide and Maintenance Costs in "" &amp; B32 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B32 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Saravanampatti, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Coimbatore's IT hub of Saravanampatti requires a balanced wellness routine suited to warm tropical weather and modern apartment enviro"&amp;"nments near Sathy Road and Keeranatham Road. Maintain optimal health by offering nutrient-dense toy-breed kibble high in protein, providing consistent indoor climate control to prevent heat exhaustion, and ensuring strict daily oral care to avoid early pe"&amp;"riodontal issues. Navigating busy tech corridors and residential complexes exposes small pets to ambient urban dust, heat stress, and seasonal parasites, making regular hydration, routine tick prevention, and gentle grooming essential. On average, annual "&amp;"maintenance costs in Saravanampatti range between ₹15,000 and ₹35,000, covering high-quality puppy nutrition, routine veterinary checkups, core vaccinations, deworming, and periodic grooming treatments.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A32 &amp; "" located in "" &amp; B32 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A32 &amp; "" Care Guide and Maintenance Costs in "" &amp; B32 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B32 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Saravanampatti, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Coimbatore's IT hub of Saravanampatti requires a balanced wellness routine suited to warm tropical weather and modern apartment enviro"&amp;"nments near Sathy Road and Keeranatham Road. Maintain optimal health by offering nutrient-dense toy-breed kibble high in protein, providing consistent indoor climate control to prevent heat exhaustion, and ensuring strict daily oral care to avoid early pe"&amp;"riodontal issues. Navigating busy tech corridors and residential complexes exposes small pets to ambient urban dust, heat stress, and seasonal parasites, making regular hydration, routine tick prevention, and gentle grooming essential. On average, annual "&amp;"maintenance costs in Saravanampatti range between ₹15,000 and ₹35,000, covering high-quality puppy nutrition, routine veterinary checkups, core vaccinations, deworming, and periodic grooming treatments.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Saravanampatti, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Coimbatore's IT hub of Saravanampatti requires a balanced wellness routine suited to warm tropical weather and modern apartment environments near Sathy Road and Keeranatham Road. Maintain optimal health by offering nutrient-dense toy-breed kibble high in protein, providing consistent indoor climate control to prevent heat exhaustion, and ensuring strict daily oral care to avoid early periodontal issues. Navigating busy tech corridors and residential complexes exposes small pets to ambient urban dust, heat stress, and seasonal parasites, making regular hydration, routine tick prevention, and gentle grooming essential. On average, annual maintenance costs in Saravanampatti range between ₹15,000 and ₹35,000, covering high-quality puppy nutrition, routine veterinary checkups, core vaccinations, deworming, and periodic grooming treatments.</v>
       </c>
       <c r="K32" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A32 &amp; "" in "" &amp; B32 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A32 &amp; "" in "" &amp; B32 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2911,11 +2933,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Saravanampatti, Coimbatore - FAQs&lt;/h2&gt;&lt;h3&gt;What local municipal rules and adoption guidelines apply to Chihuahua owners in Saravanampatti?&lt;/h3&gt;&lt;p&gt;Pet parents near Sathy Road and CHIL SEZ must comply with registration and mandatory rabies immunization standards established by the Coimbatore City Municipal Corporation. Prospective owners are encouraged to review local adoption guidelines or reach out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;pet rescue networks&lt;/a&gt; to support ethical rehoming before purchasing.&lt;/p&gt;&lt;h3&gt;Where can pet parents find specialized nearby vet care in Saravanampatti?&lt;/h3&gt;&lt;p&gt;Veterinary facilities along Keeranatham Road and near Prozone Mall provide health evaluations, vaccinations, and dental checkups tailored for toy breeds. If you suspect improper handling or cruelty at commercial kennels, contact &lt;a href="https://www.petaindia.com"&gt;animal rights advocates&lt;/a&gt; to submit a report.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for apartment living near Saravanampatti IT parks?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in modern high-rise apartments near Keeranatham Road and CHIL SEZ due to their small size. Regular indoor exercise combined with short, shaded morning walks around residential complexes keeps them active and well-balanced.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -2930,21 +2952,21 @@
       <c r="F33" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="2" t="s">
         <v>259</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="2" t="s">
         <v>261</v>
       </c>
       <c r="J33" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A33 &amp; "" located in "" &amp; B33 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A33 &amp; "" Care Guide and Maintenance Costs in "" &amp; B33 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B33 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Vadavalli, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the serene foothill environment of Vadavalli requires a dedicated wellness routine tailored to local conditions near Marudhamalai Road and "&amp;"Bharathiar University. To support long-term vitality, feed a balanced, nutrient-rich diet designed for mini breeds, maintain strict daily dental care to avoid periodontal issues, and schedule gentle exercise during the cooler morning hours. The proximity "&amp;"to the Western Ghats brings seasonal microclimate shifts, higher humidity, and ambient dust, making routine tick and flea prevention, regular coat grooming, and adequate indoor climate control essential. On average, annual maintenance costs in Vadavalli r"&amp;"ange between ₹15,000 and ₹35,000, covering high-quality kibble, routine veterinary checkups, core vaccinations, deworming, and periodic grooming treatments.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A33 &amp; "" located in "" &amp; B33 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A33 &amp; "" Care Guide and Maintenance Costs in "" &amp; B33 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B33 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Vadavalli, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the serene foothill environment of Vadavalli requires a dedicated wellness routine tailored to local conditions near Marudhamalai Road and "&amp;"Bharathiar University. To support long-term vitality, feed a balanced, nutrient-rich diet designed for mini breeds, maintain strict daily dental care to avoid periodontal issues, and schedule gentle exercise during the cooler morning hours. The proximity "&amp;"to the Western Ghats brings seasonal microclimate shifts, higher humidity, and ambient dust, making routine tick and flea prevention, regular coat grooming, and adequate indoor climate control essential. On average, annual maintenance costs in Vadavalli r"&amp;"ange between ₹15,000 and ₹35,000, covering high-quality kibble, routine veterinary checkups, core vaccinations, deworming, and periodic grooming treatments.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Vadavalli, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the serene foothill environment of Vadavalli requires a dedicated wellness routine tailored to local conditions near Marudhamalai Road and Bharathiar University. To support long-term vitality, feed a balanced, nutrient-rich diet designed for mini breeds, maintain strict daily dental care to avoid periodontal issues, and schedule gentle exercise during the cooler morning hours. The proximity to the Western Ghats brings seasonal microclimate shifts, higher humidity, and ambient dust, making routine tick and flea prevention, regular coat grooming, and adequate indoor climate control essential. On average, annual maintenance costs in Vadavalli range between ₹15,000 and ₹35,000, covering high-quality kibble, routine veterinary checkups, core vaccinations, deworming, and periodic grooming treatments.</v>
       </c>
       <c r="K33" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A33 &amp; "" in "" &amp; B33 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A33 &amp; "" in "" &amp; B33 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2954,11 +2976,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Vadavalli, Coimbatore - FAQs&lt;/h2&gt;&lt;h3&gt;What local municipal regulations and licensing apply to Chihuahua owners in Vadavalli?&lt;/h3&gt;&lt;p&gt;Pet owners near Marudhamalai Road and Maharani Avenue must register their dogs with the Coimbatore City Municipal Corporation and keep rabies immunizations current. Before purchasing a puppy, consider reviewing ethical breeding standards or reaching out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;animal rescue initiatives&lt;/a&gt; to explore pet adoption options.&lt;/p&gt;&lt;h3&gt;Where can I find specialized vet care for toy breeds around Vadavalli?&lt;/h3&gt;&lt;p&gt;Veterinary clinics located near the Vadavalli Bus Stand and Bharathiar University offer complete health checks, vaccinations, and dental care for small breeds. If you notice unethical breeding or pet neglect in the area, report it to &lt;a href="https://www.petaindia.com"&gt;animal rights protection groups&lt;/a&gt; for prompt investigation.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for the foothill climate of Vadavalli?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas adapt well to Vadavalli's environment near the Western Ghats foothills. However, due to seasonal humidity shifts, ensure your puppy stays hydrated, receives routine tick prevention, and enjoys comfortable indoor play during warm afternoons.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2973,21 +2995,21 @@
       <c r="F34" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="2" t="s">
         <v>266</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="2" t="s">
         <v>268</v>
       </c>
       <c r="J34" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A34 &amp; "" located in "" &amp; B34 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A34 &amp; "" Care Guide and Maintenance Costs in "" &amp; B34 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B34 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Ukkadam, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Ukkadam, Coimbatore requires a dedicated health and upkeep routine suited to high-density urban living. To maintain optimal vitality, provide"&amp;" nutrient-dense puppy kibble formulated for toy breeds, implement regular dental care to prevent periodontal issues, and ensure daily indoor exercise supplemented by short walks in quieter residential pockets near Valankulam Lake. Living near busy hubs li"&amp;"ke the Ukkadam Bus Terminus and Big Bazar Street exposes tiny pets to street dust, high humidity, and noise, making consistent climate control, parasite prevention, and routine coat grooming essential. On average, estimated annual maintenance costs in Ukk"&amp;"adam range from ₹15,000 to ₹35,000, covering high-quality nutrition, core vaccinations, deworming, veterinary wellness exams, and routine grooming care.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A34 &amp; "" located in "" &amp; B34 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A34 &amp; "" Care Guide and Maintenance Costs in "" &amp; B34 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B34 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Ukkadam, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Ukkadam, Coimbatore requires a dedicated health and upkeep routine suited to high-density urban living. To maintain optimal vitality, provide"&amp;" nutrient-dense puppy kibble formulated for toy breeds, implement regular dental care to prevent periodontal issues, and ensure daily indoor exercise supplemented by short walks in quieter residential pockets near Valankulam Lake. Living near busy hubs li"&amp;"ke the Ukkadam Bus Terminus and Big Bazar Street exposes tiny pets to street dust, high humidity, and noise, making consistent climate control, parasite prevention, and routine coat grooming essential. On average, estimated annual maintenance costs in Ukk"&amp;"adam range from ₹15,000 to ₹35,000, covering high-quality nutrition, core vaccinations, deworming, veterinary wellness exams, and routine grooming care.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Ukkadam, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in Ukkadam, Coimbatore requires a dedicated health and upkeep routine suited to high-density urban living. To maintain optimal vitality, provide nutrient-dense puppy kibble formulated for toy breeds, implement regular dental care to prevent periodontal issues, and ensure daily indoor exercise supplemented by short walks in quieter residential pockets near Valankulam Lake. Living near busy hubs like the Ukkadam Bus Terminus and Big Bazar Street exposes tiny pets to street dust, high humidity, and noise, making consistent climate control, parasite prevention, and routine coat grooming essential. On average, estimated annual maintenance costs in Ukkadam range from ₹15,000 to ₹35,000, covering high-quality nutrition, core vaccinations, deworming, veterinary wellness exams, and routine grooming care.</v>
       </c>
       <c r="K34" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A34 &amp; "" in "" &amp; B34 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A34 &amp; "" in "" &amp; B34 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -2997,11 +3019,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Ukkadam, Coimbatore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal regulations apply to buying a Chihuahua puppy in Ukkadam?&lt;/h3&gt;&lt;p&gt;Pet owners near Big Bazar Street and Sungam Bypass Road must adhere to Coimbatore City Municipal Corporation guidelines by securing valid pet licenses and maintaining updated rabies vaccination records. Before purchasing, consider exploring ethical pet acquisition practices or reaching out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue and adoption programs&lt;/a&gt; for alternative choices.&lt;/p&gt;&lt;h3&gt;Where can I find reliable nearby vet care for toy breeds in Ukkadam?&lt;/h3&gt;&lt;p&gt;Veterinary facilities around Ukkadam Bus Terminus and Town Hall provide routine check-ups, vaccinations, and dental care tailored for toy breeds. If you encounter mistreatment or unethical breeding facilities, report the violations to &lt;a href="https://www.petaindia.com"&gt;cruelty prevention organizations&lt;/a&gt; to safeguard animal rights.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for residential living near Valankulam Lake?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in compact urban apartments around Valankulam Lake. They require minimal space, but consistent indoor play combined with short daily walks away from busy traffic corridors keeps them active and healthy.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -3016,21 +3038,21 @@
       <c r="F35" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="2" t="s">
         <v>274</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="2" t="s">
         <v>276</v>
       </c>
       <c r="J35" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A35 &amp; "" located in "" &amp; B35 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A35 &amp; "" Care Guide and Maintenance Costs in "" &amp; B35 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B35 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kovaipudur, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the serene foothill environment of Kovaipudur, Coimbatore requires a well-structured wellness routine suited to its suburban setting and m"&amp;"ild local climate. To keep your toy breed in optimal health near Mahatma Gandhi Road and the Palakkad Main Road belt, prioritize high-protein nutrition formulated for small breeds, daily indoor play sessions, and strict oral hygiene to mitigate early dent"&amp;"al complications. Navigating the foothill breeze and local outdoor terrain near the Western Ghats requires consistent tick and flea prevention, regular coat grooming, and safeguarding small pups from evening chill or damp weather. On average, annual maint"&amp;"enance costs in Kovaipudur range between ₹15,000 and ₹35,000, covering premium toy-breed kibble, routine veterinary checkups, core vaccinations, deworming schedules, and periodic grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A35 &amp; "" located in "" &amp; B35 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A35 &amp; "" Care Guide and Maintenance Costs in "" &amp; B35 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B35 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kovaipudur, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the serene foothill environment of Kovaipudur, Coimbatore requires a well-structured wellness routine suited to its suburban setting and m"&amp;"ild local climate. To keep your toy breed in optimal health near Mahatma Gandhi Road and the Palakkad Main Road belt, prioritize high-protein nutrition formulated for small breeds, daily indoor play sessions, and strict oral hygiene to mitigate early dent"&amp;"al complications. Navigating the foothill breeze and local outdoor terrain near the Western Ghats requires consistent tick and flea prevention, regular coat grooming, and safeguarding small pups from evening chill or damp weather. On average, annual maint"&amp;"enance costs in Kovaipudur range between ₹15,000 and ₹35,000, covering premium toy-breed kibble, routine veterinary checkups, core vaccinations, deworming schedules, and periodic grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kovaipudur, Coimbatore&lt;/h2&gt;Caring for a Chihuahua puppy in the serene foothill environment of Kovaipudur, Coimbatore requires a well-structured wellness routine suited to its suburban setting and mild local climate. To keep your toy breed in optimal health near Mahatma Gandhi Road and the Palakkad Main Road belt, prioritize high-protein nutrition formulated for small breeds, daily indoor play sessions, and strict oral hygiene to mitigate early dental complications. Navigating the foothill breeze and local outdoor terrain near the Western Ghats requires consistent tick and flea prevention, regular coat grooming, and safeguarding small pups from evening chill or damp weather. On average, annual maintenance costs in Kovaipudur range between ₹15,000 and ₹35,000, covering premium toy-breed kibble, routine veterinary checkups, core vaccinations, deworming schedules, and periodic grooming services.</v>
       </c>
       <c r="K35" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A35 &amp; "" in "" &amp; B35 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A35 &amp; "" in "" &amp; B35 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3040,11 +3062,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Kovaipudur, Coimbatore - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal pet ownership rules and licensing apply in Kovaipudur?&lt;/h3&gt;&lt;p&gt;Pet parents residing near Mahatma Gandhi Road and Palakkad Main Road must comply with Coimbatore City Municipal Corporation guidelines by maintaining valid anti-rabies vaccination records and registering their dogs. Prospective owners are also encouraged to evaluate ethical adoption alternatives through &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; before bringing a new puppy home.&lt;/p&gt;&lt;h3&gt;Where can I find reliable nearby vet care for a toy breed in Kovaipudur?&lt;/h3&gt;&lt;p&gt;Veterinary clinics around Kovaipudur Junction and the Infant Jesus Shrine precinct offer comprehensive medical care, routine immunizations, and preventive health screenings tailored for delicate Chihuahua puppies. If you encounter unethical breeding operations or mistreatment in South-West Coimbatore, report the incident to &lt;a href="https://www.petaindia.com"&gt;cruelty prevention advocates&lt;/a&gt; for proper regulatory enforcement.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for the foothill climate of Kovaipudur?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas adapt exceptionally well to Kovaipudur’s breezy foothill environment. However, due to cooler evening winds coming off the Western Ghats, owners should keep small pups warm and ensure they have a comfortable indoor shelter protected from sudden drafts.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -3059,21 +3081,21 @@
       <c r="F36" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="2" t="s">
         <v>282</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="2" t="s">
         <v>284</v>
       </c>
       <c r="J36" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A36 &amp; "" located in "" &amp; B36 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A36 &amp; "" Care Guide and Maintenance Costs in "" &amp; B36 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B36 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Yercaud, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the cool hill-station climate of Yercaud requires a wellness strategy focused on thermal management, proper nutrition, and routine healthcare"&amp;". Due to the lower temperatures along the Shevaroy Hills and 32-km Loop Road, protecting these delicate toy companions from chill and damp conditions with warm clothing and cozy indoor housing is essential. Prioritize high-calorie, nutrient-dense kibble f"&amp;"ormulated for small breeds to maintain body heat, maintain strict dental hygiene to prevent early periodontitis, and schedule light walks around peaceful areas like Anna Park during warmer mid-day hours. On average, annual maintenance costs in Yercaud ran"&amp;"ge from ₹15,000 to ₹35,000, which covers quality puppy food, routine veterinary checkups, core vaccinations, deworming, and seasonal protective gear.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A36 &amp; "" located in "" &amp; B36 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A36 &amp; "" Care Guide and Maintenance Costs in "" &amp; B36 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B36 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Yercaud, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the cool hill-station climate of Yercaud requires a wellness strategy focused on thermal management, proper nutrition, and routine healthcare"&amp;". Due to the lower temperatures along the Shevaroy Hills and 32-km Loop Road, protecting these delicate toy companions from chill and damp conditions with warm clothing and cozy indoor housing is essential. Prioritize high-calorie, nutrient-dense kibble f"&amp;"ormulated for small breeds to maintain body heat, maintain strict dental hygiene to prevent early periodontitis, and schedule light walks around peaceful areas like Anna Park during warmer mid-day hours. On average, annual maintenance costs in Yercaud ran"&amp;"ge from ₹15,000 to ₹35,000, which covers quality puppy food, routine veterinary checkups, core vaccinations, deworming, and seasonal protective gear.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Yercaud, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the cool hill-station climate of Yercaud requires a wellness strategy focused on thermal management, proper nutrition, and routine healthcare. Due to the lower temperatures along the Shevaroy Hills and 32-km Loop Road, protecting these delicate toy companions from chill and damp conditions with warm clothing and cozy indoor housing is essential. Prioritize high-calorie, nutrient-dense kibble formulated for small breeds to maintain body heat, maintain strict dental hygiene to prevent early periodontitis, and schedule light walks around peaceful areas like Anna Park during warmer mid-day hours. On average, annual maintenance costs in Yercaud range from ₹15,000 to ₹35,000, which covers quality puppy food, routine veterinary checkups, core vaccinations, deworming, and seasonal protective gear.</v>
       </c>
       <c r="K36" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A36 &amp; "" in "" &amp; B36 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A36 &amp; "" in "" &amp; B36 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3083,11 +3105,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies for Sale in Yercaud, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal guidelines apply to keeping a Chihuahua puppy in Yercaud?&lt;/h3&gt;&lt;p&gt;Pet parents along the 32-km Loop Road and near Shevaroy Lake must adhere to Yercaud Town Panchayat regulations by maintaining valid rabies vaccination records and proper housing standards. Before purchasing, evaluate ethical sourcing standards or consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;regional animal welfare organizations&lt;/a&gt; to explore local adoption programs.&lt;/p&gt;&lt;h3&gt;How do I manage cold-weather care for Chihuahua puppies in the Shevaroy Hills?&lt;/h3&gt;&lt;p&gt;Due to cooler high-altitude climates near Lady's Seat road and Anna Park, toy breeds require thermal clothing, indoor heating, and high-calorie nutrition to prevent chills and hypoglycemia. If you observe unethical breeding or mistreatment under extreme weather conditions, contact &lt;a href="https://www.petaindia.com"&gt;cruelty prevention advocates&lt;/a&gt; to report concerns.&lt;/p&gt;&lt;h3&gt;Where can I access veterinary care for toy breeds in Yercaud?&lt;/h3&gt;&lt;p&gt;Primary health evaluations and essential immunizations are available through local veterinary units near Yercaud town center, while comprehensive emergency medical facilities can be accessed down the 20-hairpin Salem ghat road.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -3102,21 +3124,21 @@
       <c r="F37" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="2" t="s">
         <v>290</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="2" t="s">
         <v>292</v>
       </c>
       <c r="J37" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A37 &amp; "" located in "" &amp; B37 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A37 &amp; "" Care Guide and Maintenance Costs in "" &amp; B37 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B37 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kanyakumari, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the coastal environment of Kanyakumari requires a dedicated health routine tailored to warm weather and high atmospheric humidity. Due to"&amp;" salty ocean breeze and tropical heat near areas like Nagercoil Highway and Sunset View Point, keeping your toy breed properly hydrated, housed in well-ventilated spaces, and protected against skin moisture issues is essential. Provide nutrient-dense kibb"&amp;"le formulated specifically for small breeds to support their fast metabolism, along with regular dental cleaning and gentle daily indoor play. On average, annual maintenance costs in Kanyakumari range from ₹15,000 to ₹35,000, covering high-protein nutriti"&amp;"on, routine veterinary checkups, core vaccinations, tick prevention, and periodic grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A37 &amp; "" located in "" &amp; B37 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A37 &amp; "" Care Guide and Maintenance Costs in "" &amp; B37 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B37 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kanyakumari, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the coastal environment of Kanyakumari requires a dedicated health routine tailored to warm weather and high atmospheric humidity. Due to"&amp;" salty ocean breeze and tropical heat near areas like Nagercoil Highway and Sunset View Point, keeping your toy breed properly hydrated, housed in well-ventilated spaces, and protected against skin moisture issues is essential. Provide nutrient-dense kibb"&amp;"le formulated specifically for small breeds to support their fast metabolism, along with regular dental cleaning and gentle daily indoor play. On average, annual maintenance costs in Kanyakumari range from ₹15,000 to ₹35,000, covering high-protein nutriti"&amp;"on, routine veterinary checkups, core vaccinations, tick prevention, and periodic grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kanyakumari, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the coastal environment of Kanyakumari requires a dedicated health routine tailored to warm weather and high atmospheric humidity. Due to salty ocean breeze and tropical heat near areas like Nagercoil Highway and Sunset View Point, keeping your toy breed properly hydrated, housed in well-ventilated spaces, and protected against skin moisture issues is essential. Provide nutrient-dense kibble formulated specifically for small breeds to support their fast metabolism, along with regular dental cleaning and gentle daily indoor play. On average, annual maintenance costs in Kanyakumari range from ₹15,000 to ₹35,000, covering high-protein nutrition, routine veterinary checkups, core vaccinations, tick prevention, and periodic grooming.</v>
       </c>
       <c r="K37" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A37 &amp; "" in "" &amp; B37 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A37 &amp; "" in "" &amp; B37 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3126,11 +3148,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Kanyakumari, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal regulations and legal requirements apply to owning a Chihuahua puppy in Kanyakumari?&lt;/h3&gt;&lt;p&gt;Pet parents residing near Nagercoil Highway and the NH 66 corridor must comply with coastal municipal body rules by keeping compulsory anti-rabies vaccination certifications updated. To support ethical pet care standards or discover rescue alternatives, connect with &lt;a href="https://www.peopleforanimalsindia.org"&gt;pet adoption organizations&lt;/a&gt; across Tamil Nadu.&lt;/p&gt;&lt;h3&gt;Where can I find reliable veterinary care for toy breed puppies in Kanyakumari?&lt;/h3&gt;&lt;p&gt;Veterinary services around Nagercoil Highway and central Kanyakumari provide routine immunization schedules, patellar screenings, and treatments for humidity-related skin sensitivities. If you witness unethical breeding practices or animal abuse near high-density tourist areas, contact &lt;a href="https://www.petaindia.com"&gt;animal protection representatives&lt;/a&gt; immediately.&lt;/p&gt;&lt;h3&gt;How do I protect a Chihuahua puppy from Kanyakumari's coastal climate?&lt;/h3&gt;&lt;p&gt;Due to high humidity and salty ocean breezes near Vivekananda Rock Memorial and Sunset View Point, ensure your puppy stays well-hydrated and housed in well-ventilated indoor environments to avoid heat exhaustion and skin irritation.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -3145,21 +3167,21 @@
       <c r="F38" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="2" t="s">
         <v>297</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J38" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A38 &amp; "" located in "" &amp; B38 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A38 &amp; "" Care Guide and Maintenance Costs in "" &amp; B38 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B38 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Pondicherry&lt;/h2&gt;Caring for a Chihuahua puppy in coastal Pondicherry requires a dedicated wellness routine adapted to warm, humid seaside conditions. To maintain long-term vitality, provide nutrient"&amp;"-dense puppy food formulated for toy breeds, ensure continuous hydration, and schedule short walks along quieter stretches of White Town, Lawspet, or Heritage Town during cooler early morning or evening hours. High humidity and salty coastal breeze near P"&amp;"romenade Beach make regular coat maintenance, skin checks for moisture-induced irritation, and proactive tick prevention essential. Indoors, ensure adequate climate control to protect your small companion from tropical heat stress. On average, annual main"&amp;"tenance costs in Pondicherry range from ₹15,000 to ₹35,000, which includes high-quality kibble, routine veterinary wellness checks, essential vaccinations, deworming, and periodic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A38 &amp; "" located in "" &amp; B38 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A38 &amp; "" Care Guide and Maintenance Costs in "" &amp; B38 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B38 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Pondicherry&lt;/h2&gt;Caring for a Chihuahua puppy in coastal Pondicherry requires a dedicated wellness routine adapted to warm, humid seaside conditions. To maintain long-term vitality, provide nutrient"&amp;"-dense puppy food formulated for toy breeds, ensure continuous hydration, and schedule short walks along quieter stretches of White Town, Lawspet, or Heritage Town during cooler early morning or evening hours. High humidity and salty coastal breeze near P"&amp;"romenade Beach make regular coat maintenance, skin checks for moisture-induced irritation, and proactive tick prevention essential. Indoors, ensure adequate climate control to protect your small companion from tropical heat stress. On average, annual main"&amp;"tenance costs in Pondicherry range from ₹15,000 to ₹35,000, which includes high-quality kibble, routine veterinary wellness checks, essential vaccinations, deworming, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Pondicherry&lt;/h2&gt;Caring for a Chihuahua puppy in coastal Pondicherry requires a dedicated wellness routine adapted to warm, humid seaside conditions. To maintain long-term vitality, provide nutrient-dense puppy food formulated for toy breeds, ensure continuous hydration, and schedule short walks along quieter stretches of White Town, Lawspet, or Heritage Town during cooler early morning or evening hours. High humidity and salty coastal breeze near Promenade Beach make regular coat maintenance, skin checks for moisture-induced irritation, and proactive tick prevention essential. Indoors, ensure adequate climate control to protect your small companion from tropical heat stress. On average, annual maintenance costs in Pondicherry range from ₹15,000 to ₹35,000, which includes high-quality kibble, routine veterinary wellness checks, essential vaccinations, deworming, and periodic professional grooming.</v>
       </c>
       <c r="K38" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A38 &amp; "" in "" &amp; B38 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A38 &amp; "" in "" &amp; B38 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3169,11 +3191,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Pondicherry - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal regulations and animal welfare laws govern dog owners in Pondicherry?&lt;/h3&gt;&lt;p&gt;Pet owners across White Town and Lawspet must comply with Puducherry Municipality rules, ensuring mandatory rabies vaccinations and proper pet identification. Prior to buying a puppy, prospective parents are encouraged to check &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue initiatives&lt;/a&gt; for rescue and adoption opportunities.&lt;/p&gt;&lt;h3&gt;Where can I find nearby vet care for toy breeds in Pondicherry?&lt;/h3&gt;&lt;p&gt;Veterinary facilities located near Heritage Town and along Goubert Avenue provide specialized care for small breeds, including vaccinations, routine health checks, and dietary management. If you notice backyard breeding abuses or pet neglect along the ECR corridor, contact &lt;a href="https://www.petaindia.com"&gt;animal rights advocates&lt;/a&gt; to file an official report.&lt;/p&gt;&lt;h3&gt;How well do Chihuahua puppies adapt to humid coastal environments like Pondicherry?&lt;/h3&gt;&lt;p&gt;Chihuahuas handle apartment living near Promenade Beach exceptionally well due to their compact size, but they require protection from heat and humidity. Maintain a cool indoor environment during warm afternoons and arrange brief walks along White Town's shaded streets during early mornings or late evenings.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -3188,21 +3210,21 @@
       <c r="F39" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="2" t="s">
         <v>305</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="2" t="s">
         <v>307</v>
       </c>
       <c r="J39" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A39 &amp; "" located in "" &amp; B39 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A39 &amp; "" Care Guide and Maintenance Costs in "" &amp; B39 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B39 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kochi, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Kochi's coastal climate requires a dedicated wellness routine tailored to high humidity and humid tropical conditions near areas like Panampilly Na"&amp;"gar, Kakkanad, and Marine Drive. To support long-term health, provide high-protein nutrition formulated for toy breeds, prioritize daily indoor mental stimulation alongside brief walks, and maintain strict oral hygiene to avoid early periodontal issues. K"&amp;"ochi's coastal moisture and heavy monsoon showers expose small dogs to fungal skin irritation, dampness, and heat stress, making consistent indoor climate control, thorough coat drying, and regular parasite prevention essential. On average, annual mainten"&amp;"ance costs in Kochi range between ₹15,000 and ₹35,000, which covers high-quality puppy food, routine veterinary consultations, core vaccinations, deworming, and basic grooming supplies.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A39 &amp; "" located in "" &amp; B39 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A39 &amp; "" Care Guide and Maintenance Costs in "" &amp; B39 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B39 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kochi, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Kochi's coastal climate requires a dedicated wellness routine tailored to high humidity and humid tropical conditions near areas like Panampilly Na"&amp;"gar, Kakkanad, and Marine Drive. To support long-term health, provide high-protein nutrition formulated for toy breeds, prioritize daily indoor mental stimulation alongside brief walks, and maintain strict oral hygiene to avoid early periodontal issues. K"&amp;"ochi's coastal moisture and heavy monsoon showers expose small dogs to fungal skin irritation, dampness, and heat stress, making consistent indoor climate control, thorough coat drying, and regular parasite prevention essential. On average, annual mainten"&amp;"ance costs in Kochi range between ₹15,000 and ₹35,000, which covers high-quality puppy food, routine veterinary consultations, core vaccinations, deworming, and basic grooming supplies.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Kochi, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Kochi's coastal climate requires a dedicated wellness routine tailored to high humidity and humid tropical conditions near areas like Panampilly Nagar, Kakkanad, and Marine Drive. To support long-term health, provide high-protein nutrition formulated for toy breeds, prioritize daily indoor mental stimulation alongside brief walks, and maintain strict oral hygiene to avoid early periodontal issues. Kochi's coastal moisture and heavy monsoon showers expose small dogs to fungal skin irritation, dampness, and heat stress, making consistent indoor climate control, thorough coat drying, and regular parasite prevention essential. On average, annual maintenance costs in Kochi range between ₹15,000 and ₹35,000, which covers high-quality puppy food, routine veterinary consultations, core vaccinations, deworming, and basic grooming supplies.</v>
       </c>
       <c r="K39" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A39 &amp; "" in "" &amp; B39 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A39 &amp; "" in "" &amp; B39 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3212,11 +3234,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Kochi, Kerala - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal rules apply when bringing home a Chihuahua puppy in Kochi?&lt;/h3&gt;&lt;p&gt;Pet parents in areas like Panampilly Nagar and Kakkanad must register their dogs with the Kochi Municipal Corporation, maintain active anti-rabies vaccination records, and adhere to state pet ownership norms. To support ethical pet ownership, consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue and shelter organisations&lt;/a&gt; to explore rescue options before purchasing.&lt;/p&gt;&lt;h3&gt;How do I find local veterinary care and manage high humidity for Chihuahuas in Kochi?&lt;/h3&gt;&lt;p&gt;Veterinary facilities around Edappally, MG Road, and Marine Drive provide specialized health checks, vaccinations, and skin care treatments necessary for high-humidity coastal climates. If you witness illegal breeding setups or neglected animals, notify &lt;a href="https://www.petaindia.com"&gt;animal rights advocates&lt;/a&gt; to file an official report.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies well-suited for high-rise apartment living in Kochi?&lt;/h3&gt;&lt;p&gt;Yes, toy breeds like Chihuahuas thrive in apartment settings common across Vyttila and Marine Drive. Indoor playtime supplemented by brief early morning or evening walks helps avoid heat stress while fulfilling their daily activity needs.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -3231,21 +3253,21 @@
       <c r="F40" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="2" t="s">
         <v>313</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="2" t="s">
         <v>315</v>
       </c>
       <c r="J40" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A40 &amp; "" located in "" &amp; B40 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A40 &amp; "" Care Guide and Maintenance Costs in "" &amp; B40 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B40 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Trivandrum, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Trivandrum requires a well-balanced wellness routine tailored to South Kerala's warm, humid coastal climate. To keep your toy breed thriving a"&amp;"round residential hubs like Kowdiar, Pattom, and PMG Junction, prioritize nutrient-dense food formulated for small breeds, maintain constant hydration to prevent heat exhaustion, and schedule gentle exercise during cooler morning or evening hours near Mus"&amp;"eum Road. High coastal humidity in Thiruvananthapuram increases susceptibility to skin allergies, tick infestations, and dental issues, making regular grooming, oral hygiene, and proactive parasite control essential. On average, annual maintenance costs i"&amp;"n Trivandrum range between ₹15,000 and ₹35,000, covering high-protein puppy kibble, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A40 &amp; "" located in "" &amp; B40 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A40 &amp; "" Care Guide and Maintenance Costs in "" &amp; B40 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B40 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Trivandrum, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Trivandrum requires a well-balanced wellness routine tailored to South Kerala's warm, humid coastal climate. To keep your toy breed thriving a"&amp;"round residential hubs like Kowdiar, Pattom, and PMG Junction, prioritize nutrient-dense food formulated for small breeds, maintain constant hydration to prevent heat exhaustion, and schedule gentle exercise during cooler morning or evening hours near Mus"&amp;"eum Road. High coastal humidity in Thiruvananthapuram increases susceptibility to skin allergies, tick infestations, and dental issues, making regular grooming, oral hygiene, and proactive parasite control essential. On average, annual maintenance costs i"&amp;"n Trivandrum range between ₹15,000 and ₹35,000, covering high-protein puppy kibble, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Trivandrum, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Trivandrum requires a well-balanced wellness routine tailored to South Kerala's warm, humid coastal climate. To keep your toy breed thriving around residential hubs like Kowdiar, Pattom, and PMG Junction, prioritize nutrient-dense food formulated for small breeds, maintain constant hydration to prevent heat exhaustion, and schedule gentle exercise during cooler morning or evening hours near Museum Road. High coastal humidity in Thiruvananthapuram increases susceptibility to skin allergies, tick infestations, and dental issues, making regular grooming, oral hygiene, and proactive parasite control essential. On average, annual maintenance costs in Trivandrum range between ₹15,000 and ₹35,000, covering high-protein puppy kibble, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.</v>
       </c>
       <c r="K40" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A40 &amp; "" in "" &amp; B40 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A40 &amp; "" in "" &amp; B40 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3255,11 +3277,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Trivandrum, Kerala - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal rules and registration requirements apply to Chihuahua owners in Trivandrum?&lt;/h3&gt;&lt;p&gt;Pet owners across Kowdiar, Pattom, and PMG Junction must comply with Thiruvananthapuram Municipal Corporation guidelines by maintaining valid anti-rabies vaccination records and proper licensing. Prospective pet parents are also encouraged to consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue and adoption shelters&lt;/a&gt; to consider adoption options.&lt;/p&gt;&lt;h3&gt;Where can I access veterinary services for toy breeds near central Trivandrum?&lt;/h3&gt;&lt;p&gt;Veterinary centers located near Kowdiar Avenue, Pattom, and the Secretariat corridor provide comprehensive health checkups, core vaccinations, and heat-management advice for toy breeds. If you witness illegal breeding or animal abuse, report the violation through &lt;a href="https://www.petaindia.com"&gt;animal rights monitoring groups&lt;/a&gt;.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies well-suited for apartment living in Trivandrum?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in compact urban apartments in Thiruvananthapuram. Providing indoor play alongside short walks near Museum Road during cooler morning or evening hours ensures proper exercise while avoiding coastal heat exhaustion.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -3274,21 +3296,21 @@
       <c r="F41" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="2" t="s">
         <v>321</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="2" t="s">
         <v>323</v>
       </c>
       <c r="J41" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A41 &amp; "" located in "" &amp; B41 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A41 &amp; "" Care Guide and Maintenance Costs in "" &amp; B41 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B41 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Vellore, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Vellore requires a dedicated health and maintenance routine tailored to handle the region's warm inland climate across neighborhoods like Gan"&amp;"dhi Nagar, Sathuvachari, and Katpadi. To keep your toy breed thriving, prioritize a nutrient-rich diet designed for mini breeds, ensure continuous hydration to prevent heat stress, and maintain strict daily oral hygiene to safeguard against early dental i"&amp;"ssues. Navigating urban residential zones and transit corridors near Katpadi Junction exposes delicate pups to high afternoon temperatures, making climate-controlled indoor spaces and early morning walks essential. On average, annual care and maintenance "&amp;"costs in Vellore range from ₹15,000 to ₹35,000, which covers premium small-breed kibble, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A41 &amp; "" located in "" &amp; B41 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A41 &amp; "" Care Guide and Maintenance Costs in "" &amp; B41 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B41 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Vellore, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Vellore requires a dedicated health and maintenance routine tailored to handle the region's warm inland climate across neighborhoods like Gan"&amp;"dhi Nagar, Sathuvachari, and Katpadi. To keep your toy breed thriving, prioritize a nutrient-rich diet designed for mini breeds, ensure continuous hydration to prevent heat stress, and maintain strict daily oral hygiene to safeguard against early dental i"&amp;"ssues. Navigating urban residential zones and transit corridors near Katpadi Junction exposes delicate pups to high afternoon temperatures, making climate-controlled indoor spaces and early morning walks essential. On average, annual care and maintenance "&amp;"costs in Vellore range from ₹15,000 to ₹35,000, which covers premium small-breed kibble, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Vellore, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Vellore requires a dedicated health and maintenance routine tailored to handle the region's warm inland climate across neighborhoods like Gandhi Nagar, Sathuvachari, and Katpadi. To keep your toy breed thriving, prioritize a nutrient-rich diet designed for mini breeds, ensure continuous hydration to prevent heat stress, and maintain strict daily oral hygiene to safeguard against early dental issues. Navigating urban residential zones and transit corridors near Katpadi Junction exposes delicate pups to high afternoon temperatures, making climate-controlled indoor spaces and early morning walks essential. On average, annual care and maintenance costs in Vellore range from ₹15,000 to ₹35,000, which covers premium small-breed kibble, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.</v>
       </c>
       <c r="K41" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A41 &amp; "" in "" &amp; B41 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A41 &amp; "" in "" &amp; B41 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3298,11 +3320,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Vellore, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal regulations and local adoption guidelines apply when getting a Chihuahua puppy in Vellore?&lt;/h3&gt;&lt;p&gt;Pet owners around Gandhi Nagar, Sathuvachari, and Katpadi must register their dogs with the Vellore City Municipal Corporation and keep anti-rabies immunizations current. If you prefer adoptions over commercial buying, consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;paws and rescue foundations&lt;/a&gt; for local rehoming options.&lt;/p&gt;&lt;h3&gt;Where can I locate reliable veterinary care for small breeds in Vellore?&lt;/h3&gt;&lt;p&gt;Veterinary clinics near Katpadi Junction and Vellore Fort offer specialized wellness checks, vaccinations, and dental care for toy breeds. To report unethical breeding practices or mistreatment in the area, reach out to &lt;a href="https://www.petaindia.com"&gt;cruelty prevention advocates&lt;/a&gt; to take appropriate action.&lt;/p&gt;&lt;h3&gt;How do Chihuahua puppies adjust to Vellore's warm inland climate?&lt;/h3&gt;&lt;p&gt;Chihuahuas handle indoor apartment living very well, but high temperatures near Katpadi require climate-controlled spaces and plenty of hydration. Walking your puppy during cooler early morning hours in quiet residential pockets prevents heat exhaustion.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -3317,21 +3339,21 @@
       <c r="F42" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="2" t="s">
         <v>329</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" s="2" t="s">
         <v>331</v>
       </c>
       <c r="J42" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A42 &amp; "" located in "" &amp; B42 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A42 &amp; "" Care Guide and Maintenance Costs in "" &amp; B42 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B42 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Calicut, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Calicut demands an attentive health and maintenance regimen adapted to the warm, humid coastal climate of the Malabar region. To maintain optimum"&amp;" physical vitality near areas like Mavoor Road and Beach Road, prioritize nutrient-dense kibble formulated for toy breeds, constant hydration, and daily oral hygiene to guard against periodontal conditions. High humidity and elevated temperatures make vig"&amp;"ilant flea and tick prevention, coat maintenance, and well-ventilated indoor living essential for delicate toy puppies. On average, annual care and maintenance costs across Kozhikode range between ₹15,000 and ₹35,000, covering high-grade puppy nutrition, "&amp;"routine veterinary evaluations, core vaccinations, regular deworming, and basic professional grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A42 &amp; "" located in "" &amp; B42 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A42 &amp; "" Care Guide and Maintenance Costs in "" &amp; B42 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B42 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Calicut, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Calicut demands an attentive health and maintenance regimen adapted to the warm, humid coastal climate of the Malabar region. To maintain optimum"&amp;" physical vitality near areas like Mavoor Road and Beach Road, prioritize nutrient-dense kibble formulated for toy breeds, constant hydration, and daily oral hygiene to guard against periodontal conditions. High humidity and elevated temperatures make vig"&amp;"ilant flea and tick prevention, coat maintenance, and well-ventilated indoor living essential for delicate toy puppies. On average, annual care and maintenance costs across Kozhikode range between ₹15,000 and ₹35,000, covering high-grade puppy nutrition, "&amp;"routine veterinary evaluations, core vaccinations, regular deworming, and basic professional grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Calicut, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Calicut demands an attentive health and maintenance regimen adapted to the warm, humid coastal climate of the Malabar region. To maintain optimum physical vitality near areas like Mavoor Road and Beach Road, prioritize nutrient-dense kibble formulated for toy breeds, constant hydration, and daily oral hygiene to guard against periodontal conditions. High humidity and elevated temperatures make vigilant flea and tick prevention, coat maintenance, and well-ventilated indoor living essential for delicate toy puppies. On average, annual care and maintenance costs across Kozhikode range between ₹15,000 and ₹35,000, covering high-grade puppy nutrition, routine veterinary evaluations, core vaccinations, regular deworming, and basic professional grooming services.</v>
       </c>
       <c r="K42" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A42 &amp; "" in "" &amp; B42 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A42 &amp; "" in "" &amp; B42 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3341,11 +3363,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Calicut, Kerala - FAQs&lt;/h2&gt;&lt;h3&gt;What Kozhikode Corporation regulations apply when getting a Chihuahua puppy in Calicut?&lt;/h3&gt;&lt;p&gt;Pet parents around Mavoor Road and Focus Mall must comply with Kozhikode Corporation registration norms, maintain up-to-date rabies immunizations, and adhere to state animal care rules. Before purchasing a pup, consider checking &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue networks&lt;/a&gt; for ethical adoption options across Malabar.&lt;/p&gt;&lt;h3&gt;Where can I find reliable veterinary care for toy breeds in Kozhikode?&lt;/h3&gt;&lt;p&gt;Veterinary clinics operating near Beach Road and Kozhikode Railway Station offer specialized wellness checks, vaccinations, and climate care advice for toy dogs. To report illegal breeding practices or animal abuse around Kozhikode Bypass, contact &lt;a href="https://www.petaindia.com"&gt;cruelty prevention organizations&lt;/a&gt; to submit a formal report.&lt;/p&gt;&lt;h3&gt;How well do Chihuahua puppies adapt to the coastal climate in Calicut?&lt;/h3&gt;&lt;p&gt;Chihuahuas adapt well to indoor apartment living near areas like Mananchira Square, but require well-ventilated spaces, constant hydration, and routine grooming to comfortably handle Kozhikode's warm, high-humidity weather.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -3360,21 +3382,21 @@
       <c r="F43" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="2" t="s">
         <v>337</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="I43" s="2" t="s">
         <v>339</v>
       </c>
       <c r="J43" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A43 &amp; "" located in "" &amp; B43 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A43 &amp; "" Care Guide and Maintenance Costs in "" &amp; B43 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B43 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Nagercoil, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Nagercoil requires a wellness routine adapted to southern Tamil Nadu's humid coastal climate and warm weather conditions. To support your t"&amp;"oy breed's long-term health around neighborhoods like Vadasery, Kottar, and Chidambara Nagar, provide nutrient-dense small-kibble nutrition, ensure continuous access to fresh water to mitigate heat stress, and establish daily oral hygiene to safeguard aga"&amp;"inst early periodontal disease. Navigating local coastal humidity and dusty urban corridors along MS Road makes routine flea and tick prevention, coat maintenance, and keeping walks restricted to cooler morning or evening hours essential. On average, annu"&amp;"al care and maintenance costs in Nagercoil range between ₹15,000 and ₹35,000, which encompasses high-quality puppy food, routine veterinary checkups, core vaccinations, parasite treatments, and basic grooming essentials.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A43 &amp; "" located in "" &amp; B43 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A43 &amp; "" Care Guide and Maintenance Costs in "" &amp; B43 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B43 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Nagercoil, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Nagercoil requires a wellness routine adapted to southern Tamil Nadu's humid coastal climate and warm weather conditions. To support your t"&amp;"oy breed's long-term health around neighborhoods like Vadasery, Kottar, and Chidambara Nagar, provide nutrient-dense small-kibble nutrition, ensure continuous access to fresh water to mitigate heat stress, and establish daily oral hygiene to safeguard aga"&amp;"inst early periodontal disease. Navigating local coastal humidity and dusty urban corridors along MS Road makes routine flea and tick prevention, coat maintenance, and keeping walks restricted to cooler morning or evening hours essential. On average, annu"&amp;"al care and maintenance costs in Nagercoil range between ₹15,000 and ₹35,000, which encompasses high-quality puppy food, routine veterinary checkups, core vaccinations, parasite treatments, and basic grooming essentials.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Nagercoil, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in Nagercoil requires a wellness routine adapted to southern Tamil Nadu's humid coastal climate and warm weather conditions. To support your toy breed's long-term health around neighborhoods like Vadasery, Kottar, and Chidambara Nagar, provide nutrient-dense small-kibble nutrition, ensure continuous access to fresh water to mitigate heat stress, and establish daily oral hygiene to safeguard against early periodontal disease. Navigating local coastal humidity and dusty urban corridors along MS Road makes routine flea and tick prevention, coat maintenance, and keeping walks restricted to cooler morning or evening hours essential. On average, annual care and maintenance costs in Nagercoil range between ₹15,000 and ₹35,000, which encompasses high-quality puppy food, routine veterinary checkups, core vaccinations, parasite treatments, and basic grooming essentials.</v>
       </c>
       <c r="K43" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A43 &amp; "" in "" &amp; B43 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A43 &amp; "" in "" &amp; B43 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3384,11 +3406,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Nagercoil, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What local municipal rules apply to Chihuahua puppy owners in Nagercoil?&lt;/h3&gt;&lt;p&gt;Pet parents around Vadasery and Kottar must adhere to Nagercoil Municipal Corporation guidelines, including mandatory rabies immunizations and microchipping. Prospective owners are encouraged to review &lt;a href="https://www.peopleforanimalsindia.org"&gt;local adoption guidelines&lt;/a&gt; or connect with rescue groups prior to purchasing.&lt;/p&gt;&lt;h3&gt;Where can I find reliable nearby vet care for toy breeds in Nagercoil?&lt;/h3&gt;&lt;p&gt;Veterinary clinics along MS Road and near the Vadasery Bus Stand offer specialized health checks, vaccinations, and climate care for small dogs. If you encounter unethical breeding practices or animal abuse in the Kanyakumari district, contact &lt;a href="https://www.petaindia.com"&gt;animal rights advocacy organisations&lt;/a&gt; immediately.&lt;/p&gt;&lt;h3&gt;How do Chihuahua puppies adjust to Nagercoil's coastal weather conditions?&lt;/h3&gt;&lt;p&gt;Chihuahuas thrive in homes around Chidambara Nagar and Ramanpudur when provided with adequate cooling, continuous hydration, and scheduled outdoor walks during cooler morning or evening hours to avoid heat stress.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -3403,21 +3425,21 @@
       <c r="F44" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="2" t="s">
         <v>345</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I44" s="2" t="s">
         <v>347</v>
       </c>
       <c r="J44" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A44 &amp; "" located in "" &amp; B44 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A44 &amp; "" Care Guide and Maintenance Costs in "" &amp; B44 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B44 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Neyveli, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the peaceful township of Neyveli requires a dedicated health routine adapted to the region's warm industrial climate and residential layout. "&amp;"To maintain optimal vitality, provide nutrient-rich puppy food specifically formulated for toy breeds, ensure continuous access to fresh water to avoid heat exhaustion, and practice daily dental care to guard against periodontal disease. Exercising your p"&amp;"uppy around quiet township sectors near Block 1 through Block 30 or Mandarakuppam should be kept to cooler early morning or evening hours to protect sensitive paws from hot asphalt. On average, annual maintenance costs in Neyveli range from ₹15,000 to ₹35"&amp;",000, which accounts for premium diet kibble, routine veterinary checkups, mandatory vaccinations, parasite preventatives, and essential grooming care.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A44 &amp; "" located in "" &amp; B44 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A44 &amp; "" Care Guide and Maintenance Costs in "" &amp; B44 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B44 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Neyveli, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the peaceful township of Neyveli requires a dedicated health routine adapted to the region's warm industrial climate and residential layout. "&amp;"To maintain optimal vitality, provide nutrient-rich puppy food specifically formulated for toy breeds, ensure continuous access to fresh water to avoid heat exhaustion, and practice daily dental care to guard against periodontal disease. Exercising your p"&amp;"uppy around quiet township sectors near Block 1 through Block 30 or Mandarakuppam should be kept to cooler early morning or evening hours to protect sensitive paws from hot asphalt. On average, annual maintenance costs in Neyveli range from ₹15,000 to ₹35"&amp;",000, which accounts for premium diet kibble, routine veterinary checkups, mandatory vaccinations, parasite preventatives, and essential grooming care.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Neyveli, Tamil Nadu&lt;/h2&gt;Caring for a Chihuahua puppy in the peaceful township of Neyveli requires a dedicated health routine adapted to the region's warm industrial climate and residential layout. To maintain optimal vitality, provide nutrient-rich puppy food specifically formulated for toy breeds, ensure continuous access to fresh water to avoid heat exhaustion, and practice daily dental care to guard against periodontal disease. Exercising your puppy around quiet township sectors near Block 1 through Block 30 or Mandarakuppam should be kept to cooler early morning or evening hours to protect sensitive paws from hot asphalt. On average, annual maintenance costs in Neyveli range from ₹15,000 to ₹35,000, which accounts for premium diet kibble, routine veterinary checkups, mandatory vaccinations, parasite preventatives, and essential grooming care.</v>
       </c>
       <c r="K44" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A44 &amp; "" in "" &amp; B44 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A44 &amp; "" in "" &amp; B44 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3427,11 +3449,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Neyveli, Tamil Nadu - FAQs&lt;/h2&gt;&lt;h3&gt;What municipal regulations and animal welfare guidelines apply to Chihuahua puppies in Neyveli?&lt;/h3&gt;&lt;p&gt;Pet owners residing across Block 1 to Block 30 or near Mandarakuppam must comply with NLC township sanitation standards and mandatory anti-rabies vaccination rules. Before purchasing, review ethical breeding practices or connect with &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; to explore adoption options.&lt;/p&gt;&lt;h3&gt;Where can I find veterinary care for toy breeds in Neyveli?&lt;/h3&gt;&lt;p&gt;Veterinary clinics situated around the NLC Arch Gate and Gandhi Nagar provide routine health evaluations, immunizations, and heat-stress management for small breeds. If you observe illegal breeding operations or neglect near Four Road, notify &lt;a href="https://www.petaindia.com"&gt;animal rights protection groups&lt;/a&gt; to report the offense.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies well-suited for township living in Neyveli?&lt;/h3&gt;&lt;p&gt;Yes, their compact size makes them ideal for indoor residential quarters across the township. Due to the warm local climate, keep your puppy in well-ventilated spaces and plan short walks along quieter lanes in Mandarakuppam during cooler hours.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -3446,21 +3468,21 @@
       <c r="F45" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="2" t="s">
         <v>353</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="2" t="s">
         <v>355</v>
       </c>
       <c r="J45" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A45 &amp; "" located in "" &amp; B45 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A45 &amp; "" Care Guide and Maintenance Costs in "" &amp; B45 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B45 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Munnar, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in the cold, high-altitude climate of Munnar requires a dedicated wellness routine focused on thermal protection and proper nutrition. Given the chil"&amp;"ly mountain air around Old Munnar and Mattupetty Road, keeping your toy breed equipped with insulated fleece sweaters, warm bedding, and climate-controlled indoor shelter is essential to prevent hypothermia and cold-induced hypoglycemia. A nutrient-rich, "&amp;"high-protein diet tailored for small breeds helps maintain their fast metabolism, while regular indoor play and short walks near the Tea Museum keep them active without overexposure to damp weather. On average, annual maintenance costs in Munnar range bet"&amp;"ween ₹15,000 and ₹35,000, covering high-quality puppy kibble, routine veterinary checkups, core vaccinations, deworming, and essential cold-weather apparel.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A45 &amp; "" located in "" &amp; B45 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A45 &amp; "" Care Guide and Maintenance Costs in "" &amp; B45 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B45 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Munnar, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in the cold, high-altitude climate of Munnar requires a dedicated wellness routine focused on thermal protection and proper nutrition. Given the chil"&amp;"ly mountain air around Old Munnar and Mattupetty Road, keeping your toy breed equipped with insulated fleece sweaters, warm bedding, and climate-controlled indoor shelter is essential to prevent hypothermia and cold-induced hypoglycemia. A nutrient-rich, "&amp;"high-protein diet tailored for small breeds helps maintain their fast metabolism, while regular indoor play and short walks near the Tea Museum keep them active without overexposure to damp weather. On average, annual maintenance costs in Munnar range bet"&amp;"ween ₹15,000 and ₹35,000, covering high-quality puppy kibble, routine veterinary checkups, core vaccinations, deworming, and essential cold-weather apparel.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Munnar, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in the cold, high-altitude climate of Munnar requires a dedicated wellness routine focused on thermal protection and proper nutrition. Given the chilly mountain air around Old Munnar and Mattupetty Road, keeping your toy breed equipped with insulated fleece sweaters, warm bedding, and climate-controlled indoor shelter is essential to prevent hypothermia and cold-induced hypoglycemia. A nutrient-rich, high-protein diet tailored for small breeds helps maintain their fast metabolism, while regular indoor play and short walks near the Tea Museum keep them active without overexposure to damp weather. On average, annual maintenance costs in Munnar range between ₹15,000 and ₹35,000, covering high-quality puppy kibble, routine veterinary checkups, core vaccinations, deworming, and essential cold-weather apparel.</v>
       </c>
       <c r="K45" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A45 &amp; "" in "" &amp; B45 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A45 &amp; "" in "" &amp; B45 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3470,11 +3492,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Munnar, Kerala - FAQs&lt;/h2&gt;&lt;h3&gt;What local animal welfare laws and Panchayat rules apply to keeping a Chihuahua in Munnar?&lt;/h3&gt;&lt;p&gt;Pet owners across Old Munnar and Mattupetty Road must comply with local Kerala Panchayat regulations by keeping core vaccinations up to date and maintaining valid health records. Before purchasing, prospective owners are encouraged to review ethical pet care standards or consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;rescue dog networks in Kerala&lt;/a&gt; for adoption alternatives in the High Range region.&lt;/p&gt;&lt;h3&gt;How can I report poor breeding conditions or animal mistreatment near Munnar Market?&lt;/h3&gt;&lt;p&gt;If you encounter unauthorized breeding facilities, poor health practices, or mistreatment near the Tea Museum or commercial areas, you can reach out to &lt;a href="https://www.petaindia.com"&gt;animal cruelty reporting organizations&lt;/a&gt; to submit a formal complaint to authorities.&lt;/p&gt;&lt;h3&gt;Is the cool mountain climate of Munnar safe for short-haired Chihuahua puppies?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas can thrive in Munnar's high-altitude climate provided they receive adequate thermal protection. Equipping your puppy with warm sweaters and keeping indoor spaces climate-controlled ensures they stay safe during cold spells in Old Munnar.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -3489,21 +3511,21 @@
       <c r="F46" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="2" t="s">
         <v>361</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="I46" s="2" t="s">
         <v>363</v>
       </c>
       <c r="J46" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A46 &amp; "" located in "" &amp; B46 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A46 &amp; "" Care Guide and Maintenance Costs in "" &amp; B46 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B46 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Wayanad, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in the chilly, high-altitude terrain of Wayanad demands a tailored wellness approach focused on thermal protection and proper nutrition. Due to thei"&amp;"r small size and low tolerance for cold mountain dampness across towns like Kalpetta, Sulthan Bathery, and Mananthavady, these puppies require warm fleece sweaters, elevated bedding, and draft-free indoor spaces to prevent respiratory strain. Provide high"&amp;"-calorie, nutrient-dense kibble formulated for toy breeds to support their fast metabolism, along with daily oral hygiene to safeguard against early dental issues. Navigating high humidity during monsoon seasons also increases the need for strict tick and"&amp;" flea prevention and regular ear cleaning. Annual care and maintenance costs in Wayanad typically range between ₹15,000 and ₹35,000, covering quality puppy food, routine veterinary checkups, vaccinations, parasite control, and essential winter accessories"&amp;".")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A46 &amp; "" located in "" &amp; B46 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A46 &amp; "" Care Guide and Maintenance Costs in "" &amp; B46 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B46 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Wayanad, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in the chilly, high-altitude terrain of Wayanad demands a tailored wellness approach focused on thermal protection and proper nutrition. Due to thei"&amp;"r small size and low tolerance for cold mountain dampness across towns like Kalpetta, Sulthan Bathery, and Mananthavady, these puppies require warm fleece sweaters, elevated bedding, and draft-free indoor spaces to prevent respiratory strain. Provide high"&amp;"-calorie, nutrient-dense kibble formulated for toy breeds to support their fast metabolism, along with daily oral hygiene to safeguard against early dental issues. Navigating high humidity during monsoon seasons also increases the need for strict tick and"&amp;" flea prevention and regular ear cleaning. Annual care and maintenance costs in Wayanad typically range between ₹15,000 and ₹35,000, covering quality puppy food, routine veterinary checkups, vaccinations, parasite control, and essential winter accessories"&amp;".")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Wayanad, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in the chilly, high-altitude terrain of Wayanad demands a tailored wellness approach focused on thermal protection and proper nutrition. Due to their small size and low tolerance for cold mountain dampness across towns like Kalpetta, Sulthan Bathery, and Mananthavady, these puppies require warm fleece sweaters, elevated bedding, and draft-free indoor spaces to prevent respiratory strain. Provide high-calorie, nutrient-dense kibble formulated for toy breeds to support their fast metabolism, along with daily oral hygiene to safeguard against early dental issues. Navigating high humidity during monsoon seasons also increases the need for strict tick and flea prevention and regular ear cleaning. Annual care and maintenance costs in Wayanad typically range between ₹15,000 and ₹35,000, covering quality puppy food, routine veterinary checkups, vaccinations, parasite control, and essential winter accessories.</v>
       </c>
       <c r="K46" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A46 &amp; "" in "" &amp; B46 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A46 &amp; "" in "" &amp; B46 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3513,11 +3535,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Wayanad, Kerala - FAQs&lt;/h2&gt;&lt;h3&gt;What local animal welfare laws apply when bringing a Chihuahua puppy to Wayanad?&lt;/h3&gt;&lt;p&gt;Pet owners across Kalpetta and Sulthan Bathery must comply with Kerala state animal husbandry mandates and local Panchayath registration directives, including mandatory anti-rabies immunizations. Before purchasing, consider exploring ethical rehoming through &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; to evaluate adoption possibilities in the high-range region.&lt;/p&gt;&lt;h3&gt;Where can I find reliable veterinary care for toy breeds around Wayanad?&lt;/h3&gt;&lt;p&gt;Veterinary hospitals in Kalpetta and government pet clinics near Mananthavady offer specialized health monitoring, routine vaccinations, and cold-weather care tailored for small breeds. If you witness unethical breeding practices or neglect along the Kozhikode-Kollegal highway belt, report details to &lt;a href="https://www.petaindia.com"&gt;animal protection advocates&lt;/a&gt; to take appropriate action.&lt;/p&gt;&lt;h3&gt;How do Chihuahua puppies adapt to the chilly climate in Wayanad?&lt;/h3&gt;&lt;p&gt;Due to Wayanad's high altitude and cool mountain humidity, Chihuahua puppies require warm sweaters, padded indoor bedding, and protection from damp drafts. Keeping them indoors during heavy monsoons and providing high-calorie nutrition ensures they maintain optimal body temperature and health.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -3532,21 +3554,21 @@
       <c r="F47" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="2" t="s">
         <v>369</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I47" s="2" t="s">
         <v>371</v>
       </c>
       <c r="J47" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A47 &amp; "" located in "" &amp; B47 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A47 &amp; "" Care Guide and Maintenance Costs in "" &amp; B47 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B47 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Thrissur, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Thrissur requires a well-structured health and upkeep strategy adapted to Central Kerala's humid tropical climate and vibrant municipal environm"&amp;"ent. To safeguard your toy companion's long-term health, provide a nutrient-dense diet tailored for miniature breeds, ensure continuous indoor hydration, and maintain consistent dental brushing to avoid early periodontal issues. Navigating residential are"&amp;"as near Swaraj Round, Punkunnam, and East Fort during monsoon months introduces high humidity and seasonal rain exposure, making proactive skin fold hygiene, coat drying, and regular flea and tick preventive care essential. On average, annual maintenance "&amp;"costs in Thrissur range from ₹15,000 to ₹35,000, covering high-quality puppy kibble, routine veterinary health checkups, mandatory core immunizations, periodic deworming, and professional grooming sessions.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A47 &amp; "" located in "" &amp; B47 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A47 &amp; "" Care Guide and Maintenance Costs in "" &amp; B47 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B47 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Thrissur, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Thrissur requires a well-structured health and upkeep strategy adapted to Central Kerala's humid tropical climate and vibrant municipal environm"&amp;"ent. To safeguard your toy companion's long-term health, provide a nutrient-dense diet tailored for miniature breeds, ensure continuous indoor hydration, and maintain consistent dental brushing to avoid early periodontal issues. Navigating residential are"&amp;"as near Swaraj Round, Punkunnam, and East Fort during monsoon months introduces high humidity and seasonal rain exposure, making proactive skin fold hygiene, coat drying, and regular flea and tick preventive care essential. On average, annual maintenance "&amp;"costs in Thrissur range from ₹15,000 to ₹35,000, covering high-quality puppy kibble, routine veterinary health checkups, mandatory core immunizations, periodic deworming, and professional grooming sessions.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Thrissur, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in Thrissur requires a well-structured health and upkeep strategy adapted to Central Kerala's humid tropical climate and vibrant municipal environment. To safeguard your toy companion's long-term health, provide a nutrient-dense diet tailored for miniature breeds, ensure continuous indoor hydration, and maintain consistent dental brushing to avoid early periodontal issues. Navigating residential areas near Swaraj Round, Punkunnam, and East Fort during monsoon months introduces high humidity and seasonal rain exposure, making proactive skin fold hygiene, coat drying, and regular flea and tick preventive care essential. On average, annual maintenance costs in Thrissur range from ₹15,000 to ₹35,000, covering high-quality puppy kibble, routine veterinary health checkups, mandatory core immunizations, periodic deworming, and professional grooming sessions.</v>
       </c>
       <c r="K47" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A47 &amp; "" in "" &amp; B47 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A47 &amp; "" in "" &amp; B47 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3556,11 +3578,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Thrissur, Kerala - FAQs&lt;/h2&gt;&lt;h3&gt;What local pet registration laws apply when getting a Chihuahua puppy in Thrissur?&lt;/h3&gt;&lt;p&gt;Dog owners around Swaraj Round and Punkunnam must comply with Thrissur Municipal Corporation licensing rules, ensuring up-to-date rabies immunizations and proper microchipping. Before buying, consider checking &lt;a href="https://www.peopleforanimalsindia.org"&gt;local animal shelter programs&lt;/a&gt; to review ethical adoption alternatives in Kerala.&lt;/p&gt;&lt;h3&gt;Where can I locate nearby vet care for small breeds in Thrissur?&lt;/h3&gt;&lt;p&gt;Veterinary facilities near Patturaikkal and East Fort provide specialized health checks, vaccinations, and monsoon care routines tailored for toy breeds. If you witness unethical breeding or animal abuse in the area, report it through &lt;a href="https://www.petaindia.com"&gt;cruelty prevention channels&lt;/a&gt; immediately.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for climate conditions and apartment life in Thrissur?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in modern apartments near Sobha City Mall due to their compact size. Proper indoor climate control and routine grooming during humid monsoon periods help maintain their health and vitality.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -3575,21 +3597,21 @@
       <c r="F48" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="2" t="s">
         <v>376</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="I48" s="2" t="s">
         <v>378</v>
       </c>
       <c r="J48" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A48 &amp; "" located in "" &amp; B48 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A48 &amp; "" Care Guide and Maintenance Costs in "" &amp; B48 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B48 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in Hyderabad requires a dedicated wellness strategy adapted to high-rise apartment living and the region's warm, dry microclimate. To support their high m"&amp;"etabolism and prevent hypoglycemia, provide nutrient-dense, small-breed puppy kibble, maintain consistent indoor climate control during intense summer heatwaves, and establish a daily oral hygiene routine to avoid early periodontal issues. Navigating urba"&amp;"n surroundings around HITEC City, Jubilee Hills, and Gachibowli exposes small pets to ambient dust, traffic noise, and high summer temperatures, making hydration monitoring, tick prevention, and brief evening walks near quieter residential pockets essenti"&amp;"al. On average, annual maintenance costs in Hyderabad range between ₹15,000 and ₹35,000, which accounts for premium toy-breed nutrition, routine veterinary consultations, core vaccinations, preventive deworming, and periodic grooming sessions.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A48 &amp; "" located in "" &amp; B48 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A48 &amp; "" Care Guide and Maintenance Costs in "" &amp; B48 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B48 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in Hyderabad requires a dedicated wellness strategy adapted to high-rise apartment living and the region's warm, dry microclimate. To support their high m"&amp;"etabolism and prevent hypoglycemia, provide nutrient-dense, small-breed puppy kibble, maintain consistent indoor climate control during intense summer heatwaves, and establish a daily oral hygiene routine to avoid early periodontal issues. Navigating urba"&amp;"n surroundings around HITEC City, Jubilee Hills, and Gachibowli exposes small pets to ambient dust, traffic noise, and high summer temperatures, making hydration monitoring, tick prevention, and brief evening walks near quieter residential pockets essenti"&amp;"al. On average, annual maintenance costs in Hyderabad range between ₹15,000 and ₹35,000, which accounts for premium toy-breed nutrition, routine veterinary consultations, core vaccinations, preventive deworming, and periodic grooming sessions.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in Hyderabad requires a dedicated wellness strategy adapted to high-rise apartment living and the region's warm, dry microclimate. To support their high metabolism and prevent hypoglycemia, provide nutrient-dense, small-breed puppy kibble, maintain consistent indoor climate control during intense summer heatwaves, and establish a daily oral hygiene routine to avoid early periodontal issues. Navigating urban surroundings around HITEC City, Jubilee Hills, and Gachibowli exposes small pets to ambient dust, traffic noise, and high summer temperatures, making hydration monitoring, tick prevention, and brief evening walks near quieter residential pockets essential. On average, annual maintenance costs in Hyderabad range between ₹15,000 and ₹35,000, which accounts for premium toy-breed nutrition, routine veterinary consultations, core vaccinations, preventive deworming, and periodic grooming sessions.</v>
       </c>
       <c r="K48" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A48 &amp; "" in "" &amp; B48 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A48 &amp; "" in "" &amp; B48 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3599,11 +3621,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Hyderabad - FAQs&lt;/h2&gt;&lt;h3&gt;What GHMC pet licensing laws apply to Chihuahua owners in Hyderabad?&lt;/h3&gt;&lt;p&gt;Pet owners around Jubilee Hills, Banjara Hills, and Gachibowli must register their dogs annually with the Greater Hyderabad Municipal Corporation (GHMC), ensure microchip insertion, and maintain valid rabies vaccination records. Before purchasing, consider exploring &lt;a href="https://www.peopleforanimalsindia.org"&gt;local adoption guidelines&lt;/a&gt; or rescue shelters near the Outer Ring Road corridor.&lt;/p&gt;&lt;h3&gt;Where can I find reliable veterinary care for toy breeds in Hyderabad?&lt;/h3&gt;&lt;p&gt;Veterinary clinics operating near HITEC City and Jubilee Hills offer specialized care, dental checkups, and vaccination schedules suited for Chihuahuas. If you witness unethical breeding practices or animal mistreatment near commercial hubs, report it to &lt;a href="https://www.petaindia.com"&gt;area-specific animal welfare organizations&lt;/a&gt; to protect pet safety.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for high-rise apartment living in Hyderabad?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in high-rise apartments across HITEC City and Gachibowli due to their compact size. Providing short indoor play sessions and controlled evening walks along quieter residential lanes helps them stay healthy while avoiding intense afternoon heatwaves.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -3618,21 +3640,21 @@
       <c r="F49" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="2" t="s">
         <v>382</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I49" s="2" t="s">
         <v>384</v>
       </c>
       <c r="J49" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A49 &amp; "" located in "" &amp; B49 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A49 &amp; "" Care Guide and Maintenance Costs in "" &amp; B49 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B49 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Wayanad, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in the scenic high ranges of Wayanad requires a structured wellness routine adapted to the region's cool climate and high-altitude humidity. To keep"&amp;" your toy companion thriving around Kalpetta, Sulthan Bathery, and Meppadi, prioritize high-protein nutrition formulated for small breeds, establish strict daily oral hygiene to prevent early dental disease, and provide warm fleece apparel to guard agains"&amp;"t chilly mountain drafts. Navigating damp estate trails and monsoon rainfall increases exposure to ectoparasites, ticks, and fungal skin irritation, making consistent anti-parasitic protection and careful coat drying essential. On average, annual maintena"&amp;"nce costs in Wayanad range from ₹15,000 to ₹35,000, covering premium small-kibble food, routine veterinary checkups, core vaccinations, deworming, and basic grooming supplies.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A49 &amp; "" located in "" &amp; B49 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A49 &amp; "" Care Guide and Maintenance Costs in "" &amp; B49 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B49 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Wayanad, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in the scenic high ranges of Wayanad requires a structured wellness routine adapted to the region's cool climate and high-altitude humidity. To keep"&amp;" your toy companion thriving around Kalpetta, Sulthan Bathery, and Meppadi, prioritize high-protein nutrition formulated for small breeds, establish strict daily oral hygiene to prevent early dental disease, and provide warm fleece apparel to guard agains"&amp;"t chilly mountain drafts. Navigating damp estate trails and monsoon rainfall increases exposure to ectoparasites, ticks, and fungal skin irritation, making consistent anti-parasitic protection and careful coat drying essential. On average, annual maintena"&amp;"nce costs in Wayanad range from ₹15,000 to ₹35,000, covering premium small-kibble food, routine veterinary checkups, core vaccinations, deworming, and basic grooming supplies.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Wayanad, Kerala&lt;/h2&gt;Caring for a Chihuahua puppy in the scenic high ranges of Wayanad requires a structured wellness routine adapted to the region's cool climate and high-altitude humidity. To keep your toy companion thriving around Kalpetta, Sulthan Bathery, and Meppadi, prioritize high-protein nutrition formulated for small breeds, establish strict daily oral hygiene to prevent early dental disease, and provide warm fleece apparel to guard against chilly mountain drafts. Navigating damp estate trails and monsoon rainfall increases exposure to ectoparasites, ticks, and fungal skin irritation, making consistent anti-parasitic protection and careful coat drying essential. On average, annual maintenance costs in Wayanad range from ₹15,000 to ₹35,000, covering premium small-kibble food, routine veterinary checkups, core vaccinations, deworming, and basic grooming supplies.</v>
       </c>
       <c r="K49" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A49 &amp; "" in "" &amp; B49 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A49 &amp; "" in "" &amp; B49 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3642,11 +3664,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Wayanad, Kerala - FAQs&lt;/h2&gt;&lt;h3&gt;What local animal welfare laws and registration rules apply in Wayanad?&lt;/h3&gt;&lt;p&gt;Pet owners across Kalpetta and Sulthan Bathery must comply with local Panchayat and District Animal Husbandry department regulations, ensuring mandatory microchipping and valid anti-rabies immunizations. Prior to purchasing, consider reviewing ethical breeding standards or reaching out to &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue groups&lt;/a&gt; to explore rehoming options.&lt;/p&gt;&lt;h3&gt;How can I find reliable veterinary care for a Chihuahua puppy near Mananthavady or Meppadi?&lt;/h3&gt;&lt;p&gt;Veterinary centers along the Kozhikode-Mysore Highway corridor offer routine health checks, vaccinations, and advice on managing high-altitude humidity for small breeds. If you encounter mistreatment or unethical breeding practices in the district, report the violation through &lt;a href="https://www.petaindia.com"&gt;cruelty prevention channels&lt;/a&gt;.&lt;/p&gt;&lt;h3&gt;Are Chihuahuas suitable for the cool, damp climate of the Wayanad high ranges?&lt;/h3&gt;&lt;p&gt;Yes, but because of their minimal body fat, Chihuahuas need warm clothing during chilly mountain mornings and careful drying after damp walks near estate trails to avoid cold-induced respiratory issues.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -3661,21 +3683,21 @@
       <c r="F50" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" s="2" t="s">
         <v>390</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I50" s="2" t="s">
         <v>392</v>
       </c>
       <c r="J50" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A50 &amp; "" located in "" &amp; B50 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A50 &amp; "" Care Guide and Maintenance Costs in "" &amp; B50 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B50 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Jubilee Hills, Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in upscale Jubilee Hills requires a dedicated care routine tailored for high-rise apartment living and warmer climate conditions. To foster"&amp;" optimal development around areas like Road No. 36 and KBR National Park, provide nutrient-rich toy-breed kibble, maintain routine oral hygiene to mitigate early dental crowding, and schedule brief, shaded evening walks to prevent heat stress. Navigating "&amp;"urban high-rise settings and local humidity demands consistent tick control, hydration monitoring, and indoor mental engagement. On average, annual maintenance costs in Jubilee Hills range from ₹18,000 to ₹40,000, which covers high-grade puppy nutrition, "&amp;"routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A50 &amp; "" located in "" &amp; B50 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A50 &amp; "" Care Guide and Maintenance Costs in "" &amp; B50 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B50 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Jubilee Hills, Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in upscale Jubilee Hills requires a dedicated care routine tailored for high-rise apartment living and warmer climate conditions. To foster"&amp;" optimal development around areas like Road No. 36 and KBR National Park, provide nutrient-rich toy-breed kibble, maintain routine oral hygiene to mitigate early dental crowding, and schedule brief, shaded evening walks to prevent heat stress. Navigating "&amp;"urban high-rise settings and local humidity demands consistent tick control, hydration monitoring, and indoor mental engagement. On average, annual maintenance costs in Jubilee Hills range from ₹18,000 to ₹40,000, which covers high-grade puppy nutrition, "&amp;"routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Jubilee Hills, Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in upscale Jubilee Hills requires a dedicated care routine tailored for high-rise apartment living and warmer climate conditions. To foster optimal development around areas like Road No. 36 and KBR National Park, provide nutrient-rich toy-breed kibble, maintain routine oral hygiene to mitigate early dental crowding, and schedule brief, shaded evening walks to prevent heat stress. Navigating urban high-rise settings and local humidity demands consistent tick control, hydration monitoring, and indoor mental engagement. On average, annual maintenance costs in Jubilee Hills range from ₹18,000 to ₹40,000, which covers high-grade puppy nutrition, routine veterinary checkups, core vaccinations, deworming, and periodic professional grooming.</v>
       </c>
       <c r="K50" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A50 &amp; "" in "" &amp; B50 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A50 &amp; "" in "" &amp; B50 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3685,11 +3707,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Jubilee Hills, Hyderabad - FAQs&lt;/h2&gt;&lt;h3&gt;What GHMC licensing requirements apply to Chihuahua puppies in Jubilee Hills?&lt;/h3&gt;&lt;p&gt;Pet parents residing around Road No. 36 and Road No. 45 must secure a valid Greater Hyderabad Municipal Corporation (GHMC) pet permit, register microchip information, and ensure up-to-date rabies immunizations. Prospective owners are encouraged to review ethical breeding standards or contact &lt;a href="https://www.peopleforanimalsindia.org"&gt;local rescue organizations&lt;/a&gt; to consider adoption options.&lt;/p&gt;&lt;h3&gt;Where can I find specialized veterinary care for toy breeds near Jubilee Hills?&lt;/h3&gt;&lt;p&gt;Veterinary facilities near Peddamma Gudi Metro Station and KBR National Park offer dedicated clinical care, pediatric immunizations, and routine health evaluations for small breeds. If you witness unethical breeding practices or animal abuse around upscale residential sectors, report the incident to &lt;a href="https://www.petaindia.com"&gt;cruelty prevention representatives&lt;/a&gt; immediately.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for high-rise apartment living in Jubilee Hills?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in luxury high-rise apartments near Durgam Cheruvu Cable Bridge due to their compact size. Daily indoor mental stimulation along with short, shaded strolls near quiet neighborhood lanes keeps them healthy and energetic.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -3704,21 +3726,21 @@
       <c r="F51" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="2" t="s">
         <v>398</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="I51" s="2" t="s">
         <v>400</v>
       </c>
       <c r="J51" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A51 &amp; "" located in "" &amp; B51 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A51 &amp; "" Care Guide and Maintenance Costs in "" &amp; B51 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B51 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Banjara Hills, Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in the prestigious enclave of Banjara Hills requires a dedicated wellness regimen adapted to Hyderabad's warm climate and high-rise urban l"&amp;"ifestyle. To support long-term health, provide high-protein nutrition formulated specifically for toy breeds, ensure reliable indoor climate control during hot summer months to prevent heat stress, and implement strict daily dental hygiene to guard agains"&amp;"t early periodontal disease. Managed outdoor exercise along quieter avenues near Road No. 12 or near Kasu Brahmananda Reddy National Park during cooler morning or evening hours provides vital mental stimulation while avoiding harsh pavement heat. On avera"&amp;"ge, annual upkeep and maintenance costs in Banjara Hills range between ₹18,000 and ₹40,000, encompassing premium toy-breed nutrition, routine veterinary checkups, core vaccinations, preventative parasite care, and periodic professional grooming.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A51 &amp; "" located in "" &amp; B51 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A51 &amp; "" Care Guide and Maintenance Costs in "" &amp; B51 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B51 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Banjara Hills, Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in the prestigious enclave of Banjara Hills requires a dedicated wellness regimen adapted to Hyderabad's warm climate and high-rise urban l"&amp;"ifestyle. To support long-term health, provide high-protein nutrition formulated specifically for toy breeds, ensure reliable indoor climate control during hot summer months to prevent heat stress, and implement strict daily dental hygiene to guard agains"&amp;"t early periodontal disease. Managed outdoor exercise along quieter avenues near Road No. 12 or near Kasu Brahmananda Reddy National Park during cooler morning or evening hours provides vital mental stimulation while avoiding harsh pavement heat. On avera"&amp;"ge, annual upkeep and maintenance costs in Banjara Hills range between ₹18,000 and ₹40,000, encompassing premium toy-breed nutrition, routine veterinary checkups, core vaccinations, preventative parasite care, and periodic professional grooming.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in Banjara Hills, Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in the prestigious enclave of Banjara Hills requires a dedicated wellness regimen adapted to Hyderabad's warm climate and high-rise urban lifestyle. To support long-term health, provide high-protein nutrition formulated specifically for toy breeds, ensure reliable indoor climate control during hot summer months to prevent heat stress, and implement strict daily dental hygiene to guard against early periodontal disease. Managed outdoor exercise along quieter avenues near Road No. 12 or near Kasu Brahmananda Reddy National Park during cooler morning or evening hours provides vital mental stimulation while avoiding harsh pavement heat. On average, annual upkeep and maintenance costs in Banjara Hills range between ₹18,000 and ₹40,000, encompassing premium toy-breed nutrition, routine veterinary checkups, core vaccinations, preventative parasite care, and periodic professional grooming.</v>
       </c>
       <c r="K51" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A51 &amp; "" in "" &amp; B51 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A51 &amp; "" in "" &amp; B51 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3728,11 +3750,11 @@
         <v>&lt;h2&gt;Chihuahua Puppies in Banjara Hills, Hyderabad - FAQs&lt;/h2&gt;&lt;h3&gt;What GHMC licensing and pet ownership laws apply in Banjara Hills?&lt;/h3&gt;&lt;p&gt;Pet owners near Road No. 1 and Road No. 12 must obtain a mandatory annual GHMC pet license, ensure microchip registration, and keep rabies immunizations up to date. Prospective parents are encouraged to consult &lt;a href="https://www.peopleforanimalsindia.org"&gt;local pet rescue organizations&lt;/a&gt; to consider adoption before purchasing.&lt;/p&gt;&lt;h3&gt;Where can I locate specialized veterinary care for toy breeds in Banjara Hills?&lt;/h3&gt;&lt;p&gt;Veterinary clinics around Punjagutta and near Kasu Brahmananda Reddy National Park offer dedicated health evaluations, dental care, and vaccination protocols for small dogs. To report illegal breeding practices or mistreatment in the area, reach out to &lt;a href="https://www.petaindia.com"&gt;animal rights advocates&lt;/a&gt;.&lt;/p&gt;&lt;h3&gt;Are Chihuahua puppies suitable for high-rise apartment living near GVK One Mall?&lt;/h3&gt;&lt;p&gt;Yes, Chihuahuas thrive in apartment environments due to their compact size. Brief daily walks along quieter lanes near Road No. 10 combined with regular indoor exercise keep them mentally stimulated and physically fit.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -3747,21 +3769,21 @@
       <c r="F52" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" s="2" t="s">
         <v>406</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="I52" s="2" t="s">
         <v>408</v>
       </c>
       <c r="J52" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A52 &amp; "" located in "" &amp; B52 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A52 &amp; "" Care Guide and Maintenance Costs in "" &amp; B52 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B52 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in HITEC City, Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in Hyderabad's tech hub of HITEC City requires a dedicated wellness routine adapted to modern high-rise apartment living near Cyber Towers and"&amp;" Mindspace IT Park. To foster optimal development, provide high-quality nutrition specifically formulated for toy breeds, maintain daily oral hygiene habits to prevent early dental issues, and balance indoor play with short, controlled walks around quiete"&amp;"r spots near Durgam Cheruvu. Navigating warm local temperatures and dense urban surroundings highlights the need for indoor climate control, tick prevention, and routine grooming. On average, annual maintenance costs in HITEC City range from ₹15,000 to ₹3"&amp;"5,000, covering premium diet supplies, routine veterinary care, core vaccinations, deworming, and periodic professional grooming services.")</f>
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Act as an expert copywriter and automotive maintenance specialist. Write a unique, 1-paragraph care guide and maintenance cost breakdown for "" &amp; A52 &amp; "" located in "" &amp; B52 &amp; "". Start the output directly with an HTML h2 heading containing the vehi"&amp;"cle/service name and location (e.g., &lt;h2&gt;"" &amp; A52 &amp; "" Care Guide and Maintenance Costs in "" &amp; B52 &amp; ""&lt;/h2&gt;). Follow the heading with exactly one detailed paragraph of expert-level advice covering preventive maintenance routines, common local wear-and-t"&amp;"ear factors specific to "" &amp; B52 &amp; "", and estimated servicing costs. Ensure the content is completely original, avoids generic filler, and contains no repeated phrasing or duplicate templates across rows."")"),"&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in HITEC City, Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in Hyderabad's tech hub of HITEC City requires a dedicated wellness routine adapted to modern high-rise apartment living near Cyber Towers and"&amp;" Mindspace IT Park. To foster optimal development, provide high-quality nutrition specifically formulated for toy breeds, maintain daily oral hygiene habits to prevent early dental issues, and balance indoor play with short, controlled walks around quiete"&amp;"r spots near Durgam Cheruvu. Navigating warm local temperatures and dense urban surroundings highlights the need for indoor climate control, tick prevention, and routine grooming. On average, annual maintenance costs in HITEC City range from ₹15,000 to ₹3"&amp;"5,000, covering premium diet supplies, routine veterinary care, core vaccinations, deworming, and periodic professional grooming services.")</f>
         <v>&lt;h2&gt;Chihuahua Puppies Care Guide and Maintenance Costs in HITEC City, Hyderabad&lt;/h2&gt;Caring for a Chihuahua puppy in Hyderabad's tech hub of HITEC City requires a dedicated wellness routine adapted to modern high-rise apartment living near Cyber Towers and Mindspace IT Park. To foster optimal development, provide high-quality nutrition specifically formulated for toy breeds, maintain daily oral hygiene habits to prevent early dental issues, and balance indoor play with short, controlled walks around quieter spots near Durgam Cheruvu. Navigating warm local temperatures and dense urban surroundings highlights the need for indoor climate control, tick prevention, and routine grooming. On average, annual maintenance costs in HITEC City range from ₹15,000 to ₹35,000, covering premium diet supplies, routine veterinary care, core vaccinations, deworming, and periodic professional grooming services.</v>
       </c>
       <c r="K52" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A52 &amp; "" in "" &amp; B52 &amp; "". 
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Write 3 unique FAQs in HTML format for "" &amp; A52 &amp; "" in "" &amp; B52 &amp; "". 
 Requirements:
 1. Start the output with an &lt;h2&gt; heading containing the location and topic.
 2. Incorporate semantic and hyperlocal keywords naturally (e.g., local adoption guidelin"&amp;"es, area-specific animal welfare laws, nearby vet care).
@@ -3772,6 +3794,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>